--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G2" t="n">
         <v>2.3</v>
@@ -772,7 +772,7 @@
         <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G3" t="n">
         <v>1.62</v>
@@ -960,13 +960,13 @@
         <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J3" t="n">
         <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -984,7 +984,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>5.2</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="I4" t="n">
         <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1178,7 +1178,7 @@
         <v>2.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1345,16 +1345,16 @@
         <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K5" t="n">
         <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5.1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1363,10 +1363,10 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P5" t="n">
         <v>3.25</v>
@@ -1375,7 +1375,7 @@
         <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="S5" t="n">
         <v>2.06</v>
@@ -1396,25 +1396,25 @@
         <v>40</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
         <v>21</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1426,7 +1426,7 @@
         <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
@@ -1480,7 +1480,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="BB5" t="n">
         <v>16</v>
@@ -1489,20 +1489,20 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG5" t="n">
         <v>30</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H6" t="n">
         <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -1760,7 +1760,7 @@
         <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G10" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J12" t="n">
         <v>2.94</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.84</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>1.32</v>
       </c>
       <c r="H13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
         <v>11.5</v>
@@ -2927,10 +2927,10 @@
         <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T13" t="n">
         <v>1.73</v>
@@ -2948,25 +2948,25 @@
         <v>44</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC13" t="n">
         <v>16.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE13" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
@@ -2978,7 +2978,7 @@
         <v>25</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ13" t="n">
         <v>12</v>
@@ -2990,25 +2990,25 @@
         <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AO13" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AP13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AR13" t="n">
         <v>40</v>
       </c>
       <c r="AS13" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3020,7 +3020,7 @@
         <v>34</v>
       </c>
       <c r="AW13" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3032,7 +3032,7 @@
         <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3041,7 +3041,7 @@
         <v>11.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE13" t="n">
         <v>70</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3124,13 +3124,13 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
         <v>1.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3169,7 +3169,7 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI14" t="n">
         <v>36</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3285,16 +3285,16 @@
         <v>1.35</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
         <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3387,7 +3387,7 @@
         <v>95</v>
       </c>
       <c r="AP15" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AQ15" t="n">
         <v>42</v>
@@ -3396,16 +3396,16 @@
         <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>17.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
         <v>14.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AW15" t="n">
         <v>38</v>
@@ -3429,7 +3429,7 @@
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BE15" t="n">
         <v>34</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="H16" t="n">
         <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>310</v>
+        <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
@@ -3506,7 +3506,7 @@
         <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4273,28 +4273,28 @@
         <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P20" t="n">
         <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R20" t="n">
         <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U20" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4402,7 +4402,7 @@
         <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G21" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
@@ -4482,7 +4482,7 @@
         <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
         <v>1.74</v>
@@ -4554,10 +4554,10 @@
         <v>4.3</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>25</v>
       </c>
       <c r="AS21" t="n">
         <v>5.4</v>
@@ -4572,13 +4572,13 @@
         <v>4.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>40</v>
+        <v>5.1</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AZ21" t="n">
         <v>4.4</v>
@@ -4602,11 +4602,11 @@
         <v>11</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -4855,13 +4855,13 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
         <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q23" t="n">
         <v>2.24</v>
@@ -4870,7 +4870,7 @@
         <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
         <v>1.89</v>
@@ -4939,7 +4939,7 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.800000000000001</v>
@@ -4957,7 +4957,7 @@
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW23" t="n">
         <v>5.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="G24" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="H24" t="n">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
         <v>2.28</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>
@@ -5610,10 +5610,10 @@
         <v>1.51</v>
       </c>
       <c r="G27" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
         <v>1000</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 01:03:13</t>
+          <t>2026-03-16 03:15:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.45</v>
@@ -790,7 +790,7 @@
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="G4" t="n">
         <v>5.9</v>
@@ -1157,7 +1157,7 @@
         <v>1.73</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.7</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1348,13 +1348,13 @@
         <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K5" t="n">
         <v>4.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1375,7 +1375,7 @@
         <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="S5" t="n">
         <v>2.06</v>
@@ -1384,7 +1384,7 @@
         <v>1.52</v>
       </c>
       <c r="U5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y5" t="n">
         <v>34</v>
@@ -1402,19 +1402,19 @@
         <v>55</v>
       </c>
       <c r="AA5" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1426,7 +1426,7 @@
         <v>16.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ5" t="n">
         <v>18</v>
@@ -1453,7 +1453,7 @@
         <v>29</v>
       </c>
       <c r="AR5" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
         <v>40</v>
@@ -1480,7 +1480,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="BB5" t="n">
         <v>16</v>
@@ -1489,10 +1489,10 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BF5" t="n">
         <v>4.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
         <v>1.58</v>
@@ -1542,13 +1542,13 @@
         <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
         <v>4.6</v>
       </c>
       <c r="K6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="I9" t="n">
         <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q9" t="n">
         <v>2.18</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
         <v>3.55</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
         <v>6.8</v>
@@ -2930,10 +2930,10 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
         <v>2.28</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Y13" t="n">
         <v>55</v>
@@ -2954,19 +2954,19 @@
         <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB13" t="n">
         <v>15</v>
       </c>
       <c r="AC13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD13" t="n">
         <v>40</v>
       </c>
       <c r="AE13" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF13" t="n">
         <v>11.5</v>
@@ -2987,7 +2987,7 @@
         <v>12.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM13" t="n">
         <v>95</v>
@@ -3002,13 +3002,13 @@
         <v>38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AR13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS13" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3017,10 +3017,10 @@
         <v>15</v>
       </c>
       <c r="AV13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AW13" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
         <v>75</v>
@@ -3047,14 +3047,14 @@
         <v>70</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3124,13 +3124,13 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T14" t="n">
         <v>1.68</v>
       </c>
       <c r="U14" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>40</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC14" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>38</v>
       </c>
       <c r="AM14" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN14" t="n">
         <v>21</v>
@@ -3214,7 +3214,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AX14" t="n">
         <v>17</v>
@@ -3235,10 +3235,10 @@
         <v>23</v>
       </c>
       <c r="BD14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BE14" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BF14" t="n">
         <v>17.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="J15" t="n">
         <v>6.6</v>
@@ -3318,7 +3318,7 @@
         <v>2.06</v>
       </c>
       <c r="S15" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="T15" t="n">
         <v>1.67</v>
@@ -3336,7 +3336,7 @@
         <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>120</v>
@@ -3369,7 +3369,7 @@
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK15" t="n">
         <v>13</v>
@@ -3387,16 +3387,16 @@
         <v>95</v>
       </c>
       <c r="AP15" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AR15" t="n">
         <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>17.5</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
         <v>4.8</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q16" t="n">
         <v>2.36</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G20" t="n">
         <v>1.64</v>
@@ -4279,19 +4279,19 @@
         <v>1.27</v>
       </c>
       <c r="P20" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
       <c r="T20" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
         <v>1.94</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.96</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.62</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
         <v>3.4</v>
@@ -4751,7 +4751,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS22" t="n">
         <v>7.8</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4796,11 +4796,11 @@
         <v>6.8</v>
       </c>
       <c r="BG22" t="n">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>2.52</v>
       </c>
       <c r="H23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I23" t="n">
         <v>3.9</v>
@@ -4855,13 +4855,13 @@
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
         <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q23" t="n">
         <v>2.24</v>
@@ -4876,7 +4876,7 @@
         <v>1.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4888,7 +4888,7 @@
         <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
         <v>1000</v>
@@ -4939,16 +4939,16 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
@@ -4957,10 +4957,10 @@
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.6</v>
+        <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AX23" t="n">
         <v>12</v>
@@ -4969,32 +4969,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.7</v>
+        <v>48</v>
       </c>
       <c r="BB23" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BF23" t="n">
         <v>19.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q24" t="n">
         <v>2.28</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G27" t="n">
         <v>2.62</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 03:15:16</t>
+          <t>2026-03-16 05:27:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
         <v>6.2</v>
@@ -984,7 +984,7 @@
         <v>2.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1348,13 +1348,13 @@
         <v>5.4</v>
       </c>
       <c r="I5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1363,22 +1363,22 @@
         <v>1.02</v>
       </c>
       <c r="N5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="O5" t="n">
         <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="T5" t="n">
         <v>1.52</v>
@@ -1396,7 +1396,7 @@
         <v>38</v>
       </c>
       <c r="Y5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z5" t="n">
         <v>55</v>
@@ -1405,10 +1405,10 @@
         <v>120</v>
       </c>
       <c r="AB5" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD5" t="n">
         <v>22</v>
@@ -1435,13 +1435,13 @@
         <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM5" t="n">
         <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AO5" t="n">
         <v>36</v>
@@ -1453,10 +1453,10 @@
         <v>29</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
@@ -1471,7 +1471,7 @@
         <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
@@ -1480,10 +1480,10 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC5" t="n">
         <v>13</v>
@@ -1492,7 +1492,7 @@
         <v>20</v>
       </c>
       <c r="BE5" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BF5" t="n">
         <v>4.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
         <v>2.1</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="H10" t="n">
         <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="H12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I12" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J13" t="n">
         <v>6.8</v>
@@ -2930,7 +2930,7 @@
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T13" t="n">
         <v>1.74</v>
@@ -2945,16 +2945,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Z13" t="n">
         <v>120</v>
       </c>
       <c r="AA13" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AB13" t="n">
         <v>15</v>
@@ -3002,13 +3002,13 @@
         <v>38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AR13" t="n">
         <v>38</v>
       </c>
       <c r="AS13" t="n">
-        <v>110</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3029,10 +3029,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I14" t="n">
         <v>2.66</v>
@@ -3118,7 +3118,7 @@
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="R14" t="n">
         <v>1.47</v>
@@ -3127,7 +3127,7 @@
         <v>2.94</v>
       </c>
       <c r="T14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U14" t="n">
         <v>2.38</v>
@@ -3157,7 +3157,7 @@
         <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE14" t="n">
         <v>28</v>
@@ -3208,7 +3208,7 @@
         <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3285,16 +3285,16 @@
         <v>1.36</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I15" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K15" t="n">
         <v>6.6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>6.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3315,13 +3315,13 @@
         <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
         <v>1.87</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U15" t="n">
         <v>2.44</v>
@@ -3336,10 +3336,10 @@
         <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z15" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA15" t="n">
         <v>310</v>
@@ -3363,13 +3363,13 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK15" t="n">
         <v>13</v>
@@ -3384,25 +3384,25 @@
         <v>3.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR15" t="n">
         <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>16.5</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV15" t="n">
         <v>30</v>
@@ -3417,10 +3417,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BB15" t="n">
         <v>11.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
         <v>13.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
         <v>2.36</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4473,7 @@
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
         <v>1.89</v>
@@ -4488,7 +4488,7 @@
         <v>1.74</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4530,7 +4530,7 @@
         <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4566,19 +4566,19 @@
         <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV21" t="n">
         <v>4.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.1</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ21" t="n">
         <v>4.4</v>
@@ -4599,14 +4599,14 @@
         <v>5.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG21" t="n">
         <v>42</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.35</v>
       </c>
       <c r="I23" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J23" t="n">
         <v>3.15</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5034,13 +5034,13 @@
         <v>1.04</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 05:27:23</t>
+          <t>2026-03-16 07:39:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -772,7 +772,7 @@
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
         <v>8.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
         <v>5.1</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="I4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J4" t="n">
         <v>4.3</v>
@@ -1178,7 +1178,7 @@
         <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -1345,13 +1345,13 @@
         <v>1.64</v>
       </c>
       <c r="H5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
         <v>5.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K5" t="n">
         <v>5</v>
@@ -1369,13 +1369,13 @@
         <v>1.13</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q5" t="n">
         <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S5" t="n">
         <v>2.02</v>
@@ -1414,7 +1414,7 @@
         <v>22</v>
       </c>
       <c r="AE5" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>14.5</v>
@@ -1423,7 +1423,7 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI5" t="n">
         <v>48</v>
@@ -1435,13 +1435,13 @@
         <v>14.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM5" t="n">
         <v>55</v>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AO5" t="n">
         <v>36</v>
@@ -1453,16 +1453,16 @@
         <v>29</v>
       </c>
       <c r="AR5" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="AS5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AV5" t="n">
         <v>19</v>
@@ -1471,7 +1471,7 @@
         <v>44</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY5" t="n">
         <v>9.6</v>
@@ -1480,10 +1480,10 @@
         <v>14.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BB5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -1533,41 +1533,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.58</v>
       </c>
-      <c r="H6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.59</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
         <v>6.2</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="G8" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H8" t="n">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H9" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="K9" t="n">
         <v>3.75</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
         <v>2.18</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G10" t="n">
         <v>2.46</v>
       </c>
       <c r="H10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="J10" t="n">
         <v>3.35</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.4</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.52</v>
       </c>
       <c r="G12" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J12" t="n">
         <v>2.86</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
         <v>2.34</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -2900,13 +2900,13 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J13" t="n">
         <v>6.8</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2927,16 +2927,16 @@
         <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U13" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>44</v>
       </c>
       <c r="Y13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="Z13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AA13" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AB13" t="n">
         <v>15</v>
@@ -2975,10 +2975,10 @@
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ13" t="n">
         <v>12</v>
@@ -2993,22 +2993,22 @@
         <v>95</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP13" t="n">
         <v>38</v>
       </c>
       <c r="AQ13" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AR13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS13" t="n">
-        <v>55</v>
+        <v>110</v>
       </c>
       <c r="AT13" t="n">
         <v>13.5</v>
@@ -3029,10 +3029,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3044,17 +3044,17 @@
         <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BG13" t="n">
         <v>50</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
         <v>2.64</v>
@@ -3100,7 +3100,7 @@
         <v>3.95</v>
       </c>
       <c r="K14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O14" t="n">
         <v>1.26</v>
@@ -3124,13 +3124,13 @@
         <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T14" t="n">
         <v>1.67</v>
       </c>
       <c r="U14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3160,7 +3160,7 @@
         <v>12.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF14" t="n">
         <v>19.5</v>
@@ -3175,10 +3175,10 @@
         <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL14" t="n">
         <v>38</v>
@@ -3202,7 +3202,7 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AT14" t="n">
         <v>11.5</v>
@@ -3214,7 +3214,7 @@
         <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AX14" t="n">
         <v>17</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H15" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K15" t="n">
         <v>6.6</v>
@@ -3309,7 +3309,7 @@
         <v>1.11</v>
       </c>
       <c r="P15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
         <v>1.36</v>
@@ -3354,7 +3354,7 @@
         <v>36</v>
       </c>
       <c r="AE15" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
@@ -3363,7 +3363,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
@@ -3384,19 +3384,19 @@
         <v>3.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AQ15" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AR15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AS15" t="n">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -3473,13 +3473,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="G16" t="n">
         <v>1.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
         <v>13.5</v>
@@ -3506,7 +3506,7 @@
         <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.56</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>1.78</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>2.28</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4258,13 +4258,13 @@
         <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J20" t="n">
         <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4282,7 +4282,7 @@
         <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
@@ -4309,7 +4309,7 @@
         <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA20" t="n">
         <v>230</v>
@@ -4321,7 +4321,7 @@
         <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
         <v>120</v>
@@ -4333,7 +4333,7 @@
         <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI20" t="n">
         <v>110</v>
@@ -4363,10 +4363,10 @@
         <v>19</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>7.6</v>
@@ -4378,7 +4378,7 @@
         <v>21</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
         <v>8.199999999999999</v>
@@ -4390,7 +4390,7 @@
         <v>19</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB20" t="n">
         <v>13</v>
@@ -4402,17 +4402,17 @@
         <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
         <v>3.85</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -4473,10 +4473,10 @@
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R21" t="n">
         <v>1.37</v>
@@ -4488,7 +4488,7 @@
         <v>1.74</v>
       </c>
       <c r="U21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,34 +4497,34 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>1000</v>
@@ -4536,7 +4536,7 @@
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4545,68 +4545,68 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
         <v>25</v>
       </c>
       <c r="AS21" t="n">
-        <v>5.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
         <v>12</v>
       </c>
       <c r="BG21" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
         <v>3.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
         <v>3.55</v>
@@ -4667,7 +4667,7 @@
         <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
         <v>2.14</v>
@@ -4709,13 +4709,13 @@
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG22" t="n">
         <v>12</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT22" t="n">
         <v>8.4</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4778,29 +4778,29 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>44</v>
+        <v>8.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC22" t="n">
         <v>22</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G23" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H23" t="n">
         <v>3.35</v>
@@ -4873,10 +4873,10 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4939,16 +4939,16 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
@@ -4969,32 +4969,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6.4</v>
+        <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.4</v>
+        <v>28</v>
       </c>
       <c r="BC23" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD23" t="n">
         <v>7.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF23" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="BG23" t="n">
         <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="G24" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="H24" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5058,7 +5058,7 @@
         <v>1.63</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 07:39:32</t>
+          <t>2026-03-16 09:51:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -775,152 +775,152 @@
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.1</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="I4" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="J4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="G5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J5" t="n">
         <v>4.8</v>
@@ -1366,25 +1366,25 @@
         <v>8</v>
       </c>
       <c r="O5" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
         <v>1.41</v>
       </c>
       <c r="R5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
         <v>2.02</v>
       </c>
       <c r="T5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U5" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1417,7 +1417,7 @@
         <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
@@ -1453,16 +1453,16 @@
         <v>29</v>
       </c>
       <c r="AR5" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="AS5" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV5" t="n">
         <v>19</v>
@@ -1474,7 +1474,7 @@
         <v>13</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
         <v>14.5</v>
@@ -1489,7 +1489,7 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
         <v>42</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
         <v>6.2</v>
@@ -1736,7 +1736,7 @@
         <v>1.72</v>
       </c>
       <c r="I7" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -1760,7 +1760,7 @@
         <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="G10" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="K11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="H12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.15</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2730,7 +2730,7 @@
         <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J13" t="n">
         <v>6.8</v>
@@ -2918,10 +2918,10 @@
         <v>8.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P13" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q13" t="n">
         <v>1.38</v>
@@ -2930,7 +2930,7 @@
         <v>2.02</v>
       </c>
       <c r="S13" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.73</v>
@@ -2975,7 +2975,7 @@
         <v>11</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI13" t="n">
         <v>90</v>
@@ -2987,7 +2987,7 @@
         <v>12.5</v>
       </c>
       <c r="AL13" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AM13" t="n">
         <v>95</v>
@@ -2999,25 +2999,25 @@
         <v>100</v>
       </c>
       <c r="AP13" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AQ13" t="n">
         <v>36</v>
       </c>
       <c r="AR13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS13" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AT13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV13" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AW13" t="n">
         <v>40</v>
@@ -3032,7 +3032,7 @@
         <v>22</v>
       </c>
       <c r="BA13" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
         <v>11</v>
@@ -3044,17 +3044,17 @@
         <v>23</v>
       </c>
       <c r="BE13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3088,10 +3088,10 @@
         <v>2.68</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I14" t="n">
         <v>2.66</v>
@@ -3109,25 +3109,25 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.26</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U14" t="n">
         <v>2.4</v>
@@ -3190,10 +3190,10 @@
         <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ14" t="n">
         <v>11.5</v>
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
         <v>10.5</v>
@@ -3241,14 +3241,14 @@
         <v>34</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG14" t="n">
         <v>17</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="G15" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="J15" t="n">
         <v>6.4</v>
@@ -3309,7 +3309,7 @@
         <v>1.11</v>
       </c>
       <c r="P15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q15" t="n">
         <v>1.36</v>
@@ -3318,13 +3318,13 @@
         <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3336,7 +3336,7 @@
         <v>46</v>
       </c>
       <c r="Y15" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z15" t="n">
         <v>110</v>
@@ -3354,7 +3354,7 @@
         <v>36</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF15" t="n">
         <v>12.5</v>
@@ -3363,7 +3363,7 @@
         <v>11.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
         <v>80</v>
@@ -3375,10 +3375,10 @@
         <v>13</v>
       </c>
       <c r="AL15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM15" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN15" t="n">
         <v>3.45</v>
@@ -3393,10 +3393,10 @@
         <v>42</v>
       </c>
       <c r="AR15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AS15" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="AT15" t="n">
         <v>15</v>
@@ -3435,14 +3435,14 @@
         <v>34</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>13.5</v>
+        <v>19.5</v>
       </c>
       <c r="J16" t="n">
         <v>3.8</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="G17" t="n">
-        <v>1.78</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>2.34</v>
+        <v>1.04</v>
       </c>
       <c r="I17" t="n">
         <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>2.28</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4282,7 +4282,7 @@
         <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
@@ -4309,7 +4309,7 @@
         <v>24</v>
       </c>
       <c r="Z20" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>230</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4476,13 +4476,13 @@
         <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
         <v>1.74</v>
@@ -4497,46 +4497,46 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AB21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF21" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4545,10 +4545,10 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP21" t="n">
         <v>13</v>
@@ -4557,10 +4557,10 @@
         <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS21" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4572,41 +4572,41 @@
         <v>14</v>
       </c>
       <c r="AW21" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="AX21" t="n">
         <v>11</v>
       </c>
       <c r="AY21" t="n">
-        <v>5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
         <v>15.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.8</v>
+        <v>38</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
         <v>1.39</v>
@@ -4670,13 +4670,13 @@
         <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="T22" t="n">
         <v>1.86</v>
@@ -4691,58 +4691,58 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Z22" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
         <v>70</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC22" t="n">
         <v>8.6</v>
       </c>
       <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG22" t="n">
         <v>14</v>
       </c>
-      <c r="AE22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12</v>
-      </c>
       <c r="AH22" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AO22" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
         <v>10.5</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="AT22" t="n">
         <v>8.4</v>
@@ -4766,7 +4766,7 @@
         <v>12</v>
       </c>
       <c r="AW22" t="n">
-        <v>34</v>
+        <v>4.8</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4778,29 +4778,29 @@
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD22" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>3.35</v>
       </c>
       <c r="I23" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>3.15</v>
@@ -4873,10 +4873,10 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,70 +4885,70 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
         <v>160</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP23" t="n">
         <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR23" t="n">
         <v>18</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
@@ -4960,41 +4960,41 @@
         <v>12.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AX23" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
         <v>17</v>
       </c>
       <c r="BA23" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>4.1</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BG23" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5028,16 +5028,16 @@
         <v>1.52</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
         <v>11</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
         <v>4.4</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 09:51:18</t>
+          <t>2026-03-16 12:03:16</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,70 +766,70 @@
         <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P2" t="n">
         <v>1.63</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.24</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>1.7</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
         <v>1.83</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA2" t="n">
         <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE2" t="n">
         <v>75</v>
@@ -844,7 +844,7 @@
         <v>27</v>
       </c>
       <c r="AI2" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
         <v>34</v>
@@ -853,28 +853,28 @@
         <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO2" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ2" t="n">
         <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT2" t="n">
         <v>6.6</v>
@@ -883,51 +883,51 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BF2" t="n">
         <v>16.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.51</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>260</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="I4" t="n">
-        <v>1.76</v>
+        <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.61</v>
+        <v>1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>2.18</v>
       </c>
       <c r="O5" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.93</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="T5" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X5" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
       </c>
       <c r="Z5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
         <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL5" t="n">
         <v>48</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>23</v>
-      </c>
       <c r="AM5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>34</v>
+        <v>1.84</v>
       </c>
       <c r="AQ5" t="n">
-        <v>29</v>
+        <v>1.85</v>
       </c>
       <c r="AR5" t="n">
-        <v>46</v>
+        <v>1.91</v>
       </c>
       <c r="AS5" t="n">
-        <v>42</v>
+        <v>1.96</v>
       </c>
       <c r="AT5" t="n">
-        <v>15</v>
+        <v>1.71</v>
       </c>
       <c r="AU5" t="n">
-        <v>11</v>
+        <v>1.74</v>
       </c>
       <c r="AV5" t="n">
-        <v>19</v>
+        <v>1.96</v>
       </c>
       <c r="AW5" t="n">
-        <v>44</v>
+        <v>1.96</v>
       </c>
       <c r="AX5" t="n">
-        <v>13</v>
+        <v>1.73</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.5</v>
+        <v>1.84</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>1.96</v>
       </c>
       <c r="BB5" t="n">
-        <v>16</v>
+        <v>1.79</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>1.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>19</v>
+        <v>1.88</v>
       </c>
       <c r="BE5" t="n">
-        <v>42</v>
+        <v>1.96</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>1.96</v>
       </c>
       <c r="BG5" t="n">
-        <v>30</v>
+        <v>1.96</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>5.1</v>
       </c>
       <c r="G6" t="n">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>6.8</v>
+        <v>1.67</v>
       </c>
       <c r="I6" t="n">
-        <v>8.4</v>
+        <v>1.75</v>
       </c>
       <c r="J6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K6" t="n">
         <v>4.7</v>
       </c>
-      <c r="K6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>42</v>
+      </c>
+      <c r="BF7" t="n">
         <v>4.7</v>
       </c>
-      <c r="G7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.66</v>
+        <v>1.46</v>
       </c>
       <c r="G8" t="n">
-        <v>2.96</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>8.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>1.72</v>
       </c>
       <c r="I9" t="n">
-        <v>6.8</v>
+        <v>1.86</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.18</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.22</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7</v>
+        <v>2.64</v>
       </c>
       <c r="I10" t="n">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K10" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>2.52</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.72</v>
+        <v>2.36</v>
       </c>
       <c r="H12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.3</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>1.94</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,66 +2877,66 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.31</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
-        <v>1.32</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="K13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -2945,123 +2945,123 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,66 +3071,66 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.22</v>
+        <v>1.63</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -3139,116 +3139,116 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3303,28 +3303,28 @@
         <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R15" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S15" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="U15" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y15" t="n">
         <v>55</v>
@@ -3342,114 +3342,114 @@
         <v>110</v>
       </c>
       <c r="AA15" t="n">
-        <v>310</v>
+        <v>380</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AD15" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AE15" t="n">
         <v>130</v>
       </c>
       <c r="AF15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>13</v>
-      </c>
       <c r="AL15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
         <v>3.45</v>
       </c>
       <c r="AO15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AQ15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR15" t="n">
         <v>42</v>
       </c>
-      <c r="AR15" t="n">
-        <v>38</v>
-      </c>
       <c r="AS15" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="AT15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU15" t="n">
         <v>15</v>
       </c>
-      <c r="AU15" t="n">
-        <v>14</v>
-      </c>
       <c r="AV15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AW15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY15" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
         <v>11.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE15" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BG15" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,66 +3459,66 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>8.6</v>
       </c>
       <c r="I16" t="n">
-        <v>19.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>6.2</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,123 +3527,123 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,66 +3653,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.61</v>
+        <v>2.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>2.66</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.54</v>
+        <v>1.92</v>
       </c>
       <c r="G19" t="n">
-        <v>8.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="I19" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,66 +4235,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,66 +4429,66 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.93</v>
+        <v>2.54</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>3.85</v>
+        <v>2.04</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>2.54</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,116 +4497,116 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="G22" t="n">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>6.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>4.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,116 +4691,116 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="Y22" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB22" t="n">
         <v>13</v>
       </c>
-      <c r="Z22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU22" t="n">
+      <c r="BC22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD22" t="n">
         <v>6.6</v>
       </c>
-      <c r="AV22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BE22" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>32</v>
+        <v>7.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="G23" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="U23" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC23" t="n">
         <v>18</v>
       </c>
-      <c r="AG23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>23</v>
-      </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.52</v>
+        <v>2.42</v>
       </c>
       <c r="G24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.75</v>
       </c>
-      <c r="H24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="Q24" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB24" t="n">
         <v>11</v>
       </c>
-      <c r="J24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,66 +5205,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,7 +5770,395 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 12:03:16</t>
+          <t>2026-03-16 14:15:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-16 14:15:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Monagas</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K29" t="n">
+        <v>950</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-16 14:15:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G3" t="n">
         <v>1.55</v>
@@ -960,43 +960,43 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1014,7 +1014,7 @@
         <v>65</v>
       </c>
       <c r="AA3" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB3" t="n">
         <v>9.199999999999999</v>
@@ -1038,7 +1038,7 @@
         <v>28</v>
       </c>
       <c r="AI3" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ3" t="n">
         <v>15.5</v>
@@ -1071,7 +1071,7 @@
         <v>7.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
         <v>9.4</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.18</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -1360,25 +1360,25 @@
         <v>1.33</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
         <v>1.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.58</v>
+        <v>2.46</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1393,7 +1393,7 @@
         <v>2.66</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>36</v>
@@ -1411,7 +1411,7 @@
         <v>15.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1441,68 +1441,68 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.85</v>
+        <v>2.22</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.71</v>
+        <v>2.02</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.74</v>
+        <v>2.06</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.8</v>
+        <v>2.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.88</v>
+        <v>2.26</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.96</v>
+        <v>4.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
         <v>2.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1590,7 +1590,7 @@
         <v>21</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z6" t="n">
         <v>11.5</v>
@@ -1608,7 +1608,7 @@
         <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AF6" t="n">
         <v>44</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="AH6" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
         <v>30</v>
@@ -1665,7 +1665,7 @@
         <v>14.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY6" t="n">
         <v>17.5</v>
@@ -1674,29 +1674,29 @@
         <v>16</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE6" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC6" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7.4</v>
       </c>
       <c r="BG6" t="n">
         <v>6.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G7" t="n">
         <v>1.62</v>
@@ -1739,13 +1739,13 @@
         <v>5.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
@@ -1760,52 +1760,52 @@
         <v>3.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R7" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S7" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
         <v>1.51</v>
       </c>
       <c r="U7" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X7" t="n">
         <v>38</v>
       </c>
       <c r="Y7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Z7" t="n">
         <v>55</v>
       </c>
       <c r="AA7" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
         <v>22</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
         <v>10</v>
@@ -1814,49 +1814,49 @@
         <v>16</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
         <v>18</v>
       </c>
       <c r="AK7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN7" t="n">
         <v>5</v>
       </c>
       <c r="AO7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP7" t="n">
         <v>36</v>
       </c>
-      <c r="AP7" t="n">
-        <v>34</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AR7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS7" t="n">
         <v>42</v>
       </c>
       <c r="AT7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -1865,10 +1865,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB7" t="n">
         <v>16.5</v>
@@ -1880,17 +1880,17 @@
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -1939,152 +1939,152 @@
         <v>5.3</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P8" t="n">
         <v>2.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -2118,10 +2118,10 @@
         <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I9" t="n">
         <v>1.86</v>
@@ -2133,152 +2133,152 @@
         <v>4.4</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
         <v>2.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -2312,167 +2312,167 @@
         <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>3.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.25</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>1.01</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="H11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P11" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -2700,31 +2700,31 @@
         <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I12" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
         <v>1.91</v>
@@ -2733,134 +2733,134 @@
         <v>1.94</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -2900,161 +2900,161 @@
         <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
         <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S13" t="n">
         <v>1.01</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G14" t="n">
         <v>2.72</v>
@@ -3103,16 +3103,16 @@
         <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
@@ -3121,134 +3121,134 @@
         <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="H15" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV15" t="n">
         <v>10.5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="AW15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>380</v>
-      </c>
-      <c r="AB15" t="n">
+      <c r="AZ15" t="n">
         <v>15</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="BA15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF15" t="n">
         <v>17</v>
       </c>
-      <c r="AD15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>32</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BG15" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="G16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="H16" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3497,28 +3497,28 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="O16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="S16" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -3527,116 +3527,116 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
       </c>
       <c r="Z16" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AA16" t="n">
-        <v>310</v>
+        <v>370</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AC16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AD16" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE16" t="n">
         <v>130</v>
       </c>
       <c r="AF16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI16" t="n">
+      <c r="AL16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS16" t="n">
         <v>75</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO16" t="n">
+      <c r="AT16" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA16" t="n">
         <v>70</v>
       </c>
-      <c r="AP16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX16" t="n">
+      <c r="BB16" t="n">
         <v>11</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>48</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>12</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BG16" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -3658,61 +3658,61 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>1.37</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>1.39</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2.66</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="P17" t="n">
-        <v>2.22</v>
+        <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>1.37</v>
       </c>
       <c r="R17" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="S17" t="n">
-        <v>2.92</v>
+        <v>1.9</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="Y17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK17" t="n">
         <v>13</v>
       </c>
-      <c r="Z17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>27</v>
-      </c>
       <c r="AL17" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="AM17" t="n">
         <v>75</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.5</v>
+        <v>3.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>19.5</v>
+        <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="AQ17" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS17" t="n">
+      <c r="BD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE17" t="n">
         <v>32</v>
       </c>
-      <c r="AT17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE17" t="n">
+      <c r="BF17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG17" t="n">
         <v>55</v>
       </c>
-      <c r="BF17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>17</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.46</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="H18" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="I18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="K19" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,36 +4235,36 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.54</v>
+        <v>1.47</v>
       </c>
       <c r="G21" t="n">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>2.04</v>
+        <v>5.7</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>2.54</v>
+        <v>3.8</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1.63</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,66 +4817,66 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,66 +5011,66 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="G24" t="n">
-        <v>2.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>3.15</v>
+        <v>2.04</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>2.54</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -5079,116 +5079,116 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
@@ -5205,66 +5205,66 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.34</v>
+        <v>1.54</v>
       </c>
       <c r="G25" t="n">
-        <v>2.56</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
+        <v>4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S25" t="n">
         <v>3</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S25" t="n">
-        <v>4.2</v>
       </c>
       <c r="T25" t="n">
         <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -5273,123 +5273,123 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="Z25" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC25" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC25" t="n">
-        <v>9</v>
-      </c>
       <c r="AD25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>18</v>
       </c>
-      <c r="AE25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AK25" t="n">
         <v>17.5</v>
       </c>
-      <c r="AG25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>36</v>
-      </c>
       <c r="AL25" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9.6</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="AS25" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="AT25" t="n">
         <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>12.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF25" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BG25" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.54</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX26" t="n">
         <v>11</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,66 +5593,66 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5661,123 +5661,123 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 14:15:17</t>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.52</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.62</v>
+        <v>1000</v>
       </c>
       <c r="H29" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6028,137 +6028,719 @@
         <v>1.24</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Guarani (Par)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q30" t="n">
         <v>1.01</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-16 14:15:17</t>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:27:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Monagas</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>950</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-16 16:27:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -960,16 +960,16 @@
         <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -978,7 +978,7 @@
         <v>4.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
         <v>2.08</v>
@@ -993,43 +993,43 @@
         <v>3.25</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
         <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X3" t="n">
         <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA3" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>120</v>
       </c>
       <c r="AF3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="n">
         <v>9.800000000000001</v>
@@ -1053,22 +1053,22 @@
         <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AO3" t="n">
         <v>150</v>
       </c>
       <c r="AP3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
       </c>
       <c r="AR3" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>48</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
@@ -1080,7 +1080,7 @@
         <v>24</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AX3" t="n">
         <v>7.8</v>
@@ -1089,10 +1089,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
         <v>11.5</v>
@@ -1104,17 +1104,17 @@
         <v>32</v>
       </c>
       <c r="BE3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF3" t="n">
-        <v>7</v>
-      </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>42</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1363,16 +1363,16 @@
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O5" t="n">
         <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R5" t="n">
         <v>1.4</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>2.22</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.48</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G7" t="n">
         <v>1.62</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>5.7</v>
@@ -1745,7 +1745,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
         <v>1.02</v>
@@ -1754,7 +1754,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7" t="n">
         <v>3.3</v>
@@ -1805,7 +1805,7 @@
         <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
         <v>10</v>
@@ -1829,7 +1829,7 @@
         <v>50</v>
       </c>
       <c r="AN7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO7" t="n">
         <v>34</v>
@@ -1859,13 +1859,13 @@
         <v>48</v>
       </c>
       <c r="AX7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
         <v>42</v>
@@ -1880,7 +1880,7 @@
         <v>20</v>
       </c>
       <c r="BE7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF7" t="n">
         <v>4.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
         <v>2.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P8" t="n">
         <v>2.4</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>4.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H9" t="n">
         <v>1.73</v>
@@ -2166,7 +2166,7 @@
         <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
@@ -2274,11 +2274,11 @@
         <v>4.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.9</v>
+        <v>1.03</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
@@ -2342,7 +2342,7 @@
         <v>1.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.33</v>
       </c>
       <c r="R10" t="n">
         <v>1.25</v>
@@ -2444,7 +2444,7 @@
         <v>2.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="AZ10" t="n">
         <v>2.18</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H11" t="n">
         <v>5.8</v>
@@ -2521,7 +2521,7 @@
         <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -2548,7 +2548,7 @@
         <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
         <v>1.16</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2703,10 +2703,10 @@
         <v>2.26</v>
       </c>
       <c r="H12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
@@ -2715,13 +2715,13 @@
         <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.92</v>
+        <v>1.03</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
@@ -2739,13 +2739,13 @@
         <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
         <v>1.79</v>
@@ -2760,7 +2760,7 @@
         <v>29</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
         <v>11.5</v>
@@ -2802,7 +2802,7 @@
         <v>19.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -2814,10 +2814,10 @@
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
@@ -2826,7 +2826,7 @@
         <v>13</v>
       </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>32</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
@@ -2838,16 +2838,16 @@
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.2</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
         <v>5.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE12" t="n">
         <v>5.9</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.44</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
         <v>1000</v>
@@ -2900,19 +2900,19 @@
         <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
         <v>1.58</v>
@@ -2924,7 +2924,7 @@
         <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
         <v>1.18</v>
@@ -2942,7 +2942,7 @@
         <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>3.3</v>
@@ -3100,19 +3100,19 @@
         <v>2.94</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="P14" t="n">
         <v>1.63</v>
@@ -3121,134 +3121,134 @@
         <v>2.3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG14" t="n">
         <v>13</v>
       </c>
-      <c r="Z14" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY14" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>2.94</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>3.15</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>28</v>
+        <v>6.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.45</v>
+        <v>7</v>
       </c>
       <c r="BE14" t="n">
-        <v>3.65</v>
+        <v>7.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G15" t="n">
         <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I15" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J15" t="n">
         <v>3.95</v>
@@ -3297,7 +3297,7 @@
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
@@ -3309,7 +3309,7 @@
         <v>1.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q15" t="n">
         <v>1.74</v>
@@ -3318,7 +3318,7 @@
         <v>1.48</v>
       </c>
       <c r="S15" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
         <v>1.66</v>
@@ -3327,10 +3327,10 @@
         <v>2.42</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
         <v>19</v>
@@ -3348,25 +3348,25 @@
         <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
         <v>12</v>
       </c>
       <c r="AE15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF15" t="n">
         <v>19.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ15" t="n">
         <v>40</v>
@@ -3375,43 +3375,43 @@
         <v>27</v>
       </c>
       <c r="AL15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN15" t="n">
         <v>19.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BF15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
         <v>17</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3488,10 +3488,10 @@
         <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
@@ -3518,16 +3518,16 @@
         <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
         <v>55</v>
@@ -3536,19 +3536,19 @@
         <v>110</v>
       </c>
       <c r="AA16" t="n">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AB16" t="n">
         <v>15</v>
       </c>
       <c r="AC16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AD16" t="n">
         <v>38</v>
       </c>
       <c r="AE16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -3557,7 +3557,7 @@
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI16" t="n">
         <v>90</v>
@@ -3569,7 +3569,7 @@
         <v>12.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM16" t="n">
         <v>90</v>
@@ -3578,7 +3578,7 @@
         <v>3.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP16" t="n">
         <v>38</v>
@@ -3587,16 +3587,16 @@
         <v>46</v>
       </c>
       <c r="AR16" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AS16" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AT16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AV16" t="n">
         <v>34</v>
@@ -3626,17 +3626,17 @@
         <v>23</v>
       </c>
       <c r="BE16" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BG16" t="n">
         <v>46</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G17" t="n">
         <v>1.37</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.39</v>
-      </c>
       <c r="H17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I17" t="n">
         <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M17" t="n">
         <v>1.02</v>
@@ -3700,7 +3700,7 @@
         <v>3.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R17" t="n">
         <v>2.04</v>
@@ -3712,25 +3712,25 @@
         <v>1.63</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="X17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Y17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z17" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA17" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AB17" t="n">
         <v>16.5</v>
@@ -3742,31 +3742,31 @@
         <v>34</v>
       </c>
       <c r="AE17" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AF17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
         <v>21</v>
       </c>
       <c r="AI17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ17" t="n">
         <v>13.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM17" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN17" t="n">
         <v>3.6</v>
@@ -3775,13 +3775,13 @@
         <v>70</v>
       </c>
       <c r="AP17" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ17" t="n">
         <v>42</v>
       </c>
       <c r="AR17" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AS17" t="n">
         <v>50</v>
@@ -3790,25 +3790,25 @@
         <v>14.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW17" t="n">
         <v>38</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>10</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB17" t="n">
         <v>12</v>
@@ -3820,17 +3820,17 @@
         <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG17" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
         <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.71</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4449,164 +4449,164 @@
         <v>1.6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
         <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P21" t="n">
         <v>1.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
         <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>3.35</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5043,16 +5043,16 @@
         <v>950</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
@@ -5061,134 +5061,134 @@
         <v>1.01</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="H26" t="n">
         <v>3.95</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
         <v>2.16</v>
@@ -5667,7 +5667,7 @@
         <v>13</v>
       </c>
       <c r="Z27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
         <v>70</v>
@@ -5724,7 +5724,7 @@
         <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT27" t="n">
         <v>8.4</v>
@@ -5751,13 +5751,13 @@
         <v>4.8</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE27" t="n">
         <v>5</v>
@@ -5766,11 +5766,11 @@
         <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5813,7 @@
         <v>3.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.67</v>
       </c>
       <c r="G29" t="n">
-        <v>1000</v>
+        <v>1.82</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 16:27:12</t>
+          <t>2026-03-16 18:37:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10:00:00</t>
+          <t>08:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Shamakhi FK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Araz Nakhchivan PFK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="G2" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>2.66</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>1.45</v>
       </c>
       <c r="O2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.45</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q2" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>2.12</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W2" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX2" t="n">
         <v>12</v>
       </c>
-      <c r="Y2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AY2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE2" t="n">
         <v>50</v>
       </c>
-      <c r="AM2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6</v>
-      </c>
       <c r="BF2" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ferencvaros</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>1.55</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.9</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S3" t="n">
         <v>4.2</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="T3" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>2.84</v>
+        <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN3" t="n">
         <v>24</v>
       </c>
-      <c r="Z3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AO3" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK3" t="n">
+      <c r="AR3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF3" t="n">
         <v>16.5</v>
       </c>
-      <c r="AL3" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG3" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ukrainian Premier League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FK Kudrivka</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Polissya Zhytomyr</t>
+          <t>Ferencvaros</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>1.54</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>1.25</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>1.32</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>28</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>48</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,60 +1325,60 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>FK Kudrivka</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Polissya Zhytomyr</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.32</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>2.46</v>
+        <v>1.32</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1387,122 +1387,122 @@
         <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.22</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.32</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.02</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.24</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.06</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.14</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.16</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.26</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.38</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>5.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.7</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1557,153 +1557,153 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>2.18</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>2.32</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>2.66</v>
       </c>
       <c r="X6" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>21</v>
       </c>
-      <c r="Y6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AK6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>80</v>
-      </c>
       <c r="AO6" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>17.5</v>
+        <v>2.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>2.56</v>
       </c>
       <c r="AS6" t="n">
-        <v>15</v>
+        <v>2.64</v>
       </c>
       <c r="AT6" t="n">
-        <v>17</v>
+        <v>2.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.800000000000001</v>
+        <v>2.48</v>
       </c>
       <c r="AW6" t="n">
-        <v>14.5</v>
+        <v>2.64</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>17.5</v>
+        <v>2.24</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16</v>
+        <v>2.42</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.6</v>
+        <v>2.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>2.34</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>2.36</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>2.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.8</v>
+        <v>2.64</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG6" t="n">
-        <v>6.4</v>
+        <v>2.64</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="G7" t="n">
-        <v>1.62</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>5.7</v>
+        <v>1.75</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>2.78</v>
       </c>
       <c r="T7" t="n">
-        <v>1.51</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2.82</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.21</v>
       </c>
-      <c r="W7" t="n">
-        <v>2.6</v>
-      </c>
       <c r="X7" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="Z7" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="AB7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT7" t="n">
         <v>17</v>
       </c>
-      <c r="AC7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AU7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH7" t="n">
+      <c r="AX7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>16</v>
       </c>
-      <c r="AI7" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BA7" t="n">
-        <v>42</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>46</v>
+        <v>7.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>6.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>8.4</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.7</v>
       </c>
-      <c r="K8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BG8" t="n">
-        <v>1.1</v>
+        <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,179 +2106,179 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.7</v>
       </c>
-      <c r="G9" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.85</v>
-      </c>
       <c r="K9" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>4.1</v>
+        <v>2.34</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="P9" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.21</v>
       </c>
       <c r="S9" t="n">
-        <v>2.94</v>
+        <v>2.24</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="U9" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2</v>
+        <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.5</v>
+        <v>1.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>1.1</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5</v>
+        <v>1.1</v>
       </c>
       <c r="AT9" t="n">
-        <v>14.5</v>
+        <v>1.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.5</v>
+        <v>1.1</v>
       </c>
       <c r="AX9" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>15</v>
+        <v>1.1</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14</v>
+        <v>1.1</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.8</v>
+        <v>1.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -2300,186 +2300,186 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Goztepe</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.66</v>
+        <v>4.7</v>
       </c>
       <c r="G10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.94</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V10" t="n">
-        <v>1.53</v>
+        <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="AB10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AC10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO10" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP10" t="n">
-        <v>2.12</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.08</v>
+        <v>7.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.2</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>2.3</v>
+        <v>14.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.98</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>2.26</v>
+        <v>13.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY10" t="n">
-        <v>2.1</v>
+        <v>15</v>
       </c>
       <c r="AZ10" t="n">
-        <v>2.18</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.26</v>
+        <v>4.7</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="BE10" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.38</v>
+        <v>4.7</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.38</v>
+        <v>7.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>1.84</v>
+        <v>2.94</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>2.66</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>2.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.65</v>
+        <v>1.03</v>
       </c>
       <c r="O11" t="n">
-        <v>1.43</v>
+        <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.24</v>
+        <v>1.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="X11" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>2.18</v>
       </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>1.81</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.99</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>2.24</v>
       </c>
       <c r="X12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J13" t="n">
         <v>3.5</v>
       </c>
-      <c r="J13" t="n">
-        <v>2.56</v>
-      </c>
       <c r="K13" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>1.58</v>
+        <v>1.03</v>
       </c>
       <c r="O13" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>1.94</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>2.12</v>
       </c>
       <c r="I14" t="n">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>1.26</v>
       </c>
       <c r="O14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1.44</v>
       </c>
-      <c r="P14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.59</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
         <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>2.62</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>3.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
-        <v>2.26</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.48</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR15" t="n">
         <v>19</v>
       </c>
-      <c r="Y15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ15" t="n">
+      <c r="AS15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
         <v>12.5</v>
       </c>
-      <c r="AR15" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT15" t="n">
+      <c r="AW15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX15" t="n">
         <v>13</v>
       </c>
-      <c r="AU15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>18</v>
-      </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>30</v>
+        <v>7.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>55</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -3482,22 +3482,22 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
         <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
@@ -3509,10 +3509,10 @@
         <v>1.37</v>
       </c>
       <c r="R16" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="T16" t="n">
         <v>1.72</v>
@@ -3521,7 +3521,7 @@
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
         <v>4.1</v>
@@ -3536,7 +3536,7 @@
         <v>110</v>
       </c>
       <c r="AA16" t="n">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AB16" t="n">
         <v>15</v>
@@ -3548,7 +3548,7 @@
         <v>38</v>
       </c>
       <c r="AE16" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF16" t="n">
         <v>11.5</v>
@@ -3578,7 +3578,7 @@
         <v>3.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AP16" t="n">
         <v>38</v>
@@ -3587,10 +3587,10 @@
         <v>46</v>
       </c>
       <c r="AR16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS16" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AT16" t="n">
         <v>14.5</v>
@@ -3632,11 +3632,11 @@
         <v>3.3</v>
       </c>
       <c r="BG16" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.36</v>
+        <v>2.68</v>
       </c>
       <c r="G17" t="n">
-        <v>1.37</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X17" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC17" t="n">
         <v>8.6</v>
       </c>
-      <c r="I17" t="n">
-        <v>9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="X17" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AD17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
         <v>15.5</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AI17" t="n">
         <v>34</v>
       </c>
-      <c r="AE17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="AK17" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AM17" t="n">
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.6</v>
+        <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
-        <v>38</v>
+        <v>17.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>42</v>
+        <v>12.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>75</v>
+        <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AT17" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA17" t="n">
         <v>30</v>
       </c>
-      <c r="AW17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>46</v>
-      </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.55</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="G18" t="n">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>6.2</v>
       </c>
       <c r="K18" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>1.44</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="P18" t="n">
-        <v>1.44</v>
+        <v>3.55</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>1.36</v>
       </c>
       <c r="R18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V18" t="n">
         <v>1.12</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W18" t="n">
-        <v>2.46</v>
+        <v>3.6</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>75</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>46</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>50</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -4046,55 +4046,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="G19" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="H19" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
         <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="O19" t="n">
         <v>1.46</v>
       </c>
-      <c r="O19" t="n">
-        <v>1.39</v>
-      </c>
       <c r="P19" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
         <v>1.12</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="T19" t="n">
         <v>1.01</v>
@@ -4103,10 +4103,10 @@
         <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4163,52 +4163,52 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -4240,55 +4240,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="G20" t="n">
         <v>1.8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4297,7 +4297,7 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
         <v>2.24</v>
@@ -4357,52 +4357,52 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
         <v>1.01</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,78 +4429,78 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="G21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
         <v>1.6</v>
       </c>
-      <c r="H21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>13</v>
-      </c>
-      <c r="J21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.56</v>
-      </c>
       <c r="O21" t="n">
         <v>1.01</v>
       </c>
       <c r="P21" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="R21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.17</v>
       </c>
-      <c r="S21" t="n">
-        <v>4</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="W21" t="n">
-        <v>2.66</v>
+        <v>2.24</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,34 +4509,34 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4551,69 +4551,69 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="AU21" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AY21" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BA21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" t="n">
+        <v>13</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>30</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BB22" t="n">
         <v>2.02</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>0</v>
-      </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,19 +5049,19 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="R24" t="n">
-        <v>1.02</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BB25" t="n">
         <v>1.54</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="H25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N25" t="n">
-        <v>4</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>38</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>13</v>
-      </c>
       <c r="BC25" t="n">
-        <v>14.5</v>
+        <v>1.53</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.6</v>
+        <v>1.54</v>
       </c>
       <c r="BE25" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>1.37</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.6</v>
+        <v>1.48</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -5404,61 +5404,61 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>1.54</v>
       </c>
       <c r="G26" t="n">
-        <v>2.02</v>
+        <v>1.63</v>
       </c>
       <c r="H26" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="P26" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="R26" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="U26" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -5467,116 +5467,116 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Y26" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>18</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AK26" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL26" t="n">
         <v>36</v>
       </c>
-      <c r="AA26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="AM26" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN26" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>19</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
+      <c r="AR26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB26" t="n">
         <v>13</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS26" t="n">
+      <c r="BC26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF26" t="n">
         <v>7.2</v>
       </c>
-      <c r="AT26" t="n">
+      <c r="BG26" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="G27" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="H27" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.28</v>
       </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="X27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z27" t="n">
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
         <v>25</v>
       </c>
-      <c r="AA27" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AK27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX27" t="n">
         <v>11</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AY27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE27" t="n">
         <v>8.4</v>
       </c>
-      <c r="AU27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5</v>
-      </c>
       <c r="BF27" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.8</v>
+        <v>8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -5787,36 +5787,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="I28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J28" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5825,28 +5825,28 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA28" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AB28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC28" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG28" t="n">
         <v>14</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ28" t="n">
         <v>42</v>
       </c>
       <c r="AK28" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM28" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN28" t="n">
         <v>32</v>
       </c>
       <c r="AO28" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT28" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX28" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="G29" t="n">
-        <v>1.82</v>
+        <v>2.56</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K29" t="n">
         <v>3.4</v>
       </c>
-      <c r="K29" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
@@ -6401,159 +6401,159 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,43 +6568,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P32" t="n">
         <v>1.24</v>
@@ -6613,134 +6613,328 @@
         <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 18:37:57</t>
+          <t>2026-03-16 20:48:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Monagas</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X33" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-16 20:48:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -757,58 +757,58 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="J2" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>1.45</v>
+        <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
         <v>2.2</v>
@@ -963,10 +963,10 @@
         <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -975,40 +975,40 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
         <v>1.83</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -1017,34 +1017,34 @@
         <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG3" t="n">
         <v>13</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
       </c>
       <c r="AK3" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AL3" t="n">
         <v>48</v>
@@ -1053,22 +1053,22 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO3" t="n">
         <v>90</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1077,44 +1077,44 @@
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB3" t="n">
         <v>5.5</v>
       </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BC3" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BD3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BE3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1163,7 +1163,7 @@
         <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1229,7 +1229,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
@@ -1241,7 +1241,7 @@
         <v>16.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM4" t="n">
         <v>150</v>
@@ -1259,7 +1259,7 @@
         <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="AS4" t="n">
         <v>48</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.51</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
         <v>5.1</v>
@@ -1554,149 +1554,149 @@
         <v>1.33</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.18</v>
+        <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>2.76</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
         <v>26</v>
       </c>
-      <c r="Y6" t="n">
-        <v>36</v>
-      </c>
       <c r="Z6" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB6" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC6" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BD6" t="n">
-        <v>2.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.64</v>
+        <v>7.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1784,13 +1784,13 @@
         <v>21</v>
       </c>
       <c r="Y7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z7" t="n">
         <v>11.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AB7" t="n">
         <v>22</v>
@@ -1799,7 +1799,7 @@
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AE7" t="n">
         <v>970</v>
@@ -1823,19 +1823,19 @@
         <v>65</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.800000000000001</v>
@@ -1847,7 +1847,7 @@
         <v>15</v>
       </c>
       <c r="AT7" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AU7" t="n">
         <v>8.800000000000001</v>
@@ -1859,38 +1859,38 @@
         <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BC7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG7" t="n">
         <v>7.6</v>
       </c>
-      <c r="BD7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
@@ -1987,7 +1987,7 @@
         <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AC8" t="n">
         <v>12.5</v>
@@ -2011,7 +2011,7 @@
         <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK8" t="n">
         <v>14</v>
@@ -2041,7 +2041,7 @@
         <v>42</v>
       </c>
       <c r="AT8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU8" t="n">
         <v>11.5</v>
@@ -2062,7 +2062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
@@ -2074,7 +2074,7 @@
         <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
         <v>4.7</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2139,28 +2139,28 @@
         <v>1.03</v>
       </c>
       <c r="N9" t="n">
-        <v>2.34</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q9" t="n">
         <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.21</v>
+        <v>1.54</v>
       </c>
       <c r="S9" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -2169,7 +2169,7 @@
         <v>2.8</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2178,107 +2178,107 @@
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>13</v>
       </c>
-      <c r="AD9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.1</v>
-      </c>
       <c r="BD9" t="n">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>4.7</v>
       </c>
       <c r="G10" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="n">
         <v>1.73</v>
@@ -2333,16 +2333,16 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P10" t="n">
         <v>2.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
         <v>1.43</v>
@@ -2360,7 +2360,7 @@
         <v>2.16</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="G11" t="n">
-        <v>2.94</v>
+        <v>3.3</v>
       </c>
       <c r="H11" t="n">
-        <v>2.66</v>
+        <v>2.46</v>
       </c>
       <c r="I11" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.41</v>
@@ -2533,10 +2533,10 @@
         <v>1.31</v>
       </c>
       <c r="P11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R11" t="n">
         <v>1.25</v>
@@ -2554,7 +2554,7 @@
         <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="X11" t="n">
         <v>20</v>
@@ -2614,7 +2614,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ11" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
         <v>2.2</v>
@@ -2623,13 +2623,13 @@
         <v>2.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="AU11" t="n">
         <v>1.98</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW11" t="n">
         <v>2.26</v>
@@ -2638,7 +2638,7 @@
         <v>2.2</v>
       </c>
       <c r="AY11" t="n">
-        <v>2.1</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>2.18</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
         <v>5.8</v>
@@ -2712,7 +2712,7 @@
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2724,7 +2724,7 @@
         <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P12" t="n">
         <v>1.65</v>
@@ -2733,16 +2733,16 @@
         <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S12" t="n">
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="G13" t="n">
         <v>2.26</v>
@@ -2900,70 +2900,70 @@
         <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R13" t="n">
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
         <v>1.79</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA13" t="n">
         <v>75</v>
       </c>
       <c r="AB13" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC13" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
         <v>46</v>
@@ -2972,16 +2972,16 @@
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK13" t="n">
         <v>25</v>
@@ -2996,31 +2996,31 @@
         <v>18.5</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>12</v>
       </c>
       <c r="AR13" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>7</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX13" t="n">
         <v>11.5</v>
@@ -3032,29 +3032,29 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>42</v>
+        <v>10.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="BD13" t="n">
         <v>29</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.8</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
         <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.44</v>
@@ -3133,7 +3133,7 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
         <v>1.35</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3285,13 +3285,13 @@
         <v>2.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
         <v>3.15</v>
@@ -3306,13 +3306,13 @@
         <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P15" t="n">
         <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R15" t="n">
         <v>1.23</v>
@@ -3357,7 +3357,7 @@
         <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
@@ -3396,7 +3396,7 @@
         <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -3408,41 +3408,41 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
         <v>17</v>
       </c>
       <c r="BA15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE15" t="n">
         <v>7.2</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>25</v>
       </c>
       <c r="BG15" t="n">
         <v>42</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J16" t="n">
         <v>6.8</v>
@@ -3521,7 +3521,7 @@
         <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W16" t="n">
         <v>4.1</v>
@@ -3548,10 +3548,10 @@
         <v>38</v>
       </c>
       <c r="AE16" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3587,16 +3587,16 @@
         <v>46</v>
       </c>
       <c r="AR16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AS16" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AT16" t="n">
         <v>14.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AV16" t="n">
         <v>34</v>
@@ -3614,7 +3614,7 @@
         <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BB16" t="n">
         <v>11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G17" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H17" t="n">
         <v>2.64</v>
       </c>
       <c r="I17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -3697,16 +3697,16 @@
         <v>1.26</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R17" t="n">
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3715,13 +3715,13 @@
         <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
@@ -3730,7 +3730,7 @@
         <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB17" t="n">
         <v>13.5</v>
@@ -3757,7 +3757,7 @@
         <v>34</v>
       </c>
       <c r="AJ17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK17" t="n">
         <v>26</v>
@@ -3784,13 +3784,13 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3805,32 +3805,32 @@
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
         <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG17" t="n">
         <v>16.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>8.6</v>
       </c>
       <c r="I18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
         <v>6.2</v>
@@ -3918,13 +3918,13 @@
         <v>44</v>
       </c>
       <c r="Y18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Z18" t="n">
         <v>90</v>
       </c>
       <c r="AA18" t="n">
-        <v>290</v>
+        <v>230</v>
       </c>
       <c r="AB18" t="n">
         <v>16.5</v>
@@ -3936,10 +3936,10 @@
         <v>34</v>
       </c>
       <c r="AE18" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -3966,7 +3966,7 @@
         <v>3.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
         <v>38</v>
@@ -3978,7 +3978,7 @@
         <v>75</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AT18" t="n">
         <v>15</v>
@@ -4020,11 +4020,11 @@
         <v>3.55</v>
       </c>
       <c r="BG18" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4055,64 +4055,64 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="G19" t="n">
         <v>1.68</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N19" t="n">
-        <v>1.43</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="P19" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="R19" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="S19" t="n">
-        <v>2.28</v>
+        <v>5.2</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
         <v>2.46</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,10 +4121,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4133,22 +4133,22 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4157,68 +4157,68 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4249,46 +4249,46 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
         <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K20" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P20" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
         <v>1.12</v>
       </c>
       <c r="S20" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4297,10 +4297,10 @@
         <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W20" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4443,55 +4443,55 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="G21" t="n">
         <v>1.8</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>2.66</v>
       </c>
       <c r="O21" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R21" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="V21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="W21" t="n">
         <v>2.24</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4637,64 +4637,64 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
         <v>4.4</v>
       </c>
-      <c r="L22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="V22" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,34 +4703,34 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG22" t="n">
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AK22" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="AQ22" t="n">
-        <v>14.5</v>
+        <v>3.95</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.26</v>
+        <v>4.5</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.75</v>
+        <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.86</v>
+        <v>5.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.98</v>
+        <v>3.45</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="BA22" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.26</v>
+        <v>4.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="BF22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>2.26</v>
+        <v>4.6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H23" t="n">
         <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
         <v>3.35</v>
@@ -4852,10 +4852,10 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.73</v>
+        <v>1.03</v>
       </c>
       <c r="O23" t="n">
         <v>1.33</v>
@@ -4867,16 +4867,16 @@
         <v>1.8</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T23" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
         <v>1.28</v>
@@ -4885,46 +4885,46 @@
         <v>1.84</v>
       </c>
       <c r="X23" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Y23" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
         <v>20</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>23</v>
       </c>
       <c r="AI23" t="n">
         <v>80</v>
       </c>
       <c r="AJ23" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL23" t="n">
         <v>48</v>
@@ -4942,59 +4942,59 @@
         <v>10.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>6.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT23" t="n">
         <v>7.6</v>
       </c>
       <c r="AU23" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
         <v>14</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
         <v>19.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.11</v>
+        <v>1.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="H25" t="n">
         <v>2.04</v>
@@ -5231,37 +5231,37 @@
         <v>2.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K25" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="O25" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
         <v>1.74</v>
@@ -5270,7 +5270,7 @@
         <v>1.84</v>
       </c>
       <c r="W25" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
         <v>970</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BA25" t="n">
         <v>2.02</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.52</v>
-      </c>
       <c r="BB25" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.53</v>
+        <v>2.04</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.37</v>
+        <v>1.76</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
         <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
@@ -5437,7 +5437,7 @@
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.27</v>
@@ -5479,19 +5479,19 @@
         <v>230</v>
       </c>
       <c r="AB26" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE26" t="n">
         <v>120</v>
       </c>
       <c r="AF26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
@@ -5503,7 +5503,7 @@
         <v>110</v>
       </c>
       <c r="AJ26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
         <v>17.5</v>
@@ -5515,7 +5515,7 @@
         <v>150</v>
       </c>
       <c r="AN26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
@@ -5527,10 +5527,10 @@
         <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5554,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5563,20 +5563,20 @@
         <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5613,10 +5613,10 @@
         <v>2.14</v>
       </c>
       <c r="H27" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="I27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J27" t="n">
         <v>3.5</v>
@@ -5637,13 +5637,13 @@
         <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
         <v>3.5</v>
@@ -5661,28 +5661,28 @@
         <v>1.89</v>
       </c>
       <c r="X27" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="Y27" t="n">
         <v>15</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA27" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
         <v>13.5</v>
@@ -5691,86 +5691,86 @@
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
         <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP27" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR27" t="n">
         <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
       </c>
       <c r="AU27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA27" t="n">
         <v>7.4</v>
       </c>
-      <c r="AV27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW27" t="n">
+      <c r="BB27" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE27" t="n">
         <v>7.8</v>
       </c>
-      <c r="AX27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD27" t="n">
+      <c r="BF27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG27" t="n">
         <v>7.4</v>
       </c>
-      <c r="BE27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>8</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G28" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H28" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I28" t="n">
         <v>3.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5861,19 +5861,19 @@
         <v>13</v>
       </c>
       <c r="Z28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA28" t="n">
         <v>70</v>
       </c>
       <c r="AB28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>48</v>
@@ -5891,13 +5891,13 @@
         <v>65</v>
       </c>
       <c r="AJ28" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK28" t="n">
         <v>32</v>
       </c>
       <c r="AL28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
         <v>140</v>
@@ -5906,7 +5906,7 @@
         <v>32</v>
       </c>
       <c r="AO28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP28" t="n">
         <v>10.5</v>
@@ -5918,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5930,7 +5930,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX28" t="n">
         <v>14</v>
@@ -5942,29 +5942,29 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BB28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G29" t="n">
         <v>2.56</v>
       </c>
       <c r="H29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
         <v>3.6</v>
@@ -6025,16 +6025,16 @@
         <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R29" t="n">
         <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T29" t="n">
         <v>1.89</v>
@@ -6058,7 +6058,7 @@
         <v>28</v>
       </c>
       <c r="AA29" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
         <v>10.5</v>
@@ -6067,7 +6067,7 @@
         <v>9</v>
       </c>
       <c r="AD29" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE29" t="n">
         <v>60</v>
@@ -6076,31 +6076,31 @@
         <v>17.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ29" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK29" t="n">
         <v>36</v>
       </c>
       <c r="AL29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
         <v>160</v>
       </c>
       <c r="AN29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
         <v>9.6</v>
@@ -6109,22 +6109,22 @@
         <v>9.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
         <v>7.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV29" t="n">
         <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
         <v>12.5</v>
@@ -6136,29 +6136,29 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6195,10 +6195,10 @@
         <v>1.82</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
@@ -6207,152 +6207,152 @@
         <v>3.95</v>
       </c>
       <c r="L30" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
         <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V30" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X30" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD30" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF30" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ30" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AK30" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.32</v>
+        <v>1.61</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.83</v>
+        <v>5.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.95</v>
+        <v>4.4</v>
       </c>
       <c r="AV30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AZ30" t="n">
         <v>2.18</v>
       </c>
-      <c r="AW30" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>2.2</v>
-      </c>
       <c r="BA30" t="n">
-        <v>2.32</v>
+        <v>1.6</v>
       </c>
       <c r="BB30" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BD30" t="n">
         <v>2.12</v>
       </c>
-      <c r="BC30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BE30" t="n">
-        <v>2.32</v>
+        <v>1.61</v>
       </c>
       <c r="BF30" t="n">
-        <v>2.32</v>
+        <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>2.32</v>
+        <v>1.61</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6401,13 +6401,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
         <v>1.44</v>
@@ -6416,13 +6416,13 @@
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R31" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6491,52 +6491,52 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
         <v>1.01</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
@@ -6613,7 +6613,7 @@
         <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
         <v>1.01</v>
@@ -6685,52 +6685,52 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>
@@ -6771,103 +6771,103 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.04</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="H33" t="n">
         <v>3.65</v>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="R33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.27</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="X33" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
         <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.91</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 20:48:27</t>
+          <t>2026-03-16 22:57:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J2" t="n">
         <v>2.94</v>
       </c>
-      <c r="H2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="I2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.74</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
@@ -805,10 +805,10 @@
         <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -981,10 +981,10 @@
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.25</v>
@@ -1002,7 +1002,7 @@
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X3" t="n">
         <v>13</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G4" t="n">
         <v>1.54</v>
@@ -1160,7 +1160,7 @@
         <v>4.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1184,10 +1184,10 @@
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U4" t="n">
         <v>1.89</v>
@@ -1205,7 +1205,7 @@
         <v>24</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
         <v>1000</v>
@@ -1235,7 +1235,7 @@
         <v>110</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK4" t="n">
         <v>16.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
@@ -1835,7 +1835,7 @@
         <v>8.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
         <v>8.800000000000001</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -1990,16 +1990,16 @@
         <v>17.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -2032,7 +2032,7 @@
         <v>36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AR8" t="n">
         <v>50</v>
@@ -2062,7 +2062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,70 +2106,70 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55</v>
+        <v>970</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="J9" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
         <v>1.03</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.9</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="R9" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2178,25 +2178,25 @@
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2208,77 +2208,77 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2309,177 +2309,177 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9</v>
+        <v>970</v>
       </c>
       <c r="H10" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>1.86</v>
+        <v>970</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>1.06</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.77</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="G11" t="n">
-        <v>3.3</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>2.46</v>
+        <v>6.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="S11" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.46</v>
+        <v>2.8</v>
       </c>
       <c r="X11" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AB11" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
         <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AF11" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="AL11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
         <v>9.4</v>
       </c>
-      <c r="AR11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AV11" t="n">
-        <v>10.5</v>
+        <v>6.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.26</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>2.2</v>
+        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>2.18</v>
+        <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>2.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.26</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.38</v>
+        <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.38</v>
+        <v>7.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
         <v>7.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -2724,7 +2724,7 @@
         <v>1.65</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P12" t="n">
         <v>1.65</v>
@@ -2739,16 +2739,16 @@
         <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -2972,7 +2972,7 @@
         <v>15</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>18</v>
@@ -3008,7 +3008,7 @@
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>8.6</v>
@@ -3032,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB13" t="n">
         <v>25</v>
@@ -3044,7 +3044,7 @@
         <v>29</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BF13" t="n">
         <v>13</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3106,19 +3106,19 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
         <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.45</v>
@@ -3378,10 +3378,10 @@
         <v>55</v>
       </c>
       <c r="AM15" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
         <v>60</v>
@@ -3396,7 +3396,7 @@
         <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -3408,7 +3408,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3420,10 +3420,10 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC15" t="n">
         <v>6.4</v>
@@ -3432,7 +3432,7 @@
         <v>6.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF15" t="n">
         <v>25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="G16" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="I16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -3497,146 +3497,146 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
         <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="T16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="X16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Z16" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>360</v>
+        <v>230</v>
       </c>
       <c r="AB16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AE16" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AF16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI16" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AJ16" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AK16" t="n">
         <v>12.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="AP16" t="n">
         <v>38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AR16" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AS16" t="n">
         <v>110</v>
       </c>
       <c r="AT16" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU16" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AW16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BB16" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3691,10 +3691,10 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
         <v>2.3</v>
@@ -3706,7 +3706,7 @@
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3715,7 +3715,7 @@
         <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="H18" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
         <v>1.21</v>
@@ -3885,146 +3885,146 @@
         <v>1.02</v>
       </c>
       <c r="N18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
         <v>1.12</v>
       </c>
       <c r="P18" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R18" t="n">
         <v>2.04</v>
       </c>
       <c r="S18" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="T18" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="X18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z18" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="AB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC18" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC18" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AE18" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AF18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK18" t="n">
         <v>12.5</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AM18" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AP18" t="n">
         <v>38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AR18" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="AS18" t="n">
         <v>110</v>
       </c>
       <c r="AT18" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU18" t="n">
         <v>15</v>
       </c>
-      <c r="AU18" t="n">
-        <v>14</v>
-      </c>
       <c r="AV18" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AW18" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BA18" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BB18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BC18" t="n">
         <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4046,73 +4046,73 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="G19" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="H19" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>5.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="O19" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.62</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="X19" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
         <v>1000</v>
@@ -4121,10 +4121,10 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
         <v>1000</v>
@@ -4133,22 +4133,22 @@
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
         <v>1000</v>
@@ -4157,68 +4157,68 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>4.7</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>7</v>
+        <v>1.63</v>
       </c>
       <c r="AS19" t="n">
-        <v>7.4</v>
+        <v>1.34</v>
       </c>
       <c r="AT19" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="AU19" t="n">
         <v>4.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.4</v>
+        <v>2.18</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="AX19" t="n">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="AY19" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ19" t="n">
-        <v>6.6</v>
+        <v>2.24</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.4</v>
+        <v>1.33</v>
       </c>
       <c r="BB19" t="n">
-        <v>13.5</v>
+        <v>2.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>2.2</v>
       </c>
       <c r="BD19" t="n">
-        <v>7</v>
+        <v>1.65</v>
       </c>
       <c r="BE19" t="n">
-        <v>7.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>1.69</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>1.27</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4434,73 +4434,73 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>7.6</v>
       </c>
       <c r="I21" t="n">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.11</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.21</v>
-      </c>
       <c r="W21" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,10 +4509,10 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>1000</v>
@@ -4521,22 +4521,22 @@
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI21" t="n">
         <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL21" t="n">
         <v>1000</v>
@@ -4545,68 +4545,68 @@
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.7</v>
+        <v>7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.63</v>
+        <v>7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.34</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AU21" t="n">
         <v>4.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AY21" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.24</v>
+        <v>6.6</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>2.18</v>
+        <v>13.5</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.2</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.34</v>
+        <v>7.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.27</v>
+        <v>7.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="H22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I22" t="n">
         <v>12.5</v>
@@ -4658,7 +4658,7 @@
         <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="N22" t="n">
         <v>2.64</v>
@@ -4688,7 +4688,7 @@
         <v>1.1</v>
       </c>
       <c r="W22" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -4709,7 +4709,7 @@
         <v>11.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
@@ -4745,7 +4745,7 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ22" t="n">
         <v>3.95</v>
@@ -4760,22 +4760,22 @@
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW22" t="n">
         <v>4.6</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA22" t="n">
         <v>4.6</v>
@@ -4796,11 +4796,11 @@
         <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -4855,10 +4855,10 @@
         <v>1.07</v>
       </c>
       <c r="N23" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P23" t="n">
         <v>1.73</v>
@@ -4894,7 +4894,7 @@
         <v>30</v>
       </c>
       <c r="AA23" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB23" t="n">
         <v>9.4</v>
@@ -4945,7 +4945,7 @@
         <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS23" t="n">
         <v>7.2</v>
@@ -4975,7 +4975,7 @@
         <v>7.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
         <v>18.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5237,34 +5237,34 @@
         <v>3.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="O25" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R25" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
         <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V25" t="n">
         <v>1.84</v>
@@ -5327,62 +5327,62 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AW25" t="n">
         <v>2.32</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AY25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BB25" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="BC25" t="n">
         <v>2.04</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="BE25" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="G26" t="n">
         <v>1.63</v>
@@ -5422,7 +5422,7 @@
         <v>6.2</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J26" t="n">
         <v>4.2</v>
@@ -5485,7 +5485,7 @@
         <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE26" t="n">
         <v>120</v>
@@ -5527,10 +5527,10 @@
         <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5542,7 +5542,7 @@
         <v>21</v>
       </c>
       <c r="AW26" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AX26" t="n">
         <v>8.199999999999999</v>
@@ -5554,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5563,20 +5563,20 @@
         <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -5879,13 +5879,13 @@
         <v>48</v>
       </c>
       <c r="AF28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI28" t="n">
         <v>65</v>
@@ -5918,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5930,7 +5930,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX28" t="n">
         <v>14</v>
@@ -5942,29 +5942,29 @@
         <v>16.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.3</v>
+        <v>44</v>
       </c>
       <c r="BB28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>2.56</v>
       </c>
       <c r="H29" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I29" t="n">
         <v>3.6</v>
@@ -6037,10 +6037,10 @@
         <v>4.3</v>
       </c>
       <c r="T29" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U29" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V29" t="n">
         <v>1.38</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6410,13 +6410,13 @@
         <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>
@@ -6789,28 +6789,28 @@
         <v>5.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M33" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
         <v>1.59</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6934,7 +6934,1171 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-16 22:57:54</t>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="K34" t="n">
+        <v>950</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>18</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X36" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X37" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Mexican Liga MX</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>23:07:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Leon</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K39" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N39" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-17 01:08:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -760,16 +760,16 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="H2" t="n">
         <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -799,10 +799,10 @@
         <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
         <v>2.18</v>
@@ -975,7 +975,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
@@ -993,7 +993,7 @@
         <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U3" t="n">
         <v>1.7</v>
@@ -1017,7 +1017,7 @@
         <v>120</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
@@ -1059,16 +1059,16 @@
         <v>90</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1077,10 +1077,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1089,32 +1089,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD3" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF3" t="n">
         <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1145,25 +1145,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G4" t="n">
         <v>1.54</v>
       </c>
       <c r="H4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I4" t="n">
         <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1184,13 +1184,13 @@
         <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T4" t="n">
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
@@ -1199,7 +1199,7 @@
         <v>2.84</v>
       </c>
       <c r="X4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y4" t="n">
         <v>24</v>
@@ -1208,10 +1208,10 @@
         <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC4" t="n">
         <v>10.5</v>
@@ -1223,7 +1223,7 @@
         <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
@@ -1268,7 +1268,7 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.51</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
@@ -1551,7 +1551,7 @@
         <v>5.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M6" t="n">
         <v>1.05</v>
@@ -1563,13 +1563,13 @@
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
         <v>1.72</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S6" t="n">
         <v>2.76</v>
@@ -1584,7 +1584,7 @@
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1635,22 +1635,22 @@
         <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1662,7 +1662,7 @@
         <v>21</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX6" t="n">
         <v>8.4</v>
@@ -1674,7 +1674,7 @@
         <v>18.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -1686,17 +1686,17 @@
         <v>6.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF6" t="n">
         <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J7" t="n">
         <v>4.1</v>
@@ -1757,13 +1757,13 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
         <v>2.78</v>
@@ -1775,13 +1775,13 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W7" t="n">
         <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y7" t="n">
         <v>10.5</v>
@@ -1832,13 +1832,13 @@
         <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP7" t="n">
         <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR7" t="n">
         <v>10</v>
@@ -1874,23 +1874,23 @@
         <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
         <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         <v>1.61</v>
       </c>
       <c r="H8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I8" t="n">
         <v>5.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>5.7</v>
       </c>
       <c r="J8" t="n">
         <v>4.9</v>
@@ -1948,7 +1948,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P8" t="n">
         <v>3.35</v>
@@ -1993,7 +1993,7 @@
         <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
@@ -2032,13 +2032,13 @@
         <v>36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AR8" t="n">
         <v>50</v>
       </c>
       <c r="AS8" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AT8" t="n">
         <v>16</v>
@@ -2050,7 +2050,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2059,7 +2059,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA8" t="n">
         <v>42</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G9" t="n">
         <v>970</v>
@@ -2124,7 +2124,7 @@
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="J9" t="n">
         <v>1.03</v>
@@ -2163,7 +2163,7 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G11" t="n">
         <v>1.55</v>
       </c>
       <c r="H11" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I11" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>5.2</v>
@@ -2539,10 +2539,10 @@
         <v>1.64</v>
       </c>
       <c r="R11" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
         <v>1.81</v>
@@ -2566,7 +2566,7 @@
         <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AB11" t="n">
         <v>11</v>
@@ -2578,7 +2578,7 @@
         <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF11" t="n">
         <v>10.5</v>
@@ -2611,16 +2611,16 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>20</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT11" t="n">
         <v>9</v>
@@ -2632,7 +2632,7 @@
         <v>6.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX11" t="n">
         <v>8.6</v>
@@ -2644,7 +2644,7 @@
         <v>18</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
         <v>11.5</v>
@@ -2653,20 +2653,20 @@
         <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF11" t="n">
         <v>5.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="G12" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H12" t="n">
         <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
         <v>4.2</v>
@@ -2718,10 +2718,10 @@
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>1.65</v>
+        <v>2.86</v>
       </c>
       <c r="O12" t="n">
         <v>1.44</v>
@@ -2733,22 +2733,22 @@
         <v>2.24</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2760,10 +2760,10 @@
         <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="AC12" t="n">
         <v>1000</v>
@@ -2772,7 +2772,7 @@
         <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF12" t="n">
         <v>1000</v>
@@ -2784,7 +2784,7 @@
         <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2796,7 +2796,7 @@
         <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AN12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
         <v>2.26</v>
@@ -2900,7 +2900,7 @@
         <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J13" t="n">
         <v>3.5</v>
@@ -2921,7 +2921,7 @@
         <v>1.32</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q13" t="n">
         <v>1.95</v>
@@ -2930,7 +2930,7 @@
         <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>1.75</v>
@@ -2966,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF13" t="n">
         <v>15</v>
@@ -3008,7 +3008,7 @@
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT13" t="n">
         <v>8.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>2.12</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
         <v>2.5</v>
@@ -3109,16 +3109,16 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O14" t="n">
         <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
@@ -3133,10 +3133,10 @@
         <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="H15" t="n">
         <v>3.2</v>
@@ -3303,19 +3303,19 @@
         <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O15" t="n">
         <v>1.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q15" t="n">
         <v>2.28</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
@@ -3330,7 +3330,7 @@
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X15" t="n">
         <v>11.5</v>
@@ -3363,10 +3363,10 @@
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
         <v>42</v>
@@ -3384,7 +3384,7 @@
         <v>34</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP15" t="n">
         <v>8.6</v>
@@ -3396,7 +3396,7 @@
         <v>19</v>
       </c>
       <c r="AS15" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -3408,7 +3408,7 @@
         <v>12.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3417,22 +3417,22 @@
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD15" t="n">
         <v>7</v>
       </c>
-      <c r="BB15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE15" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
         <v>25</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3512,10 +3512,10 @@
         <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
         <v>2.5</v>
@@ -3536,16 +3536,16 @@
         <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
       <c r="AB16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AC16" t="n">
         <v>15.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE16" t="n">
         <v>90</v>
@@ -3575,7 +3575,7 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AO16" t="n">
         <v>60</v>
@@ -3584,7 +3584,7 @@
         <v>38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AR16" t="n">
         <v>75</v>
@@ -3599,7 +3599,7 @@
         <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW16" t="n">
         <v>38</v>
@@ -3614,7 +3614,7 @@
         <v>19</v>
       </c>
       <c r="BA16" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BB16" t="n">
         <v>12.5</v>
@@ -3626,17 +3626,17 @@
         <v>21</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF16" t="n">
         <v>3.55</v>
       </c>
       <c r="BG16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G17" t="n">
         <v>2.7</v>
       </c>
       <c r="H17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="I17" t="n">
         <v>2.64</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -3706,7 +3706,7 @@
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3745,7 +3745,7 @@
         <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3766,7 +3766,7 @@
         <v>34</v>
       </c>
       <c r="AM17" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN17" t="n">
         <v>19</v>
@@ -3784,7 +3784,7 @@
         <v>17.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
@@ -3811,16 +3811,16 @@
         <v>30</v>
       </c>
       <c r="BB17" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD17" t="n">
         <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF17" t="n">
         <v>17</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>1.32</v>
       </c>
       <c r="H18" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
         <v>11</v>
@@ -3900,7 +3900,7 @@
         <v>2.04</v>
       </c>
       <c r="S18" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="T18" t="n">
         <v>1.72</v>
@@ -3939,7 +3939,7 @@
         <v>120</v>
       </c>
       <c r="AF18" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
@@ -3960,7 +3960,7 @@
         <v>25</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN18" t="n">
         <v>3.4</v>
@@ -3975,10 +3975,10 @@
         <v>46</v>
       </c>
       <c r="AR18" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AS18" t="n">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AT18" t="n">
         <v>14.5</v>
@@ -3987,10 +3987,10 @@
         <v>15</v>
       </c>
       <c r="AV18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AW18" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AX18" t="n">
         <v>10.5</v>
@@ -3999,10 +3999,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA18" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BB18" t="n">
         <v>11</v>
@@ -4014,17 +4014,17 @@
         <v>23</v>
       </c>
       <c r="BE18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF18" t="n">
         <v>3.3</v>
       </c>
       <c r="BG18" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4073,7 +4073,7 @@
         <v>3.95</v>
       </c>
       <c r="L19" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="M19" t="n">
         <v>1.11</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="H20" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I20" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="L20" t="n">
         <v>1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.5</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.44</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>2.44</v>
       </c>
       <c r="R20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.12</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.08</v>
-      </c>
       <c r="W20" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>1.68</v>
       </c>
       <c r="H21" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L21" t="n">
         <v>1.5</v>
@@ -4473,10 +4473,10 @@
         <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="R21" t="n">
         <v>1.16</v>
@@ -4485,7 +4485,7 @@
         <v>5.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="U21" t="n">
         <v>1.48</v>
@@ -4551,7 +4551,7 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ21" t="n">
         <v>14.5</v>
@@ -4563,7 +4563,7 @@
         <v>7.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AU21" t="n">
         <v>4.4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G22" t="n">
         <v>1.64</v>
@@ -4646,13 +4646,13 @@
         <v>7.6</v>
       </c>
       <c r="I22" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
         <v>3.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
         <v>1.01</v>
@@ -4661,28 +4661,28 @@
         <v>1.12</v>
       </c>
       <c r="N22" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P22" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T22" t="n">
         <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V22" t="n">
         <v>1.1</v>
@@ -4694,7 +4694,7 @@
         <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4721,7 +4721,7 @@
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
@@ -4730,7 +4730,7 @@
         <v>970</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT22" t="n">
         <v>4.9</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX22" t="n">
         <v>6.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BB22" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BC22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -4831,58 +4831,58 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>1.37</v>
       </c>
       <c r="I23" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N23" t="n">
-        <v>2.92</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
         <v>1.32</v>
       </c>
       <c r="P23" t="n">
-        <v>1.73</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="T23" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="X23" t="n">
         <v>14</v>
@@ -4891,10 +4891,10 @@
         <v>15.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AA23" t="n">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="AB23" t="n">
         <v>9.4</v>
@@ -4903,67 +4903,67 @@
         <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>17.5</v>
+        <v>36</v>
       </c>
       <c r="AE23" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="AF23" t="n">
         <v>13.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>880</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>95</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>550</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AR23" t="n">
         <v>20</v>
       </c>
-      <c r="AI23" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AS23" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.6</v>
+        <v>2.04</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>7.4</v>
+        <v>2.58</v>
       </c>
       <c r="AX23" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23" t="n">
         <v>9.4</v>
@@ -4972,29 +4972,29 @@
         <v>16</v>
       </c>
       <c r="BA23" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="BB23" t="n">
         <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>7.6</v>
+        <v>2.56</v>
       </c>
       <c r="BE23" t="n">
-        <v>7.4</v>
+        <v>2.6</v>
       </c>
       <c r="BF23" t="n">
         <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>7</v>
+        <v>2.6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5327,37 +5327,37 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.68</v>
+        <v>4.1</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR25" t="n">
         <v>2.1</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="AW25" t="n">
-        <v>2.32</v>
+        <v>1.98</v>
       </c>
       <c r="AX25" t="n">
         <v>1.99</v>
       </c>
       <c r="AY25" t="n">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="BA25" t="n">
         <v>2.04</v>
@@ -5366,10 +5366,10 @@
         <v>1.77</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.06</v>
+        <v>1.76</v>
       </c>
       <c r="BE25" t="n">
         <v>1.78</v>
@@ -5378,11 +5378,11 @@
         <v>1.77</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.96</v>
+        <v>1.69</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5446,7 @@
         <v>2.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R26" t="n">
         <v>1.41</v>
@@ -5479,7 +5479,7 @@
         <v>230</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
@@ -5491,7 +5491,7 @@
         <v>120</v>
       </c>
       <c r="AF26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
         <v>10.5</v>
@@ -5527,10 +5527,10 @@
         <v>19</v>
       </c>
       <c r="AR26" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT26" t="n">
         <v>7.6</v>
@@ -5554,7 +5554,7 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB26" t="n">
         <v>13</v>
@@ -5563,20 +5563,20 @@
         <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
         <v>6.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5634,10 +5634,10 @@
         <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
@@ -5649,16 +5649,16 @@
         <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U27" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V27" t="n">
         <v>1.28</v>
       </c>
       <c r="W27" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X27" t="n">
         <v>15.5</v>
@@ -5694,28 +5694,28 @@
         <v>20</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
         <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN27" t="n">
         <v>17</v>
       </c>
       <c r="AO27" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>12</v>
@@ -5724,7 +5724,7 @@
         <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT27" t="n">
         <v>7.8</v>
@@ -5736,7 +5736,7 @@
         <v>14.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX27" t="n">
         <v>10.5</v>
@@ -5757,10 +5757,10 @@
         <v>19</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
         <v>12.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G28" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="J28" t="n">
         <v>3.25</v>
@@ -5825,7 +5825,7 @@
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O28" t="n">
         <v>1.39</v>
@@ -5834,10 +5834,10 @@
         <v>1.76</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
         <v>4</v>
@@ -5891,10 +5891,10 @@
         <v>65</v>
       </c>
       <c r="AJ28" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL28" t="n">
         <v>50</v>
@@ -5918,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT28" t="n">
         <v>8.4</v>
@@ -5930,10 +5930,10 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
@@ -5951,20 +5951,20 @@
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6025,10 +6025,10 @@
         <v>1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R29" t="n">
         <v>1.25</v>
@@ -6055,16 +6055,16 @@
         <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB29" t="n">
         <v>10.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD29" t="n">
         <v>18.5</v>
@@ -6100,10 +6100,10 @@
         <v>30</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>9.6</v>
@@ -6112,7 +6112,7 @@
         <v>19.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AT29" t="n">
         <v>7.6</v>
@@ -6124,7 +6124,7 @@
         <v>12.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX29" t="n">
         <v>12.5</v>
@@ -6136,29 +6136,29 @@
         <v>17</v>
       </c>
       <c r="BA29" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF29" t="n">
         <v>20</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G30" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="H30" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I30" t="n">
         <v>7.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P30" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R30" t="n">
         <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
         <v>2.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="V30" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="X30" t="n">
         <v>970</v>
@@ -6249,7 +6249,7 @@
         <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
@@ -6264,7 +6264,7 @@
         <v>28</v>
       </c>
       <c r="AE30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
         <v>970</v>
@@ -6276,13 +6276,13 @@
         <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AJ30" t="n">
         <v>970</v>
       </c>
       <c r="AK30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
         <v>65</v>
@@ -6300,59 +6300,59 @@
         <v>4.8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.12</v>
+        <v>32</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="BB30" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="BF30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6789,7 +6789,7 @@
         <v>5.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
@@ -6798,7 +6798,7 @@
         <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
         <v>2.02</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -6968,16 +6968,16 @@
         <v>2.42</v>
       </c>
       <c r="G34" t="n">
-        <v>3.85</v>
+        <v>970</v>
       </c>
       <c r="H34" t="n">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="I34" t="n">
         <v>3.4</v>
       </c>
       <c r="J34" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="K34" t="n">
         <v>950</v>
@@ -7016,7 +7016,7 @@
         <v>1.41</v>
       </c>
       <c r="W34" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7177,7 +7177,7 @@
         <v>3.4</v>
       </c>
       <c r="L35" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
@@ -7189,7 +7189,7 @@
         <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q35" t="n">
         <v>2.06</v>
@@ -7219,7 +7219,7 @@
         <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA35" t="n">
         <v>38</v>
@@ -7231,7 +7231,7 @@
         <v>9</v>
       </c>
       <c r="AD35" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE35" t="n">
         <v>36</v>
@@ -7246,13 +7246,13 @@
         <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ35" t="n">
         <v>65</v>
       </c>
       <c r="AK35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL35" t="n">
         <v>55</v>
@@ -7261,7 +7261,7 @@
         <v>130</v>
       </c>
       <c r="AN35" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO35" t="n">
         <v>30</v>
@@ -7270,13 +7270,13 @@
         <v>11</v>
       </c>
       <c r="AQ35" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR35" t="n">
         <v>13</v>
       </c>
       <c r="AS35" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT35" t="n">
         <v>10</v>
@@ -7300,29 +7300,29 @@
         <v>15.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BG35" t="n">
         <v>18</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="G36" t="n">
-        <v>2.78</v>
+        <v>2.46</v>
       </c>
       <c r="H36" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J36" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
         <v>3.6</v>
@@ -7374,79 +7374,79 @@
         <v>1.38</v>
       </c>
       <c r="M36" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N36" t="n">
         <v>3.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P36" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R36" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U36" t="n">
         <v>2.24</v>
       </c>
       <c r="V36" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="X36" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AD36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
         <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
         <v>1000</v>
@@ -7461,62 +7461,62 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>2.18</v>
+        <v>13</v>
       </c>
       <c r="AQ36" t="n">
-        <v>2.2</v>
+        <v>12.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.38</v>
+        <v>10</v>
       </c>
       <c r="AT36" t="n">
-        <v>2.12</v>
+        <v>9.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>2.34</v>
+        <v>9.4</v>
       </c>
       <c r="AX36" t="n">
-        <v>2.22</v>
+        <v>13.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>2.12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ36" t="n">
-        <v>2.22</v>
+        <v>13.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>2.36</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB36" t="n">
-        <v>2.34</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE36" t="n">
-        <v>2.44</v>
+        <v>10.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.44</v>
+        <v>13</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7550,37 +7550,37 @@
         <v>1.88</v>
       </c>
       <c r="G37" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="H37" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I37" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M37" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N37" t="n">
         <v>3.25</v>
       </c>
       <c r="O37" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R37" t="n">
         <v>1.27</v>
@@ -7598,10 +7598,10 @@
         <v>1.2</v>
       </c>
       <c r="W37" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X37" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
@@ -7661,10 +7661,10 @@
         <v>11</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AT37" t="n">
         <v>6.2</v>
@@ -7673,10 +7673,10 @@
         <v>5.1</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AX37" t="n">
         <v>5.6</v>
@@ -7688,19 +7688,19 @@
         <v>11.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="BC37" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BE37" t="n">
         <v>2.3</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>2.42</v>
       </c>
       <c r="BF37" t="n">
         <v>9.800000000000001</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G38" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="H38" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="I38" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
@@ -7765,16 +7765,16 @@
         <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="O38" t="n">
         <v>1.11</v>
       </c>
       <c r="P38" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R38" t="n">
         <v>1.16</v>
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W38" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7849,62 +7849,62 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AR38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AZ38" t="n">
         <v>1.9</v>
       </c>
-      <c r="AS38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.88</v>
-      </c>
       <c r="BA38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BD38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BE38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BF38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BG38" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="G39" t="n">
         <v>1.51</v>
@@ -7944,16 +7944,16 @@
         <v>7.6</v>
       </c>
       <c r="I39" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K39" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L39" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M39" t="n">
         <v>1.04</v>
@@ -7980,125 +7980,125 @@
         <v>1.86</v>
       </c>
       <c r="U39" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V39" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W39" t="n">
         <v>2.96</v>
       </c>
       <c r="X39" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y39" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Z39" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA39" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC39" t="n">
         <v>12</v>
       </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>13.5</v>
       </c>
-      <c r="AD39" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AK39" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL39" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN39" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
       </c>
       <c r="AP39" t="n">
-        <v>2.34</v>
+        <v>19</v>
       </c>
       <c r="AQ39" t="n">
         <v>22</v>
       </c>
       <c r="AR39" t="n">
-        <v>48</v>
+        <v>7.6</v>
       </c>
       <c r="AS39" t="n">
-        <v>2.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU39" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV39" t="n">
         <v>22</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.34</v>
+        <v>8</v>
       </c>
       <c r="AX39" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG39" t="n">
         <v>8</v>
       </c>
-      <c r="AY39" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>11</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>2.34</v>
-      </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 01:08:34</t>
+          <t>2026-03-17 03:19:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="H2" t="n">
         <v>2.76</v>
@@ -769,7 +769,7 @@
         <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="K2" t="n">
         <v>3.4</v>
@@ -784,7 +784,7 @@
         <v>2.56</v>
       </c>
       <c r="O2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P2" t="n">
         <v>1.5</v>
@@ -808,7 +808,7 @@
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
         <v>3.6</v>
@@ -975,7 +975,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
@@ -990,22 +990,22 @@
         <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
         <v>1.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y3" t="n">
         <v>970</v>
@@ -1020,13 +1020,13 @@
         <v>8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF3" t="n">
         <v>13.5</v>
@@ -1056,19 +1056,19 @@
         <v>26</v>
       </c>
       <c r="AO3" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1077,10 +1077,10 @@
         <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.1</v>
+        <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1089,32 +1089,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD3" t="n">
         <v>6.4</v>
       </c>
-      <c r="BB3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF3" t="n">
         <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1151,7 @@
         <v>1.54</v>
       </c>
       <c r="H4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I4" t="n">
         <v>7.6</v>
@@ -1163,7 +1163,7 @@
         <v>4.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1190,7 +1190,7 @@
         <v>2.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V4" t="n">
         <v>1.15</v>
@@ -1223,7 +1223,7 @@
         <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
@@ -1548,7 +1548,7 @@
         <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1560,10 +1560,10 @@
         <v>4.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
         <v>1.72</v>
@@ -1584,7 +1584,7 @@
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1647,7 +1647,7 @@
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>7.8</v>
@@ -1689,14 +1689,14 @@
         <v>7.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
         <v>7.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1757,13 +1757,13 @@
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S7" t="n">
         <v>2.78</v>
@@ -1775,7 +1775,7 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W7" t="n">
         <v>1.21</v>
@@ -1886,11 +1886,11 @@
         <v>10</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.6</v>
       </c>
-      <c r="G8" t="n">
-        <v>1.61</v>
-      </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
@@ -1957,7 +1957,7 @@
         <v>1.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="S8" t="n">
         <v>2</v>
@@ -1966,19 +1966,19 @@
         <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X8" t="n">
         <v>38</v>
       </c>
       <c r="Y8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z8" t="n">
         <v>55</v>
@@ -1999,7 +1999,7 @@
         <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG8" t="n">
         <v>10</v>
@@ -2041,7 +2041,7 @@
         <v>100</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AU8" t="n">
         <v>11.5</v>
@@ -2050,7 +2050,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2059,7 +2059,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA8" t="n">
         <v>42</v>
@@ -2074,17 +2074,17 @@
         <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG8" t="n">
         <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>110</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,70 +2300,70 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Goztepe</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
         <v>1.04</v>
       </c>
-      <c r="G10" t="n">
-        <v>970</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I10" t="n">
-        <v>970</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K10" t="n">
-        <v>950</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N10" t="n">
-        <v>1.06</v>
+        <v>5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="R10" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y10" t="n">
         <v>1000</v>
@@ -2372,25 +2372,25 @@
         <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
@@ -2402,84 +2402,84 @@
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.49</v>
+        <v>1.67</v>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
         <v>4.5</v>
       </c>
-      <c r="K11" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X11" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AS11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8.6</v>
       </c>
       <c r="AY11" t="n">
         <v>9</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.65</v>
+        <v>2.18</v>
       </c>
       <c r="G12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T12" t="n">
         <v>1.76</v>
       </c>
-      <c r="H12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S12" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.14</v>
-      </c>
       <c r="U12" t="n">
-        <v>1.69</v>
+        <v>2.16</v>
       </c>
       <c r="V12" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
-        <v>2.3</v>
+        <v>1.79</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>160</v>
+        <v>46</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI12" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>5.2</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.22</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.22</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.79</v>
+        <v>11</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.72</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>2.72</v>
       </c>
       <c r="I13" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="J13" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P13" t="n">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="T13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U13" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>11.5</v>
+        <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>1.15</v>
       </c>
       <c r="AS13" t="n">
-        <v>11.5</v>
+        <v>1.15</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>1.15</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>11.5</v>
+        <v>1.15</v>
       </c>
       <c r="AW13" t="n">
-        <v>10.5</v>
+        <v>1.15</v>
       </c>
       <c r="AX13" t="n">
-        <v>11.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.6</v>
+        <v>1.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>1.15</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>1.15</v>
       </c>
       <c r="BC13" t="n">
-        <v>20</v>
+        <v>1.15</v>
       </c>
       <c r="BD13" t="n">
-        <v>29</v>
+        <v>1.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.4</v>
+        <v>1.15</v>
       </c>
       <c r="BF13" t="n">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>1.15</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H14" t="n">
-        <v>2.12</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>110</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.29</v>
+        <v>1.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.43</v>
+        <v>2.34</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.35</v>
+        <v>1.6</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>1.31</v>
       </c>
       <c r="G15" t="n">
-        <v>2.74</v>
+        <v>1.32</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>11.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>6.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>2.92</v>
+        <v>8.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>1.64</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4</v>
+        <v>1.94</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>1.58</v>
+        <v>4.1</v>
       </c>
       <c r="X15" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>360</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="BD15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE15" t="n">
         <v>70</v>
       </c>
-      <c r="AB15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>25</v>
+        <v>3.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>8.6</v>
       </c>
       <c r="I16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>6.2</v>
@@ -3512,13 +3512,13 @@
         <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V16" t="n">
         <v>1.12</v>
@@ -3539,7 +3539,7 @@
         <v>270</v>
       </c>
       <c r="AB16" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC16" t="n">
         <v>15.5</v>
@@ -3584,13 +3584,13 @@
         <v>38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AR16" t="n">
         <v>75</v>
       </c>
       <c r="AS16" t="n">
-        <v>110</v>
+        <v>50</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -3602,7 +3602,7 @@
         <v>30</v>
       </c>
       <c r="AW16" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="AX16" t="n">
         <v>11.5</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA16" t="n">
         <v>60</v>
@@ -3629,14 +3629,14 @@
         <v>60</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BG16" t="n">
         <v>55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>2.7</v>
       </c>
       <c r="H17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I17" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.35</v>
@@ -3706,7 +3706,7 @@
         <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
         <v>1.66</v>
@@ -3715,19 +3715,19 @@
         <v>2.42</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W17" t="n">
         <v>1.58</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA17" t="n">
         <v>38</v>
@@ -3745,7 +3745,7 @@
         <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG17" t="n">
         <v>12</v>
@@ -3790,7 +3790,7 @@
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,184 +3847,184 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.31</v>
+        <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="H18" t="n">
-        <v>10</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="J18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="X18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
         <v>6.8</v>
       </c>
-      <c r="K18" t="n">
-        <v>7</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AC18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV18" t="n">
         <v>4.1</v>
       </c>
-      <c r="X18" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>360</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY18" t="n">
         <v>3.4</v>
       </c>
-      <c r="AO18" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>46</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>75</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>21</v>
+        <v>4.1</v>
       </c>
       <c r="BA18" t="n">
-        <v>75</v>
+        <v>4.5</v>
       </c>
       <c r="BB18" t="n">
-        <v>11</v>
+        <v>3.7</v>
       </c>
       <c r="BC18" t="n">
-        <v>11.5</v>
+        <v>3.95</v>
       </c>
       <c r="BD18" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>70</v>
+        <v>4.5</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>50</v>
+        <v>4.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4055,28 +4055,28 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="G19" t="n">
         <v>1.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I19" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
         <v>2.66</v>
@@ -4085,7 +4085,7 @@
         <v>1.49</v>
       </c>
       <c r="P19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q19" t="n">
         <v>2.34</v>
@@ -4097,13 +4097,13 @@
         <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W19" t="n">
         <v>2.24</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.34</v>
+        <v>1.66</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AU19" t="n">
         <v>4.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="AW19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.33</v>
       </c>
-      <c r="AX19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BF19" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="H20" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="M20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.11</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.12</v>
-      </c>
       <c r="W20" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="AC20" t="n">
         <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AG20" t="n">
         <v>13</v>
       </c>
       <c r="AH20" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AL20" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.74</v>
+        <v>4.4</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>3.7</v>
+        <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I21" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
         <v>1.12</v>
       </c>
       <c r="N21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q21" t="n">
         <v>2.38</v>
       </c>
-      <c r="O21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.64</v>
-      </c>
       <c r="R21" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD21" t="n">
         <v>5.2</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="BE21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>46</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>20</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BG21" t="n">
-        <v>7.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="G22" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>1.54</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.44</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>2.58</v>
+        <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB22" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>48</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF22" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AJ22" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AK22" t="n">
         <v>24</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AQ22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE22" t="n">
         <v>4.5</v>
       </c>
-      <c r="AR22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC22" t="n">
+      <c r="BF22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG22" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,49 +4822,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
         <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
@@ -4873,7 +4873,7 @@
         <v>1.01</v>
       </c>
       <c r="T23" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
         <v>1.01</v>
@@ -4882,126 +4882,126 @@
         <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>370</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,88 +5016,88 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W24" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
@@ -5133,69 +5133,69 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,184 +5205,184 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>1.56</v>
       </c>
       <c r="G25" t="n">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
-        <v>1.49</v>
+        <v>1.27</v>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>1.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z25" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB25" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AC25" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.1</v>
+        <v>8</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.97</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT25" t="n">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.08</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.98</v>
+        <v>70</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.99</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.91</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.94</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.04</v>
+        <v>8.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.77</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.76</v>
+        <v>7.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.78</v>
+        <v>8.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.77</v>
+        <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.69</v>
+        <v>8.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="G26" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="H26" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="O26" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X26" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="Z26" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="AA26" t="n">
-        <v>230</v>
+        <v>110</v>
       </c>
       <c r="AB26" t="n">
         <v>9</v>
       </c>
       <c r="AC26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="BC26" t="n">
         <v>19</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
         <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.96</v>
+        <v>2.38</v>
       </c>
       <c r="G27" t="n">
-        <v>2.14</v>
+        <v>2.54</v>
       </c>
       <c r="H27" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
         <v>2.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN27" t="n">
         <v>32</v>
       </c>
-      <c r="AA27" t="n">
-        <v>110</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF27" t="n">
+      <c r="AO27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX27" t="n">
         <v>13.5</v>
       </c>
-      <c r="AG27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AY27" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ27" t="n">
         <v>16.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.4</v>
+        <v>44</v>
       </c>
       <c r="BB27" t="n">
-        <v>21</v>
+        <v>5.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="BE27" t="n">
-        <v>8</v>
+        <v>5.9</v>
       </c>
       <c r="BF27" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G28" t="n">
         <v>2.56</v>
       </c>
       <c r="H28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J28" t="n">
         <v>3.2</v>
-      </c>
-      <c r="I28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.25</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
       </c>
       <c r="N28" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P28" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U28" t="n">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y28" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y28" t="n">
-        <v>13</v>
-      </c>
       <c r="Z28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA28" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
         <v>10.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF28" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH28" t="n">
         <v>21</v>
       </c>
       <c r="AI28" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
         <v>36</v>
       </c>
       <c r="AK28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN28" t="n">
         <v>30</v>
       </c>
-      <c r="AL28" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>32</v>
-      </c>
       <c r="AO28" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AP28" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.6</v>
+        <v>55</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU28" t="n">
         <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ28" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.36</v>
+        <v>1.69</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="H29" t="n">
-        <v>3.35</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="O29" t="n">
         <v>1.48</v>
       </c>
-      <c r="M29" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.41</v>
-      </c>
       <c r="P29" t="n">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T29" t="n">
-        <v>1.87</v>
+        <v>2.26</v>
       </c>
       <c r="U29" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="V29" t="n">
-        <v>1.38</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK29" t="n">
         <v>25</v>
       </c>
-      <c r="AA29" t="n">
-        <v>75</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AG29" t="n">
+      <c r="AL29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF29" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>20</v>
-      </c>
       <c r="BG29" t="n">
-        <v>5.1</v>
+        <v>1.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.66</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.44</v>
+        <v>1.46</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.4</v>
+        <v>1.46</v>
       </c>
       <c r="T30" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O31" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,55 +6568,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,60 +6757,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>2.82</v>
       </c>
       <c r="G33" t="n">
-        <v>2.48</v>
+        <v>3.15</v>
       </c>
       <c r="H33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.65</v>
       </c>
-      <c r="I33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="O33" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="P33" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.59</v>
+        <v>1.87</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S33" t="n">
-        <v>2.36</v>
+        <v>3.6</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,129 +6819,129 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="W33" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,184 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.42</v>
+        <v>3.2</v>
       </c>
       <c r="G34" t="n">
-        <v>970</v>
+        <v>3.5</v>
       </c>
       <c r="H34" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="I34" t="n">
-        <v>3.4</v>
+        <v>2.58</v>
       </c>
       <c r="J34" t="n">
-        <v>2.18</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>1.82</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R34" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V34" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="W34" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="G35" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="H35" t="n">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="I35" t="n">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M35" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="U35" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="V35" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="W35" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="X35" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS35" t="n">
         <v>9</v>
       </c>
-      <c r="AD35" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>30</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT35" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV35" t="n">
         <v>10</v>
       </c>
       <c r="AW35" t="n">
-        <v>23</v>
+        <v>8.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ35" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA35" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BC35" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.5</v>
+        <v>30</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="BG35" t="n">
-        <v>18</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="G36" t="n">
-        <v>2.46</v>
+        <v>1.94</v>
       </c>
       <c r="H36" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="I36" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="M36" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="P36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T36" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.69</v>
-      </c>
       <c r="U36" t="n">
-        <v>2.24</v>
+        <v>1.92</v>
       </c>
       <c r="V36" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="W36" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF36" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
       <c r="AG36" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP36" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ36" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR36" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AS36" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AT36" t="n">
-        <v>9.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU36" t="n">
         <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW36" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX36" t="n">
         <v>9.4</v>
       </c>
-      <c r="AX36" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AY36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ36" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BC36" t="n">
-        <v>8.199999999999999</v>
+        <v>19</v>
       </c>
       <c r="BD36" t="n">
-        <v>9.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="BF36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
@@ -7533,96 +7533,96 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.88</v>
+        <v>2.24</v>
       </c>
       <c r="G37" t="n">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="H37" t="n">
-        <v>5.2</v>
+        <v>3.25</v>
       </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="K37" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>1.11</v>
       </c>
       <c r="P37" t="n">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="S37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T37" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>1.88</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="X37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
         <v>970</v>
       </c>
       <c r="Z37" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AA37" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="AC37" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AE37" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
         <v>20</v>
@@ -7631,93 +7631,93 @@
         <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>500</v>
+        <v>29</v>
       </c>
       <c r="AI37" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AK37" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="AL37" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>7</v>
+        <v>2.02</v>
       </c>
       <c r="AQ37" t="n">
-        <v>11</v>
+        <v>1.81</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AT37" t="n">
-        <v>6.2</v>
+        <v>1.72</v>
       </c>
       <c r="AU37" t="n">
-        <v>5.1</v>
+        <v>1.71</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AX37" t="n">
-        <v>5.6</v>
+        <v>1.85</v>
       </c>
       <c r="AY37" t="n">
-        <v>6.2</v>
+        <v>1.82</v>
       </c>
       <c r="AZ37" t="n">
-        <v>11.5</v>
+        <v>1.9</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="BF37" t="n">
-        <v>9.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="BG37" t="n">
-        <v>34</v>
+        <v>2.02</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,378 +7727,184 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>23:07:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.24</v>
+        <v>1.42</v>
       </c>
       <c r="G38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S38" t="n">
         <v>2.56</v>
       </c>
-      <c r="H38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V38" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="W38" t="n">
-        <v>1.64</v>
+        <v>2.96</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y38" t="n">
-        <v>970</v>
+        <v>32</v>
       </c>
       <c r="Z38" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AA38" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AB38" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG38" t="n">
         <v>11</v>
       </c>
-      <c r="AC38" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD38" t="n">
+      <c r="AH38" t="n">
         <v>24</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>30</v>
-      </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ38" t="n">
-        <v>48</v>
+        <v>13.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>46</v>
+        <v>15.5</v>
       </c>
       <c r="AL38" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.02</v>
+        <v>19</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.8</v>
+        <v>22</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.93</v>
+        <v>8</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.02</v>
+        <v>8.6</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.71</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.87</v>
+        <v>22</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.82</v>
+        <v>9</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="BA38" t="n">
-        <v>2.02</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.95</v>
+        <v>12.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>2.02</v>
+        <v>7</v>
       </c>
       <c r="BE38" t="n">
-        <v>2.02</v>
+        <v>8.4</v>
       </c>
       <c r="BF38" t="n">
-        <v>2.02</v>
+        <v>5.2</v>
       </c>
       <c r="BG38" t="n">
-        <v>2.02</v>
+        <v>8.6</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 03:19:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>23:07:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Guadalajara</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Leon</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X39" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>8</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-03-17 03:19:10</t>
+          <t>2026-03-17 05:29:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
@@ -775,152 +775,152 @@
         <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="O2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>1.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -993,16 +993,16 @@
         <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
         <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1023,7 +1023,7 @@
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>70</v>
@@ -1032,13 +1032,13 @@
         <v>13.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI3" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ3" t="n">
         <v>28</v>
@@ -1053,10 +1053,10 @@
         <v>170</v>
       </c>
       <c r="AN3" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP3" t="n">
         <v>9.199999999999999</v>
@@ -1065,10 +1065,10 @@
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC3" t="n">
         <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF3" t="n">
         <v>15.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1181,7 @@
         <v>1.87</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
         <v>3.25</v>
@@ -1223,7 +1223,7 @@
         <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1381,10 +1381,10 @@
         <v>1.32</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H6" t="n">
         <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
         <v>4.8</v>
@@ -1584,7 +1584,7 @@
         <v>1.15</v>
       </c>
       <c r="W6" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.67</v>
       </c>
       <c r="I7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="J7" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
@@ -1760,7 +1760,7 @@
         <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
@@ -1775,10 +1775,10 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
         <v>20</v>
@@ -1874,23 +1874,23 @@
         <v>10.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE7" t="n">
         <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>5.7</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -1963,7 +1963,7 @@
         <v>2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="U8" t="n">
         <v>2.82</v>
@@ -1987,10 +1987,10 @@
         <v>130</v>
       </c>
       <c r="AB8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>22</v>
@@ -2062,7 +2062,7 @@
         <v>15.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB8" t="n">
         <v>16.5</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.68</v>
+        <v>1.39</v>
       </c>
       <c r="G9" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J9" t="n">
         <v>1.1</v>
@@ -2139,13 +2139,13 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
         <v>1.31</v>
@@ -2154,19 +2154,19 @@
         <v>1.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H10" t="n">
         <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K10" t="n">
         <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
@@ -2339,7 +2339,7 @@
         <v>1.21</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
         <v>1.64</v>
@@ -2351,7 +2351,7 @@
         <v>2.58</v>
       </c>
       <c r="T10" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.08</v>
@@ -2360,7 +2360,7 @@
         <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X10" t="n">
         <v>26</v>
@@ -2432,7 +2432,7 @@
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV10" t="n">
         <v>6.8</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G11" t="n">
         <v>1.81</v>
@@ -2518,16 +2518,16 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
       </c>
       <c r="N11" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O11" t="n">
         <v>1.44</v>
@@ -2545,7 +2545,7 @@
         <v>4.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
         <v>1.71</v>
@@ -2554,7 +2554,7 @@
         <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G12" t="n">
         <v>2.26</v>
@@ -2706,43 +2706,43 @@
         <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
         <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V12" t="n">
         <v>1.35</v>
@@ -2754,31 +2754,31 @@
         <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z12" t="n">
         <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
         <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12" t="n">
         <v>970</v>
@@ -2802,10 +2802,10 @@
         <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
         <v>12</v>
@@ -2814,53 +2814,53 @@
         <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
         <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AX12" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ12" t="n">
         <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BF12" t="n">
         <v>13</v>
       </c>
       <c r="BG12" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="G13" t="n">
         <v>3.7</v>
       </c>
       <c r="H13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J13" t="n">
         <v>2.72</v>
       </c>
-      <c r="I13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.7</v>
-      </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2924,13 +2924,13 @@
         <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T13" t="n">
         <v>1.79</v>
@@ -2939,7 +2939,7 @@
         <v>1.87</v>
       </c>
       <c r="V13" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W13" t="n">
         <v>1.39</v>
@@ -3014,7 +3014,7 @@
         <v>1.15</v>
       </c>
       <c r="AU13" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
         <v>1.15</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G14" t="n">
         <v>2.68</v>
@@ -3097,13 +3097,13 @@
         <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K14" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
@@ -3127,7 +3127,7 @@
         <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
         <v>1.94</v>
@@ -3136,7 +3136,7 @@
         <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
         <v>10</v>
@@ -3163,7 +3163,7 @@
         <v>50</v>
       </c>
       <c r="AF14" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
         <v>13</v>
@@ -3202,7 +3202,7 @@
         <v>19</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT14" t="n">
         <v>7.6</v>
@@ -3214,7 +3214,7 @@
         <v>12.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX14" t="n">
         <v>13.5</v>
@@ -3223,22 +3223,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD14" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
         <v>25</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J15" t="n">
         <v>6.8</v>
@@ -3318,7 +3318,7 @@
         <v>2.04</v>
       </c>
       <c r="S15" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="T15" t="n">
         <v>1.72</v>
@@ -3327,7 +3327,7 @@
         <v>2.32</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
         <v>4.1</v>
@@ -3339,13 +3339,13 @@
         <v>55</v>
       </c>
       <c r="Z15" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA15" t="n">
         <v>360</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC15" t="n">
         <v>16.5</v>
@@ -3363,7 +3363,7 @@
         <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
         <v>90</v>
@@ -3378,7 +3378,7 @@
         <v>24</v>
       </c>
       <c r="AM15" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN15" t="n">
         <v>3.4</v>
@@ -3393,10 +3393,10 @@
         <v>48</v>
       </c>
       <c r="AR15" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AS15" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AT15" t="n">
         <v>14.5</v>
@@ -3405,10 +3405,10 @@
         <v>15.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AW15" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
         <v>10.5</v>
@@ -3438,11 +3438,11 @@
         <v>3.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>1.38</v>
       </c>
       <c r="H16" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I16" t="n">
         <v>8.800000000000001</v>
@@ -3518,7 +3518,7 @@
         <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
         <v>1.12</v>
@@ -3536,7 +3536,7 @@
         <v>90</v>
       </c>
       <c r="AA16" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="AB16" t="n">
         <v>16.5</v>
@@ -3548,10 +3548,10 @@
         <v>32</v>
       </c>
       <c r="AE16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
@@ -3572,7 +3572,7 @@
         <v>23</v>
       </c>
       <c r="AM16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AN16" t="n">
         <v>3.65</v>
@@ -3584,13 +3584,13 @@
         <v>38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AR16" t="n">
         <v>75</v>
       </c>
       <c r="AS16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="AT16" t="n">
         <v>15</v>
@@ -3599,7 +3599,7 @@
         <v>14</v>
       </c>
       <c r="AV16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW16" t="n">
         <v>75</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
         <v>60</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>2.64</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J17" t="n">
         <v>3.95</v>
@@ -3703,40 +3703,40 @@
         <v>1.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="T17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U17" t="n">
         <v>2.42</v>
       </c>
       <c r="V17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W17" t="n">
         <v>1.59</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y17" t="n">
         <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
         <v>38</v>
       </c>
       <c r="AB17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
         <v>12</v>
@@ -3772,7 +3772,7 @@
         <v>19</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="n">
         <v>17.5</v>
@@ -3790,7 +3790,7 @@
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV17" t="n">
         <v>11</v>
@@ -3802,10 +3802,10 @@
         <v>18</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA17" t="n">
         <v>30</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -3861,13 +3861,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I18" t="n">
         <v>8.4</v>
@@ -3888,13 +3888,13 @@
         <v>2.56</v>
       </c>
       <c r="O18" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P18" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R18" t="n">
         <v>1.2</v>
@@ -3912,7 +3912,7 @@
         <v>1.13</v>
       </c>
       <c r="W18" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X18" t="n">
         <v>11.5</v>
@@ -3930,7 +3930,7 @@
         <v>6.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
         <v>40</v>
@@ -3951,7 +3951,7 @@
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AK18" t="n">
         <v>28</v>
@@ -3969,62 +3969,62 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AV18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>1.76</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="H19" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
         <v>6.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
@@ -4079,7 +4079,7 @@
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O19" t="n">
         <v>1.49</v>
@@ -4094,7 +4094,7 @@
         <v>1.21</v>
       </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T19" t="n">
         <v>2.22</v>
@@ -4103,10 +4103,10 @@
         <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W19" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4121,7 +4121,7 @@
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AC19" t="n">
         <v>1000</v>
@@ -4163,62 +4163,62 @@
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.6</v>
+        <v>3.6</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AT19" t="n">
         <v>3.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="AW19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BD19" t="n">
         <v>1.65</v>
       </c>
-      <c r="AX19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -4249,52 +4249,52 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G20" t="n">
         <v>1.68</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="K20" t="n">
         <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P20" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="R20" t="n">
         <v>1.16</v>
       </c>
       <c r="S20" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="T20" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
@@ -4303,10 +4303,10 @@
         <v>2.46</v>
       </c>
       <c r="X20" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,34 +4315,34 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AK20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
         <v>14.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU20" t="n">
         <v>7.8</v>
       </c>
       <c r="AV20" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA20" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>7.4</v>
       </c>
       <c r="BB20" t="n">
         <v>13.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>5.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.4</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="G21" t="n">
         <v>1.63</v>
       </c>
       <c r="H21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I21" t="n">
         <v>11</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M21" t="n">
         <v>1.12</v>
@@ -4470,10 +4470,10 @@
         <v>2.78</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="P21" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
         <v>2.38</v>
@@ -4482,19 +4482,19 @@
         <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T21" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="U21" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X21" t="n">
         <v>11.5</v>
@@ -4509,19 +4509,19 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE21" t="n">
         <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AG21" t="n">
         <v>970</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB21" t="n">
         <v>4.6</v>
       </c>
-      <c r="AR21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC21" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF21" t="n">
         <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G22" t="n">
         <v>2.22</v>
@@ -4652,22 +4652,22 @@
         <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L22" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="Q22" t="n">
         <v>1.8</v>
@@ -4676,10 +4676,10 @@
         <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>3.35</v>
+        <v>1.02</v>
       </c>
       <c r="T22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
@@ -4688,7 +4688,7 @@
         <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
         <v>14</v>
@@ -4700,7 +4700,7 @@
         <v>32</v>
       </c>
       <c r="AA22" t="n">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AB22" t="n">
         <v>9.4</v>
@@ -4718,13 +4718,13 @@
         <v>13.5</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="AI22" t="n">
-        <v>360</v>
+        <v>110</v>
       </c>
       <c r="AJ22" t="n">
         <v>27</v>
@@ -4736,71 +4736,71 @@
         <v>190</v>
       </c>
       <c r="AM22" t="n">
-        <v>880</v>
+        <v>140</v>
       </c>
       <c r="AN22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO22" t="n">
         <v>550</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AR22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS22" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
         <v>7.8</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX22" t="n">
-        <v>5.5</v>
+        <v>9.4</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="BB22" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="BC22" t="n">
         <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BF22" t="n">
         <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -4864,19 +4864,19 @@
         <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.1</v>
+        <v>1.38</v>
       </c>
       <c r="R23" t="n">
         <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -5064,7 +5064,7 @@
         <v>1.2</v>
       </c>
       <c r="S24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
         <v>2.1</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G25" t="n">
         <v>1.63</v>
@@ -5228,7 +5228,7 @@
         <v>6.2</v>
       </c>
       <c r="I25" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J25" t="n">
         <v>4.2</v>
@@ -5252,7 +5252,7 @@
         <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R25" t="n">
         <v>1.41</v>
@@ -5273,7 +5273,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Y25" t="n">
         <v>24</v>
@@ -5333,13 +5333,13 @@
         <v>19</v>
       </c>
       <c r="AR25" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU25" t="n">
         <v>8.6</v>
@@ -5348,7 +5348,7 @@
         <v>21</v>
       </c>
       <c r="AW25" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="AX25" t="n">
         <v>8.199999999999999</v>
@@ -5360,7 +5360,7 @@
         <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
@@ -5369,20 +5369,20 @@
         <v>14.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BF25" t="n">
         <v>6.4</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -5413,61 +5413,61 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G26" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H26" t="n">
         <v>3.95</v>
       </c>
       <c r="I26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
         <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O26" t="n">
         <v>1.34</v>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
         <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
         <v>2.04</v>
       </c>
       <c r="V26" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="X26" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y26" t="n">
         <v>15</v>
@@ -5485,10 +5485,10 @@
         <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF26" t="n">
         <v>13.5</v>
@@ -5503,22 +5503,22 @@
         <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM26" t="n">
         <v>120</v>
       </c>
       <c r="AN26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO26" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
         <v>12</v>
@@ -5530,7 +5530,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="AT26" t="n">
         <v>7.8</v>
@@ -5542,7 +5542,7 @@
         <v>14.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.6</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="n">
         <v>10.5</v>
@@ -5554,7 +5554,7 @@
         <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB26" t="n">
         <v>21</v>
@@ -5563,20 +5563,20 @@
         <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>24</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BF26" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.6</v>
+        <v>29</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -5628,31 +5628,31 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
         <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -5670,7 +5670,7 @@
         <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
         <v>10.5</v>
@@ -5694,7 +5694,7 @@
         <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
         <v>36</v>
@@ -5706,7 +5706,7 @@
         <v>50</v>
       </c>
       <c r="AM27" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
         <v>32</v>
@@ -5727,7 +5727,7 @@
         <v>5.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX27" t="n">
         <v>13.5</v>
@@ -5745,32 +5745,32 @@
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>44</v>
+        <v>5.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>38</v>
+        <v>5.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF27" t="n">
         <v>19.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="G28" t="n">
         <v>2.56</v>
@@ -5819,7 +5819,7 @@
         <v>3.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M28" t="n">
         <v>1.09</v>
@@ -5852,13 +5852,13 @@
         <v>1.38</v>
       </c>
       <c r="W28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X28" t="n">
         <v>11.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z28" t="n">
         <v>25</v>
@@ -5873,7 +5873,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>60</v>
@@ -5906,7 +5906,7 @@
         <v>30</v>
       </c>
       <c r="AO28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
         <v>9.6</v>
@@ -5918,7 +5918,7 @@
         <v>19.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>55</v>
+        <v>6.2</v>
       </c>
       <c r="AT28" t="n">
         <v>7.6</v>
@@ -5930,7 +5930,7 @@
         <v>12.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX28" t="n">
         <v>12.5</v>
@@ -5942,36 +5942,36 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>46</v>
+        <v>6.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF28" t="n">
         <v>20</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.69</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
-        <v>3.75</v>
+        <v>5.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="P29" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>1.94</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="X29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
         <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
         <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR29" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.42</v>
+        <v>1.03</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.44</v>
+        <v>1.03</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.79</v>
+        <v>1.03</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF29" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.46</v>
+        <v>2.4</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>1.46</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.02</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,55 +6568,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O32" t="n">
         <v>1.32</v>
       </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.22</v>
-      </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,60 +6757,60 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.82</v>
+        <v>1.89</v>
       </c>
       <c r="G33" t="n">
-        <v>3.15</v>
+        <v>2.54</v>
       </c>
       <c r="H33" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="I33" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M33" t="n">
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="P33" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.87</v>
+        <v>1.59</v>
       </c>
       <c r="R33" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="S33" t="n">
-        <v>3.6</v>
+        <v>2.36</v>
       </c>
       <c r="T33" t="n">
         <v>1.01</v>
@@ -6819,129 +6819,129 @@
         <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="W33" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,184 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="G34" t="n">
         <v>3.2</v>
       </c>
-      <c r="G34" t="n">
-        <v>3.5</v>
-      </c>
       <c r="H34" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="I34" t="n">
-        <v>2.58</v>
+        <v>2.82</v>
       </c>
       <c r="J34" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T34" t="n">
         <v>1.78</v>
       </c>
       <c r="U34" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V34" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="W34" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="X34" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AA34" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AB34" t="n">
         <v>14</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD34" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AE34" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AF34" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG34" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH34" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AI34" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ34" t="n">
         <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL34" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM34" t="n">
         <v>120</v>
       </c>
       <c r="AN34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP34" t="n">
         <v>11</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR34" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AS34" t="n">
-        <v>30</v>
+        <v>3.9</v>
       </c>
       <c r="AT34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV34" t="n">
         <v>10.5</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>10</v>
       </c>
       <c r="AW34" t="n">
         <v>24</v>
       </c>
       <c r="AX34" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY34" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA34" t="n">
-        <v>36</v>
+        <v>3.9</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.4</v>
+        <v>3.95</v>
       </c>
       <c r="BC34" t="n">
-        <v>32</v>
+        <v>3.85</v>
       </c>
       <c r="BD34" t="n">
-        <v>38</v>
+        <v>3.95</v>
       </c>
       <c r="BE34" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="BF34" t="n">
-        <v>30</v>
+        <v>3.8</v>
       </c>
       <c r="BG34" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.26</v>
+        <v>3.15</v>
       </c>
       <c r="G35" t="n">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="H35" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="I35" t="n">
-        <v>3.65</v>
+        <v>2.58</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K35" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L35" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M35" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R35" t="n">
         <v>1.3</v>
       </c>
-      <c r="P35" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="T35" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="U35" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V35" t="n">
-        <v>1.37</v>
+        <v>1.63</v>
       </c>
       <c r="W35" t="n">
-        <v>1.69</v>
+        <v>1.41</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB35" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AC35" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG35" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN35" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP35" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ35" t="n">
-        <v>12.5</v>
+        <v>8.4</v>
       </c>
       <c r="AR35" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AS35" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="AT35" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU35" t="n">
         <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>8.4</v>
+        <v>24</v>
       </c>
       <c r="AX35" t="n">
-        <v>6.4</v>
+        <v>19</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>6.4</v>
+        <v>16</v>
       </c>
       <c r="BA35" t="n">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="BB35" t="n">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="BC35" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BD35" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF35" t="n">
         <v>30</v>
       </c>
-      <c r="BE35" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>13</v>
-      </c>
       <c r="BG35" t="n">
-        <v>8.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,179 +7344,179 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.9</v>
+        <v>2.26</v>
       </c>
       <c r="G36" t="n">
-        <v>1.94</v>
+        <v>2.48</v>
       </c>
       <c r="H36" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="I36" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="J36" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L36" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P36" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="R36" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.98</v>
+        <v>1.7</v>
       </c>
       <c r="U36" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="V36" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="W36" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ36" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y36" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>700</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>450</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>10</v>
-      </c>
       <c r="AR36" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AT36" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="AU36" t="n">
         <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="AX36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE36" t="n">
         <v>9.4</v>
       </c>
-      <c r="AY36" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA36" t="n">
+      <c r="BF36" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG36" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB36" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
@@ -7533,378 +7533,572 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.24</v>
+        <v>1.88</v>
       </c>
       <c r="G37" t="n">
-        <v>2.46</v>
+        <v>1.94</v>
       </c>
       <c r="H37" t="n">
-        <v>3.25</v>
+        <v>5.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="J37" t="n">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M37" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>1.61</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="P37" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="R37" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="W37" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Z37" t="n">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="AA37" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG37" t="n">
         <v>11</v>
       </c>
-      <c r="AC37" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD37" t="n">
+      <c r="AH37" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK37" t="n">
         <v>24</v>
       </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>46</v>
-      </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.02</v>
+        <v>10</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.81</v>
+        <v>13</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.93</v>
+        <v>17</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.02</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.72</v>
+        <v>6.6</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.71</v>
+        <v>7</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.88</v>
+        <v>17.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.85</v>
+        <v>9.4</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.82</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.9</v>
+        <v>14</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.95</v>
+        <v>18.5</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.95</v>
+        <v>11.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.02</v>
+        <v>8</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.04</v>
+        <v>28</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.02</v>
+        <v>14</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.02</v>
+        <v>9</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 05:29:50</t>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-17 07:40:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>23:07:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Leon</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F39" t="n">
         <v>1.42</v>
       </c>
-      <c r="G38" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="H38" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I38" t="n">
+      <c r="G39" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8</v>
+      </c>
+      <c r="I39" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J39" t="n">
         <v>4.8</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K39" t="n">
         <v>5.5</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L39" t="n">
         <v>1.27</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M39" t="n">
         <v>1.04</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N39" t="n">
         <v>4.9</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O39" t="n">
         <v>1.21</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P39" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>1.63</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>1.52</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>2.56</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T39" t="n">
         <v>1.86</v>
       </c>
-      <c r="U38" t="n">
+      <c r="U39" t="n">
         <v>1.97</v>
       </c>
-      <c r="V38" t="n">
+      <c r="V39" t="n">
         <v>1.12</v>
       </c>
-      <c r="W38" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="W39" t="n">
+        <v>3</v>
+      </c>
+      <c r="X39" t="n">
         <v>26</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y39" t="n">
         <v>32</v>
       </c>
-      <c r="Z38" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA38" t="n">
+      <c r="Z39" t="n">
+        <v>75</v>
+      </c>
+      <c r="AA39" t="n">
         <v>280</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AB39" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AC39" t="n">
         <v>12</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AD39" t="n">
         <v>32</v>
       </c>
-      <c r="AE38" t="n">
+      <c r="AE39" t="n">
         <v>130</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AF39" t="n">
         <v>10</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AG39" t="n">
         <v>11</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AH39" t="n">
         <v>24</v>
       </c>
-      <c r="AI38" t="n">
+      <c r="AI39" t="n">
         <v>110</v>
       </c>
-      <c r="AJ38" t="n">
+      <c r="AJ39" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK38" t="n">
+      <c r="AK39" t="n">
         <v>15.5</v>
       </c>
-      <c r="AL38" t="n">
+      <c r="AL39" t="n">
         <v>34</v>
       </c>
-      <c r="AM38" t="n">
+      <c r="AM39" t="n">
         <v>130</v>
       </c>
-      <c r="AN38" t="n">
+      <c r="AN39" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
         <v>19</v>
       </c>
-      <c r="AQ38" t="n">
+      <c r="AQ39" t="n">
         <v>22</v>
       </c>
-      <c r="AR38" t="n">
+      <c r="AR39" t="n">
         <v>8</v>
       </c>
-      <c r="AS38" t="n">
+      <c r="AS39" t="n">
         <v>8.6</v>
       </c>
-      <c r="AT38" t="n">
+      <c r="AT39" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU38" t="n">
+      <c r="AU39" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AV38" t="n">
+      <c r="AV39" t="n">
         <v>22</v>
       </c>
-      <c r="AW38" t="n">
+      <c r="AW39" t="n">
         <v>8.4</v>
       </c>
-      <c r="AX38" t="n">
+      <c r="AX39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY38" t="n">
+      <c r="AY39" t="n">
         <v>9</v>
       </c>
-      <c r="AZ38" t="n">
+      <c r="AZ39" t="n">
         <v>19</v>
       </c>
-      <c r="BA38" t="n">
+      <c r="BA39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB38" t="n">
+      <c r="BB39" t="n">
         <v>11</v>
       </c>
-      <c r="BC38" t="n">
+      <c r="BC39" t="n">
         <v>12.5</v>
       </c>
-      <c r="BD38" t="n">
+      <c r="BD39" t="n">
         <v>7</v>
       </c>
-      <c r="BE38" t="n">
+      <c r="BE39" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF38" t="n">
+      <c r="BF39" t="n">
         <v>5.2</v>
       </c>
-      <c r="BG38" t="n">
+      <c r="BG39" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-03-17 05:29:50</t>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-17 07:40:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,13 +760,13 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
         <v>2.92</v>
@@ -799,19 +799,19 @@
         <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
         <v>11.5</v>
@@ -832,7 +832,7 @@
         <v>16.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF2" t="n">
         <v>19</v>
@@ -844,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>50</v>
@@ -862,65 +862,65 @@
         <v>46</v>
       </c>
       <c r="AO2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.8</v>
-      </c>
       <c r="AR2" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE2" t="n">
         <v>5.1</v>
       </c>
-      <c r="BC2" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
         <v>4.5</v>
@@ -966,7 +966,7 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -975,7 +975,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
@@ -987,7 +987,7 @@
         <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
         <v>4.3</v>
@@ -1002,7 +1002,7 @@
         <v>1.27</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
@@ -1023,13 +1023,13 @@
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>70</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
@@ -1056,19 +1056,19 @@
         <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>10.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>15</v>
       </c>
       <c r="AW3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC3" t="n">
         <v>22</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG3" t="n">
         <v>7.4</v>
       </c>
-      <c r="BF3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>7</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>4.7</v>
       </c>
       <c r="K4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
         <v>1.39</v>
@@ -1169,16 +1169,16 @@
         <v>1.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>1.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
@@ -1223,7 +1223,7 @@
         <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
@@ -1268,7 +1268,7 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>9.6</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.32</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>1.37</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
         <v>2.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>20</v>
@@ -1799,7 +1799,7 @@
         <v>10.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE7" t="n">
         <v>970</v>
@@ -1829,10 +1829,10 @@
         <v>110</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AP7" t="n">
         <v>17</v>
@@ -1859,7 +1859,7 @@
         <v>14.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY7" t="n">
         <v>18</v>
@@ -1868,29 +1868,29 @@
         <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF7" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BG7" t="n">
         <v>7.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I8" t="n">
         <v>5.6</v>
       </c>
-      <c r="I8" t="n">
-        <v>5.7</v>
-      </c>
       <c r="J8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
         <v>5.2</v>
@@ -1954,25 +1954,25 @@
         <v>3.35</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
         <v>1.98</v>
       </c>
-      <c r="S8" t="n">
-        <v>2</v>
-      </c>
       <c r="T8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="U8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X8" t="n">
         <v>38</v>
@@ -1990,7 +1990,7 @@
         <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
         <v>22</v>
@@ -2005,7 +2005,7 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI8" t="n">
         <v>46</v>
@@ -2014,16 +2014,16 @@
         <v>17.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL8" t="n">
         <v>21</v>
       </c>
       <c r="AM8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO8" t="n">
         <v>34</v>
@@ -2035,7 +2035,7 @@
         <v>32</v>
       </c>
       <c r="AR8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AS8" t="n">
         <v>100</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,70 +2106,70 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>1.54</v>
       </c>
       <c r="H9" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.04</v>
       </c>
-      <c r="I9" t="n">
-        <v>870</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="O9" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>2.58</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.53</v>
+        <v>1.14</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3</v>
+        <v>2.84</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
         <v>1000</v>
@@ -2178,25 +2178,25 @@
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2208,84 +2208,84 @@
         <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL9" t="n">
         <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="H10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I10" t="n">
         <v>7</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB10" t="n">
         <v>7.8</v>
       </c>
-      <c r="J10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N10" t="n">
-        <v>5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="X10" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>11</v>
-      </c>
       <c r="AC10" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD10" t="n">
         <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
         <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
         <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV10" t="n">
         <v>6.2</v>
       </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AW10" t="n">
         <v>7.8</v>
       </c>
-      <c r="AS10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT10" t="n">
+      <c r="AX10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AY10" t="n">
         <v>9</v>
       </c>
-      <c r="AU10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AW10" t="n">
+      <c r="AZ10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE10" t="n">
         <v>8</v>
       </c>
-      <c r="AX10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF10" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>2.68</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="I11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="X11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU11" t="n">
         <v>7</v>
       </c>
-      <c r="J11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV11" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.1</v>
+        <v>15.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.2</v>
+        <v>34</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="G12" t="n">
-        <v>2.26</v>
+        <v>3.7</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W12" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="X12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>1.15</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>13.5</v>
+        <v>1.15</v>
       </c>
       <c r="AW12" t="n">
-        <v>28</v>
+        <v>1.15</v>
       </c>
       <c r="AX12" t="n">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>16</v>
+        <v>1.15</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>1.15</v>
       </c>
       <c r="BB12" t="n">
-        <v>25</v>
+        <v>1.15</v>
       </c>
       <c r="BC12" t="n">
-        <v>21</v>
+        <v>1.15</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>1.15</v>
       </c>
       <c r="BE12" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="BF12" t="n">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="BG12" t="n">
-        <v>34</v>
+        <v>1.15</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -2882,34 +2882,34 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7</v>
+        <v>2.68</v>
       </c>
       <c r="H13" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
         <v>3.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M13" t="n">
         <v>1.11</v>
@@ -2918,150 +2918,150 @@
         <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S13" t="n">
-        <v>1.05</v>
+        <v>4.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.59</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.15</v>
+        <v>9.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.15</v>
+        <v>19</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.15</v>
+        <v>7.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.15</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.15</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.15</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.15</v>
+        <v>8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.15</v>
+        <v>25</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.15</v>
+        <v>42</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.52</v>
+        <v>1.37</v>
       </c>
       <c r="G14" t="n">
-        <v>2.68</v>
+        <v>1.38</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>9</v>
       </c>
       <c r="I14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="X14" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN14" t="n">
         <v>3.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N14" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AO14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>80</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY14" t="n">
         <v>10</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AZ14" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC14" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL14" t="n">
+      <c r="BD14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BG14" t="n">
         <v>55</v>
       </c>
-      <c r="AM14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>42</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.31</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>1.32</v>
+        <v>2.68</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>2.64</v>
       </c>
       <c r="I15" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV15" t="n">
         <v>11</v>
       </c>
-      <c r="J15" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>360</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AW15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AG15" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>95</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV15" t="n">
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB15" t="n">
         <v>34</v>
       </c>
-      <c r="AW15" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>11</v>
-      </c>
       <c r="BC15" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BD15" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BE15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.3</v>
+        <v>17.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="G16" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="H16" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="I16" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="J16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L16" t="n">
         <v>1.21</v>
@@ -3497,153 +3497,153 @@
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.12</v>
       </c>
       <c r="P16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R16" t="n">
         <v>2.04</v>
       </c>
       <c r="S16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="X16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z16" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="AA16" t="n">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="AB16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AC16" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AD16" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE16" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AF16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG16" t="n">
         <v>11</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI16" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="AJ16" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK16" t="n">
         <v>12.5</v>
       </c>
       <c r="AL16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AO16" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="AP16" t="n">
         <v>38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AR16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA16" t="n">
         <v>75</v>
       </c>
-      <c r="AS16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>29</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>60</v>
-      </c>
       <c r="BB16" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BC16" t="n">
         <v>11.5</v>
       </c>
       <c r="BD16" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BE16" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BG16" t="n">
         <v>60</v>
       </c>
-      <c r="BF16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>55</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="X17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT17" t="n">
         <v>2.7</v>
       </c>
-      <c r="H17" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="X17" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>13</v>
-      </c>
       <c r="AU17" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AW17" t="n">
-        <v>23</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
-        <v>18</v>
+        <v>3.05</v>
       </c>
       <c r="AY17" t="n">
-        <v>11.5</v>
+        <v>3.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>30</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>34</v>
+        <v>3.65</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>3.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>4.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>17</v>
+        <v>3.65</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.6</v>
       </c>
-      <c r="G18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="Q18" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S18" t="n">
-        <v>1.02</v>
+        <v>4.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="V18" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>2.52</v>
+        <v>2.2</v>
       </c>
       <c r="X18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>1.33</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.4</v>
+        <v>1.32</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.05</v>
+        <v>4.7</v>
       </c>
       <c r="AY18" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AZ18" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.4</v>
+        <v>1.32</v>
       </c>
       <c r="BB18" t="n">
-        <v>3.65</v>
+        <v>2.86</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.85</v>
+        <v>2.18</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>1.31</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>1.33</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.65</v>
+        <v>1.41</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>1.33</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="G19" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR19" t="n">
         <v>6.4</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K19" t="n">
+      <c r="AS19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AV19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD19" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BE19" t="n">
-        <v>1.68</v>
+        <v>6.8</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.69</v>
+        <v>5.2</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.68</v>
+        <v>6.8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,78 +4235,78 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="G20" t="n">
-        <v>1.68</v>
+        <v>1.55</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I20" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
         <v>1.12</v>
       </c>
       <c r="N20" t="n">
-        <v>2.4</v>
+        <v>2.78</v>
       </c>
       <c r="O20" t="n">
-        <v>1.59</v>
+        <v>1.49</v>
       </c>
       <c r="P20" t="n">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="X20" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,10 +4315,10 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD20" t="n">
         <v>44</v>
@@ -4327,22 +4327,22 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AG20" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AK20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,16 +4351,16 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>14.5</v>
+        <v>5.2</v>
       </c>
       <c r="AR20" t="n">
         <v>6.2</v>
@@ -4369,57 +4369,57 @@
         <v>6.6</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX20" t="n">
         <v>6.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>4.3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BA20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG20" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BG20" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.63</v>
+        <v>2.2</v>
       </c>
       <c r="H21" t="n">
-        <v>7.8</v>
+        <v>3.7</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="O21" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.38</v>
+        <v>1.8</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>1.02</v>
       </c>
       <c r="T21" t="n">
-        <v>2.38</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="W21" t="n">
-        <v>2.58</v>
+        <v>1.83</v>
       </c>
       <c r="X21" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG21" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y21" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>970</v>
-      </c>
       <c r="AH21" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="AK21" t="n">
         <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="AW21" t="n">
         <v>6.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.7</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
-        <v>5.2</v>
+        <v>18.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE21" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,55 +4855,55 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.25</v>
       </c>
-      <c r="O23" t="n">
-        <v>1.37</v>
-      </c>
       <c r="P23" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.38</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S23" t="n">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>5.1</v>
+        <v>1.62</v>
       </c>
       <c r="H24" t="n">
-        <v>2.04</v>
+        <v>6.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N24" t="n">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="P24" t="n">
-        <v>1.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>1.79</v>
       </c>
       <c r="R24" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="V24" t="n">
-        <v>1.84</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>1.25</v>
+        <v>2.6</v>
       </c>
       <c r="X24" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Y24" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Z24" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB24" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC24" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>970</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.1</v>
+        <v>7.4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.97</v>
+        <v>8</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.98</v>
+        <v>7.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.98</v>
+        <v>7.6</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.99</v>
+        <v>8.6</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.91</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.94</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.04</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.77</v>
+        <v>13</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.76</v>
+        <v>14.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.76</v>
+        <v>6.8</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.78</v>
+        <v>7.8</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.69</v>
+        <v>7.8</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>2.04</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K25" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="P25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U25" t="n">
         <v>2.06</v>
       </c>
-      <c r="Q25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.94</v>
-      </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB25" t="n">
         <v>21</v>
       </c>
-      <c r="Y25" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ25" t="n">
+      <c r="BC25" t="n">
         <v>19</v>
       </c>
-      <c r="AR25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BD25" t="n">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="BF25" t="n">
-        <v>6.4</v>
+        <v>13.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.99</v>
+        <v>2.44</v>
       </c>
       <c r="G26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U26" t="n">
         <v>2.08</v>
       </c>
-      <c r="H26" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="V26" t="n">
         <v>1.42</v>
       </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="X26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>190</v>
+        <v>48</v>
       </c>
       <c r="AF26" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK26" t="n">
         <v>34</v>
       </c>
-      <c r="AK26" t="n">
-        <v>23</v>
-      </c>
       <c r="AL26" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
         <v>12</v>
       </c>
-      <c r="AQ26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR26" t="n">
+      <c r="AW26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC26" t="n">
         <v>22</v>
       </c>
-      <c r="AS26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA26" t="n">
+      <c r="BD26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG26" t="n">
         <v>30</v>
       </c>
-      <c r="BB26" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>29</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5593,81 +5593,81 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J27" t="n">
         <v>3.2</v>
       </c>
-      <c r="I27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="P27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -5676,19 +5676,19 @@
         <v>10.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD27" t="n">
         <v>16</v>
       </c>
       <c r="AE27" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF27" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH27" t="n">
         <v>21</v>
@@ -5700,77 +5700,77 @@
         <v>36</v>
       </c>
       <c r="AK27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
         <v>30</v>
       </c>
-      <c r="AL27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>32</v>
-      </c>
       <c r="AO27" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AQ27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU27" t="n">
         <v>6.6</v>
       </c>
       <c r="AV27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.34</v>
+        <v>1.69</v>
       </c>
       <c r="G28" t="n">
-        <v>2.56</v>
+        <v>1.81</v>
       </c>
       <c r="H28" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J28" t="n">
         <v>3.6</v>
       </c>
-      <c r="J28" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="W28" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Y28" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF28" t="n">
         <v>12</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15.5</v>
       </c>
       <c r="AG28" t="n">
         <v>12.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AK28" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM28" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO28" t="n">
         <v>160</v>
       </c>
-      <c r="AN28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP28" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.6</v>
+        <v>14.5</v>
       </c>
       <c r="AR28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>19.5</v>
       </c>
-      <c r="AS28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY28" t="n">
+      <c r="BA28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF28" t="n">
         <v>10</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>20</v>
-      </c>
       <c r="BG28" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="G29" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="H29" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
         <v>4.7</v>
       </c>
-      <c r="I29" t="n">
-        <v>8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>2.44</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>1.46</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>1.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
         <v>1.48</v>
       </c>
       <c r="P30" t="n">
-        <v>1.6</v>
+        <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="R30" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>4.4</v>
+        <v>1.48</v>
       </c>
       <c r="T30" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="U30" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W30" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z30" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD30" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE30" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI30" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM30" t="n">
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30" t="n">
-        <v>3.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR30" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW30" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY30" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="BB30" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BD30" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -6407,22 +6407,22 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O31" t="n">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="P31" t="n">
         <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R31" t="n">
         <v>1.18</v>
       </c>
       <c r="S31" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="T31" t="n">
         <v>1.01</v>
@@ -6546,14 +6546,14 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,55 +6568,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L32" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="O32" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="P32" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R32" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S32" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.89</v>
+        <v>2.84</v>
       </c>
       <c r="G33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H33" t="n">
         <v>2.54</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.65</v>
       </c>
-      <c r="I33" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>5.1</v>
-      </c>
       <c r="L33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R33" t="n">
         <v>1.32</v>
       </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.39</v>
-      </c>
       <c r="S33" t="n">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V33" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="W33" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF33" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,60 +6951,60 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="G34" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="H34" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="I34" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R34" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
         <v>1.78</v>
@@ -7013,82 +7013,82 @@
         <v>2.08</v>
       </c>
       <c r="V34" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="W34" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X34" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z34" t="n">
         <v>16</v>
       </c>
-      <c r="Y34" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>22</v>
-      </c>
       <c r="AA34" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AB34" t="n">
         <v>14</v>
       </c>
       <c r="AC34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AE34" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF34" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG34" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI34" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ34" t="n">
         <v>60</v>
       </c>
       <c r="AK34" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL34" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM34" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN34" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AO34" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AP34" t="n">
         <v>11</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>3.9</v>
+        <v>30</v>
       </c>
       <c r="AT34" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV34" t="n">
         <v>10.5</v>
@@ -7097,38 +7097,38 @@
         <v>24</v>
       </c>
       <c r="AX34" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AY34" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.9</v>
+        <v>36</v>
       </c>
       <c r="BB34" t="n">
-        <v>3.95</v>
+        <v>7.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>3.85</v>
+        <v>32</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.95</v>
+        <v>38</v>
       </c>
       <c r="BE34" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.8</v>
+        <v>30</v>
       </c>
       <c r="BG34" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="G35" t="n">
-        <v>3.4</v>
+        <v>2.48</v>
       </c>
       <c r="H35" t="n">
-        <v>2.42</v>
+        <v>3.25</v>
       </c>
       <c r="I35" t="n">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M35" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O35" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="S35" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="T35" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="U35" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="V35" t="n">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="W35" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
         <v>13</v>
       </c>
-      <c r="Y35" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>16</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>11</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>13.5</v>
+        <v>6.8</v>
       </c>
       <c r="AS35" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="AT35" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU35" t="n">
         <v>7</v>
       </c>
       <c r="AV35" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>24</v>
+        <v>7.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>19</v>
+        <v>5.9</v>
       </c>
       <c r="AY35" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AZ35" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BB35" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC35" t="n">
         <v>6.8</v>
       </c>
-      <c r="BC35" t="n">
-        <v>32</v>
-      </c>
       <c r="BD35" t="n">
-        <v>38</v>
+        <v>7.4</v>
       </c>
       <c r="BE35" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF35" t="n">
-        <v>30</v>
+        <v>6.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,191 +7339,191 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Deportivo Cali</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="F36" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q36" t="n">
         <v>2.26</v>
       </c>
-      <c r="G36" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="H36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="I36" t="n">
+      <c r="R36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X36" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV36" t="n">
         <v>3.65</v>
       </c>
-      <c r="J36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U36" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>10</v>
-      </c>
       <c r="AW36" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AX36" t="n">
-        <v>6.4</v>
+        <v>3.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.800000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BC36" t="n">
-        <v>7.4</v>
+        <v>3.95</v>
       </c>
       <c r="BD36" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="BE36" t="n">
-        <v>9.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF36" t="n">
-        <v>13</v>
+        <v>3.95</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Mexican Liga MX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,572 +7533,184 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>23:07:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Leon</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.88</v>
+        <v>1.41</v>
       </c>
       <c r="G37" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="H37" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>5.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="K37" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="L37" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="M37" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="O37" t="n">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="P37" t="n">
-        <v>1.76</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="R37" t="n">
-        <v>1.29</v>
+        <v>1.52</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="U37" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V37" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="W37" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="X37" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="Y37" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="Z37" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AA37" t="n">
-        <v>700</v>
+        <v>280</v>
       </c>
       <c r="AB37" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AD37" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AE37" t="n">
-        <v>700</v>
+        <v>130</v>
       </c>
       <c r="AF37" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AG37" t="n">
         <v>11</v>
       </c>
       <c r="AH37" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ37" t="n">
         <v>22</v>
       </c>
-      <c r="AI37" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>13</v>
-      </c>
       <c r="AR37" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AS37" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT37" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD37" t="n">
         <v>7</v>
       </c>
-      <c r="AV37" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>8</v>
-      </c>
       <c r="BE37" t="n">
-        <v>28</v>
+        <v>8.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>14</v>
+        <v>5.2</v>
       </c>
       <c r="BG37" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 07:40:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Colombian Primera A</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>22:30:00</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Deportivo Cali</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Santa Fe</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="G38" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="H38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="I38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N38" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X38" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-03-17 07:40:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Mexican Liga MX</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>23:07:00</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Guadalajara</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Leon</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H39" t="n">
-        <v>8</v>
-      </c>
-      <c r="I39" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J39" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH39" t="inlineStr">
-        <is>
-          <t>2026-03-17 07:40:15</t>
+          <t>2026-03-17 09:50:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,145 +757,145 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>2.64</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.11</v>
       </c>
-      <c r="N2" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.94</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO2" t="n">
         <v>75</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>65</v>
-      </c>
       <c r="AP2" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AW2" t="n">
         <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.1</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="BA2" t="n">
         <v>4.9</v>
@@ -913,14 +913,14 @@
         <v>5.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -975,146 +975,146 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X3" t="n">
         <v>12.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
         <v>22</v>
       </c>
       <c r="AE3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG3" t="n">
         <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ3" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK3" t="n">
         <v>28</v>
       </c>
-      <c r="AK3" t="n">
-        <v>27</v>
-      </c>
       <c r="AL3" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>5.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>6</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.52</v>
       </c>
       <c r="G4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H4" t="n">
         <v>7</v>
@@ -1157,13 +1157,13 @@
         <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
         <v>1.06</v>
@@ -1172,31 +1172,31 @@
         <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P4" t="n">
         <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
       </c>
       <c r="S4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W4" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X4" t="n">
         <v>17</v>
@@ -1223,13 +1223,13 @@
         <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI4" t="n">
         <v>110</v>
@@ -1247,19 +1247,19 @@
         <v>150</v>
       </c>
       <c r="AN4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO4" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AQ4" t="n">
         <v>20</v>
       </c>
       <c r="AR4" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AS4" t="n">
         <v>48</v>
@@ -1268,7 +1268,7 @@
         <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV4" t="n">
         <v>24</v>
@@ -1277,13 +1277,13 @@
         <v>38</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA4" t="n">
         <v>38</v>
@@ -1301,14 +1301,14 @@
         <v>44</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG4" t="n">
         <v>42</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>9.6</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I5" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.32</v>
@@ -1363,22 +1363,22 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O5" t="n">
         <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T5" t="n">
         <v>2.46</v>
@@ -1387,7 +1387,7 @@
         <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="W5" t="n">
         <v>1.06</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.3</v>
+        <v>1.92</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.27</v>
+        <v>1.87</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.28</v>
+        <v>1.89</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.31</v>
+        <v>1.93</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.31</v>
+        <v>1.94</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1536,19 +1536,19 @@
         <v>1.52</v>
       </c>
       <c r="G6" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.33</v>
@@ -1563,7 +1563,7 @@
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
         <v>1.72</v>
@@ -1581,31 +1581,31 @@
         <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W6" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y6" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="Z6" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA6" t="n">
         <v>230</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
         <v>110</v>
@@ -1614,10 +1614,10 @@
         <v>10.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
         <v>100</v>
@@ -1626,31 +1626,31 @@
         <v>18</v>
       </c>
       <c r="AK6" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AM6" t="n">
         <v>130</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AQ6" t="n">
         <v>20</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1659,22 +1659,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX6" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ6" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
         <v>12.5</v>
@@ -1683,20 +1683,20 @@
         <v>13.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>7.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.67</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.71</v>
-      </c>
       <c r="J7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R7" t="n">
         <v>1.48</v>
       </c>
       <c r="S7" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="W7" t="n">
         <v>1.21</v>
       </c>
       <c r="X7" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA7" t="n">
         <v>20</v>
       </c>
-      <c r="Y7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA7" t="n">
-        <v>970</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>10</v>
-      </c>
       <c r="AE7" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AG7" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AH7" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AJ7" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AK7" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AL7" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AO7" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP7" t="n">
-        <v>17</v>
+        <v>4.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>18.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AW7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX7" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AY7" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>5.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>5.3</v>
       </c>
       <c r="BD7" t="n">
-        <v>50</v>
+        <v>5.3</v>
       </c>
       <c r="BE7" t="n">
-        <v>11</v>
+        <v>5.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G8" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I8" t="n">
         <v>5.6</v>
       </c>
       <c r="J8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K8" t="n">
         <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.2</v>
       </c>
       <c r="L8" t="n">
         <v>1.23</v>
@@ -1951,16 +1951,16 @@
         <v>1.12</v>
       </c>
       <c r="P8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S8" t="n">
         <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.98</v>
       </c>
       <c r="T8" t="n">
         <v>1.51</v>
@@ -1972,7 +1972,7 @@
         <v>1.21</v>
       </c>
       <c r="W8" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="X8" t="n">
         <v>38</v>
@@ -1984,7 +1984,7 @@
         <v>55</v>
       </c>
       <c r="AA8" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB8" t="n">
         <v>17</v>
@@ -2005,25 +2005,25 @@
         <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI8" t="n">
         <v>46</v>
       </c>
       <c r="AJ8" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL8" t="n">
         <v>21</v>
       </c>
       <c r="AM8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AN8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO8" t="n">
         <v>34</v>
@@ -2035,10 +2035,10 @@
         <v>32</v>
       </c>
       <c r="AR8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS8" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="AT8" t="n">
         <v>15.5</v>
@@ -2050,7 +2050,7 @@
         <v>20</v>
       </c>
       <c r="AW8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX8" t="n">
         <v>13.5</v>
@@ -2059,13 +2059,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA8" t="n">
         <v>40</v>
       </c>
       <c r="BB8" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC8" t="n">
         <v>13</v>
@@ -2074,17 +2074,17 @@
         <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
         <v>30</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G9" t="n">
         <v>1.54</v>
       </c>
       <c r="H9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9" t="n">
         <v>4.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
         <v>1.04</v>
@@ -2145,7 +2145,7 @@
         <v>1.21</v>
       </c>
       <c r="P9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q9" t="n">
         <v>1.64</v>
@@ -2154,10 +2154,10 @@
         <v>1.56</v>
       </c>
       <c r="S9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U9" t="n">
         <v>2.08</v>
@@ -2169,25 +2169,25 @@
         <v>2.84</v>
       </c>
       <c r="X9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z9" t="n">
         <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AB9" t="n">
         <v>11</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE9" t="n">
         <v>110</v>
@@ -2199,19 +2199,19 @@
         <v>11</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM9" t="n">
         <v>120</v>
@@ -2223,28 +2223,28 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>20</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT9" t="n">
         <v>9</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AW9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AX9" t="n">
         <v>8.800000000000001</v>
@@ -2256,36 +2256,36 @@
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BB9" t="n">
         <v>11.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,179 +2300,179 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.66</v>
+        <v>2.48</v>
       </c>
       <c r="G10" t="n">
-        <v>1.79</v>
+        <v>2.68</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>3.6</v>
       </c>
       <c r="J10" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="K10" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P10" t="n">
         <v>1.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>1.59</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA10" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>9</v>
+        <v>7.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM10" t="n">
         <v>150</v>
       </c>
-      <c r="AF10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>250</v>
-      </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AS10" t="n">
         <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
         <v>7.8</v>
       </c>
       <c r="AX10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC10" t="n">
         <v>7.4</v>
       </c>
-      <c r="AY10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BA10" t="n">
+      <c r="BD10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB10" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7</v>
-      </c>
       <c r="BE10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG10" t="n">
         <v>8</v>
       </c>
-      <c r="BF10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.68</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q11" t="n">
         <v>2.2</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.96</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T11" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U11" t="n">
-        <v>2.14</v>
+        <v>1.87</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="W11" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>1.15</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>1.15</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>13.5</v>
+        <v>1.15</v>
       </c>
       <c r="AW11" t="n">
-        <v>28</v>
+        <v>1.15</v>
       </c>
       <c r="AX11" t="n">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>1.15</v>
       </c>
       <c r="AZ11" t="n">
-        <v>16</v>
+        <v>1.15</v>
       </c>
       <c r="BA11" t="n">
-        <v>14.5</v>
+        <v>1.15</v>
       </c>
       <c r="BB11" t="n">
-        <v>25</v>
+        <v>1.15</v>
       </c>
       <c r="BC11" t="n">
-        <v>19</v>
+        <v>1.15</v>
       </c>
       <c r="BD11" t="n">
-        <v>32</v>
+        <v>1.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="BF11" t="n">
-        <v>15.5</v>
+        <v>1.15</v>
       </c>
       <c r="BG11" t="n">
-        <v>34</v>
+        <v>1.15</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -2688,186 +2688,186 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.68</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H12" t="n">
         <v>3.7</v>
       </c>
-      <c r="H12" t="n">
-        <v>2.58</v>
-      </c>
       <c r="I12" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W12" t="n">
         <v>1.79</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.15</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.15</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.15</v>
+        <v>28</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.15</v>
+        <v>16</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.15</v>
+        <v>11.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.15</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.15</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.15</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.15</v>
+        <v>10.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.15</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.52</v>
+        <v>1.66</v>
       </c>
       <c r="G13" t="n">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>2.96</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.59</v>
+        <v>2.22</v>
       </c>
       <c r="X13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="Z13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="AF13" t="n">
-        <v>16.5</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
         <v>13</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ13" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AN13" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.6</v>
+        <v>3.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>19</v>
+        <v>4.1</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.6</v>
+        <v>4.3</v>
       </c>
       <c r="AT13" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX13" t="n">
         <v>7.6</v>
       </c>
-      <c r="AU13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>3.9</v>
       </c>
       <c r="BA13" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB13" t="n">
-        <v>8.4</v>
+        <v>3.65</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>3.65</v>
       </c>
       <c r="BD13" t="n">
-        <v>8.6</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="BF13" t="n">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="BG13" t="n">
-        <v>42</v>
+        <v>4.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Deportivo Tachira</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.37</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>1.38</v>
+        <v>150</v>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>1.61</v>
       </c>
       <c r="I14" t="n">
-        <v>9.199999999999999</v>
+        <v>1.84</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X14" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y14" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P14" t="n">
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3.55</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X14" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>23</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN14" t="n">
+      <c r="AS14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV14" t="n">
         <v>3.6</v>
       </c>
-      <c r="AO14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>44</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>15</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>14</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>30</v>
-      </c>
       <c r="AW14" t="n">
-        <v>80</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>19</v>
+        <v>4.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>65</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>5.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="BE14" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="BG14" t="n">
-        <v>55</v>
+        <v>3.75</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>1.36</v>
       </c>
       <c r="G15" t="n">
-        <v>2.68</v>
+        <v>1.37</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>9.4</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.76</v>
+        <v>1.36</v>
       </c>
       <c r="R15" t="n">
-        <v>1.52</v>
+        <v>2.08</v>
       </c>
       <c r="S15" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="T15" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U15" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.59</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.59</v>
+        <v>3.7</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="Y15" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>26</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>38</v>
-      </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>12.5</v>
       </c>
       <c r="AL15" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AM15" t="n">
         <v>70</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.5</v>
+        <v>3.55</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="AR15" t="n">
-        <v>17.5</v>
+        <v>75</v>
       </c>
       <c r="AS15" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU15" t="n">
-        <v>8.6</v>
+        <v>14.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="AW15" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AX15" t="n">
-        <v>18</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC15" t="n">
         <v>11.5</v>
       </c>
-      <c r="AZ15" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>23</v>
-      </c>
       <c r="BD15" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
         <v>60</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.5</v>
+        <v>3.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>1.32</v>
+        <v>2.74</v>
       </c>
       <c r="H16" t="n">
-        <v>10.5</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X16" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>11.5</v>
       </c>
-      <c r="J16" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>7</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>42</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AZ16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE16" t="n">
         <v>55</v>
       </c>
-      <c r="Z16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>360</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>75</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>70</v>
-      </c>
       <c r="BF16" t="n">
-        <v>3.3</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>1.66</v>
+        <v>1.31</v>
       </c>
       <c r="H17" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="I17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N17" t="n">
         <v>8.4</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.4</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.51</v>
+        <v>1.13</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.48</v>
+        <v>1.39</v>
       </c>
       <c r="R17" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="S17" t="n">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>2.26</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="W17" t="n">
-        <v>2.48</v>
+        <v>4.2</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="Y17" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="Z17" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AD17" t="n">
         <v>40</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF17" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AK17" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="AL17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>85</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA17" t="n">
         <v>80</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BB17" t="n">
-        <v>3.65</v>
+        <v>10.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.85</v>
+        <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>80</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.4</v>
+        <v>85</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -3852,73 +3852,73 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N18" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="O18" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="S18" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T18" t="n">
-        <v>2.22</v>
+        <v>2.58</v>
       </c>
       <c r="U18" t="n">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z18" t="n">
         <v>1000</v>
@@ -3927,31 +3927,31 @@
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK18" t="n">
         <v>1000</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3.6</v>
+        <v>5.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.3</v>
+        <v>7.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AU18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="AX18" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.32</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.86</v>
+        <v>5.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.18</v>
+        <v>6.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.31</v>
+        <v>7.4</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.41</v>
+        <v>5.7</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="K19" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
         <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="R19" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="S19" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="U19" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="X19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="n">
         <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AE19" t="n">
         <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG19" t="n">
         <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI19" t="n">
         <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AK19" t="n">
         <v>28</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AO19" t="n">
         <v>1000</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB19" t="n">
         <v>3.85</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX19" t="n">
+      <c r="BC19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3.85</v>
       </c>
-      <c r="AY19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BG19" t="n">
-        <v>6.8</v>
+        <v>4.7</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,78 +4235,78 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Boyaca Chico</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="G20" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="H20" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="O20" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P20" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R20" t="n">
         <v>1.21</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="U20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,34 +4315,34 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4357,69 +4357,69 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.2</v>
+        <v>2.96</v>
       </c>
       <c r="AR20" t="n">
-        <v>6.2</v>
+        <v>2.24</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.6</v>
+        <v>1.98</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.2</v>
+        <v>3.85</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>5.8</v>
+        <v>2.34</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="AX20" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.7</v>
+        <v>2.18</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.4</v>
+        <v>2.3</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.2</v>
+        <v>2.14</v>
       </c>
       <c r="BD20" t="n">
-        <v>6</v>
+        <v>2.26</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>1.99</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>2.1</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.6</v>
+        <v>1.51</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Manta FC</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Guayaquil City</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="H21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J21" t="n">
         <v>3.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY21" t="n">
         <v>4.6</v>
       </c>
-      <c r="J21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X21" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>27</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>190</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW21" t="n">
+      <c r="AZ21" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BA21" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>19</v>
+        <v>5.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.25</v>
+        <v>2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="T22" t="n">
-        <v>1.11</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,55 +4855,55 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>2.2</v>
+        <v>1.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P23" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>1.05</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4939,69 +4939,69 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,184 +5011,184 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>1.62</v>
+        <v>5.5</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>2.04</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV24" t="n">
         <v>4.2</v>
       </c>
-      <c r="K24" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="AW24" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BD24" t="n">
         <v>1.9</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X24" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>24</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BE24" t="n">
-        <v>7.8</v>
+        <v>1.92</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.8</v>
+        <v>1.91</v>
       </c>
       <c r="BG24" t="n">
-        <v>7.8</v>
+        <v>1.82</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.98</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="H25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.04</v>
       </c>
-      <c r="H25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="V25" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="Y25" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="Z25" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI25" t="n">
         <v>110</v>
       </c>
-      <c r="AB25" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>15.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AL25" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="AM25" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW25" t="n">
         <v>36</v>
       </c>
-      <c r="AT25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>38</v>
-      </c>
       <c r="AX25" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AY25" t="n">
         <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BB25" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="BD25" t="n">
         <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="BG25" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -5399,184 +5399,184 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
-        <v>2.56</v>
+        <v>2.04</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="P26" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="R26" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U26" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W26" t="n">
-        <v>1.64</v>
+        <v>1.97</v>
       </c>
       <c r="X26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB26" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AC26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE26" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF26" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK26" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW26" t="n">
         <v>46</v>
       </c>
-      <c r="AP26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="AX26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AR26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>14</v>
-      </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.6</v>
+        <v>30</v>
       </c>
       <c r="BB26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD26" t="n">
         <v>30</v>
       </c>
-      <c r="BC26" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE26" t="n">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="BF26" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="G27" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="H27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.4</v>
       </c>
-      <c r="I27" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.35</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="U27" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="V27" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W27" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
         <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB27" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD27" t="n">
         <v>16</v>
       </c>
       <c r="AE27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI27" t="n">
         <v>60</v>
       </c>
-      <c r="AF27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AN27" t="n">
         <v>30</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AY27" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC27" t="n">
         <v>23</v>
       </c>
       <c r="BD27" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Zamora FC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Portuguesa FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="G28" t="n">
-        <v>1.81</v>
+        <v>2.92</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>2.82</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L28" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2.32</v>
       </c>
       <c r="O28" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="P28" t="n">
-        <v>1.88</v>
+        <v>1.49</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>2.22</v>
+        <v>1.57</v>
       </c>
       <c r="X28" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="Z28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN28" t="n">
         <v>48</v>
       </c>
-      <c r="AA28" t="n">
-        <v>200</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AO28" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="AP28" t="n">
-        <v>11</v>
+        <v>3.45</v>
       </c>
       <c r="AQ28" t="n">
-        <v>14.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR28" t="n">
         <v>4.4</v>
       </c>
       <c r="AS28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB28" t="n">
         <v>4.7</v>
       </c>
-      <c r="AT28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>15.5</v>
-      </c>
       <c r="BC28" t="n">
-        <v>17</v>
+        <v>4.8</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF28" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N29" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P29" t="n">
         <v>1.81</v>
       </c>
-      <c r="H29" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I29" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q29" t="n">
-        <v>2.46</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z29" t="n">
         <v>60</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB29" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE29" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG29" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI29" t="n">
-        <v>170</v>
+        <v>120</v>
       </c>
       <c r="AJ29" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
         <v>25</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>5.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>32</v>
+        <v>5.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.98</v>
+        <v>19</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AZ29" t="n">
-        <v>2.44</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.6</v>
+        <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.22</v>
+        <v>17</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.46</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF29" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Atletico MG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.48</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="n">
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="O31" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,55 +6568,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M32" t="n">
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.22</v>
+        <v>1.48</v>
       </c>
       <c r="P32" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="R32" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="S32" t="n">
-        <v>2.36</v>
+        <v>1.48</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6625,10 +6625,10 @@
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
         <v>1000</v>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="O33" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P33" t="n">
-        <v>1.83</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="T33" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="G34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J34" t="n">
         <v>3.4</v>
       </c>
-      <c r="H34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I34" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="J34" t="n">
-        <v>3.35</v>
-      </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="M34" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="P34" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.06</v>
+        <v>1.55</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>2.36</v>
       </c>
       <c r="T34" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.64</v>
+        <v>1.27</v>
       </c>
       <c r="W34" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="X34" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,191 +7145,191 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.34</v>
+        <v>2.84</v>
       </c>
       <c r="G35" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="H35" t="n">
-        <v>3.25</v>
+        <v>2.54</v>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="J35" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="K35" t="n">
         <v>3.65</v>
       </c>
       <c r="L35" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="O35" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="P35" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="R35" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="S35" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="T35" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="U35" t="n">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="V35" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="W35" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="X35" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y35" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA35" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB35" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AC35" t="n">
         <v>9.4</v>
       </c>
       <c r="AD35" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AG35" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP35" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>13</v>
-      </c>
       <c r="AQ35" t="n">
-        <v>12.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU35" t="n">
         <v>6.8</v>
       </c>
-      <c r="AS35" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>7</v>
-      </c>
       <c r="AV35" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AW35" t="n">
-        <v>7.6</v>
+        <v>22</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.9</v>
+        <v>17.5</v>
       </c>
       <c r="AY35" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ35" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA35" t="n">
-        <v>7.6</v>
+        <v>3.85</v>
       </c>
       <c r="BB35" t="n">
-        <v>7.2</v>
+        <v>3.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="BD35" t="n">
-        <v>7.4</v>
+        <v>3.9</v>
       </c>
       <c r="BE35" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BG35" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,378 +7339,960 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="G36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H36" t="n">
         <v>2.44</v>
       </c>
-      <c r="H36" t="n">
-        <v>3.65</v>
-      </c>
       <c r="I36" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="J36" t="n">
-        <v>2.84</v>
+        <v>3.35</v>
       </c>
       <c r="K36" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S36" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.42</v>
       </c>
-      <c r="M36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P36" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T36" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U36" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.71</v>
-      </c>
       <c r="X36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD36" t="n">
         <v>12</v>
       </c>
-      <c r="Y36" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AE36" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG36" t="n">
         <v>20</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 09:50:56</t>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X37" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:01:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:01:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G39" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X39" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:01:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>23:07:00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Leon</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F40" t="n">
         <v>1.41</v>
       </c>
-      <c r="G37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="G40" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H40" t="n">
         <v>8</v>
       </c>
-      <c r="I37" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="I40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K40" t="n">
         <v>5.5</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L40" t="n">
         <v>1.27</v>
       </c>
-      <c r="M37" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N37" t="n">
+      <c r="M40" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N40" t="n">
         <v>4.9</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O40" t="n">
         <v>1.21</v>
       </c>
-      <c r="P37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>26</v>
-      </c>
-      <c r="Y37" t="n">
+      <c r="P40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X40" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y40" t="n">
         <v>32</v>
       </c>
-      <c r="Z37" t="n">
-        <v>75</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>280</v>
-      </c>
-      <c r="AB37" t="n">
+      <c r="Z40" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB40" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AC40" t="n">
         <v>12</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AD40" t="n">
         <v>32</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AE40" t="n">
         <v>130</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AF40" t="n">
         <v>10</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AG40" t="n">
         <v>11</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AH40" t="n">
         <v>24</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AI40" t="n">
         <v>110</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AJ40" t="n">
         <v>13.5</v>
       </c>
-      <c r="AK37" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL37" t="n">
+      <c r="AK40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL40" t="n">
         <v>34</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AM40" t="n">
         <v>130</v>
       </c>
-      <c r="AN37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
+      <c r="AN40" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
         <v>19</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AQ40" t="n">
         <v>22</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AR40" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA40" t="n">
         <v>8</v>
       </c>
-      <c r="AS37" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX37" t="n">
+      <c r="BB40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE40" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY37" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA37" t="n">
+      <c r="BF40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG40" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB37" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>2026-03-17 09:50:56</t>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-17 12:01:47</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH42"/>
+  <dimension ref="A1:BH43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="H2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.41</v>
@@ -796,19 +796,19 @@
         <v>1.22</v>
       </c>
       <c r="S2" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W2" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
@@ -975,7 +975,7 @@
         <v>1.1</v>
       </c>
       <c r="N3" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="O3" t="n">
         <v>1.46</v>
@@ -984,25 +984,25 @@
         <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="V3" t="n">
         <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
@@ -1065,13 +1065,13 @@
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>27</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU3" t="n">
         <v>6.8</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.53</v>
@@ -1169,10 +1169,10 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P4" t="n">
         <v>1.46</v>
@@ -1190,19 +1190,19 @@
         <v>2.36</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1217,7 +1217,7 @@
         <v>8.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
@@ -1229,7 +1229,7 @@
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1241,7 +1241,7 @@
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1253,16 +1253,16 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4" t="n">
         <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AT4" t="n">
         <v>5</v>
@@ -1271,44 +1271,44 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AW4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX4" t="n">
         <v>7.8</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BF4" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
         <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
         <v>1.85</v>
@@ -1381,7 +1381,7 @@
         <v>3.2</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>1.91</v>
@@ -1393,7 +1393,7 @@
         <v>2.88</v>
       </c>
       <c r="X5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>25</v>
@@ -1414,25 +1414,25 @@
         <v>28</v>
       </c>
       <c r="AE5" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH5" t="n">
         <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
         <v>13.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
         <v>38</v>
@@ -1447,7 +1447,7 @@
         <v>140</v>
       </c>
       <c r="AP5" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>22</v>
@@ -1462,7 +1462,7 @@
         <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV5" t="n">
         <v>24</v>
@@ -1471,13 +1471,13 @@
         <v>38</v>
       </c>
       <c r="AX5" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
         <v>38</v>
@@ -1486,7 +1486,7 @@
         <v>11.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>32</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>19</v>
@@ -1542,37 +1542,37 @@
         <v>1.31</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.55</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.35</v>
       </c>
       <c r="T6" t="n">
         <v>1.11</v>
@@ -1581,7 +1581,7 @@
         <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1590,13 +1590,13 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.6</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J7" t="n">
         <v>1.03</v>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.01</v>
@@ -1760,13 +1760,13 @@
         <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K8" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
         <v>1.33</v>
@@ -1951,7 +1951,7 @@
         <v>1.27</v>
       </c>
       <c r="P8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q8" t="n">
         <v>1.71</v>
@@ -1963,16 +1963,16 @@
         <v>2.76</v>
       </c>
       <c r="T8" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="U8" t="n">
         <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W8" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="X8" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
         <v>230</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC8" t="n">
         <v>11</v>
@@ -2005,7 +2005,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
         <v>100</v>
@@ -2029,16 +2029,16 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT8" t="n">
         <v>8.4</v>
@@ -2047,10 +2047,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV8" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX8" t="n">
         <v>8.6</v>
@@ -2059,10 +2059,10 @@
         <v>9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB8" t="n">
         <v>12.5</v>
@@ -2071,20 +2071,20 @@
         <v>13.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2118,19 +2118,19 @@
         <v>5.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="I9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="J9" t="n">
         <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L9" t="n">
         <v>1.33</v>
@@ -2163,7 +2163,7 @@
         <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="W9" t="n">
         <v>1.19</v>
@@ -2187,10 +2187,10 @@
         <v>10.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AF9" t="n">
         <v>1000</v>
@@ -2217,7 +2217,7 @@
         <v>120</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO9" t="n">
         <v>8.199999999999999</v>
@@ -2235,7 +2235,7 @@
         <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU9" t="n">
         <v>9</v>
@@ -2247,38 +2247,38 @@
         <v>14</v>
       </c>
       <c r="AX9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY9" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB9" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC9" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC9" t="n">
-        <v>9</v>
-      </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="BE9" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG9" t="n">
         <v>7.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="G10" t="n">
         <v>1.62</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.63</v>
       </c>
       <c r="H10" t="n">
         <v>5.4</v>
@@ -2348,22 +2348,22 @@
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="T10" t="n">
         <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="V10" t="n">
         <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y10" t="n">
         <v>36</v>
@@ -2378,7 +2378,7 @@
         <v>17.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
         <v>21</v>
@@ -2411,10 +2411,10 @@
         <v>50</v>
       </c>
       <c r="AN10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AP10" t="n">
         <v>36</v>
@@ -2426,7 +2426,7 @@
         <v>50</v>
       </c>
       <c r="AS10" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AT10" t="n">
         <v>16</v>
@@ -2465,14 +2465,14 @@
         <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG10" t="n">
         <v>30</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G11" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H11" t="n">
         <v>7.2</v>
@@ -2518,43 +2518,43 @@
         <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M11" t="n">
         <v>1.04</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V11" t="n">
         <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X11" t="n">
         <v>27</v>
@@ -2620,10 +2620,10 @@
         <v>7.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>9.4</v>
@@ -2659,14 +2659,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>1.69</v>
       </c>
       <c r="G12" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,34 +2721,34 @@
         <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.44</v>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R12" t="n">
         <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
         <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
         <v>12.5</v>
@@ -2799,13 +2799,13 @@
         <v>240</v>
       </c>
       <c r="AN12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
         <v>3.65</v>
@@ -2820,13 +2820,13 @@
         <v>5.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX12" t="n">
         <v>7.8</v>
@@ -2835,16 +2835,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="BA12" t="n">
         <v>4.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD12" t="n">
         <v>4.1</v>
@@ -2853,14 +2853,14 @@
         <v>4.3</v>
       </c>
       <c r="BF12" t="n">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="BG12" t="n">
         <v>4.3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H13" t="n">
         <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>1.34</v>
@@ -2915,16 +2915,16 @@
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R13" t="n">
         <v>1.36</v>
@@ -2933,7 +2933,7 @@
         <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U13" t="n">
         <v>2.24</v>
@@ -2942,7 +2942,7 @@
         <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
@@ -2957,7 +2957,7 @@
         <v>70</v>
       </c>
       <c r="AB13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC13" t="n">
         <v>7.8</v>
@@ -3002,13 +3002,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
         <v>23</v>
       </c>
       <c r="AS13" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="AT13" t="n">
         <v>9</v>
@@ -3032,7 +3032,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
         <v>25</v>
@@ -3044,17 +3044,17 @@
         <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
         <v>15.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="G14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K14" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3112,13 +3112,13 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
         <v>1.23</v>
@@ -3127,16 +3127,16 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V14" t="n">
         <v>1.48</v>
       </c>
       <c r="W14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3208,7 +3208,7 @@
         <v>1.15</v>
       </c>
       <c r="AU14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV14" t="n">
         <v>1.15</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
         <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3309,10 +3309,10 @@
         <v>1.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R15" t="n">
         <v>1.25</v>
@@ -3321,28 +3321,28 @@
         <v>4.6</v>
       </c>
       <c r="T15" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
         <v>9.4</v>
@@ -3351,22 +3351,22 @@
         <v>6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
         <v>44</v>
@@ -3381,37 +3381,37 @@
         <v>140</v>
       </c>
       <c r="AN15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
         <v>19.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT15" t="n">
         <v>8</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV15" t="n">
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.4</v>
+        <v>40</v>
       </c>
       <c r="AX15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -3420,29 +3420,29 @@
         <v>15.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>1.81</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R16" t="n">
         <v>1.28</v>
@@ -3515,10 +3515,10 @@
         <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>2.16</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G17" t="n">
         <v>1.38</v>
       </c>
       <c r="H17" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>9.199999999999999</v>
@@ -3697,7 +3697,7 @@
         <v>1.11</v>
       </c>
       <c r="P17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
         <v>1.35</v>
@@ -3706,7 +3706,7 @@
         <v>2.08</v>
       </c>
       <c r="S17" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="T17" t="n">
         <v>1.64</v>
@@ -3730,7 +3730,7 @@
         <v>95</v>
       </c>
       <c r="AA17" t="n">
-        <v>240</v>
+        <v>290</v>
       </c>
       <c r="AB17" t="n">
         <v>17</v>
@@ -3769,7 +3769,7 @@
         <v>70</v>
       </c>
       <c r="AN17" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AO17" t="n">
         <v>70</v>
@@ -3781,13 +3781,13 @@
         <v>44</v>
       </c>
       <c r="AR17" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AS17" t="n">
         <v>100</v>
       </c>
       <c r="AT17" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU17" t="n">
         <v>14.5</v>
@@ -3823,14 +3823,14 @@
         <v>60</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -3861,16 +3861,16 @@
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G18" t="n">
         <v>2.7</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.74</v>
-      </c>
       <c r="H18" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="I18" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="J18" t="n">
         <v>4</v>
@@ -3879,37 +3879,37 @@
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R18" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S18" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U18" t="n">
         <v>2.52</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
         <v>1.58</v>
@@ -3921,13 +3921,13 @@
         <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
         <v>38</v>
       </c>
       <c r="AB18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC18" t="n">
         <v>9.6</v>
@@ -3975,7 +3975,7 @@
         <v>13.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
         <v>34</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX18" t="n">
         <v>18.5</v>
@@ -4017,14 +4017,14 @@
         <v>55</v>
       </c>
       <c r="BF18" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I19" t="n">
         <v>11</v>
-      </c>
-      <c r="I19" t="n">
-        <v>11.5</v>
       </c>
       <c r="J19" t="n">
         <v>6.8</v>
@@ -4079,49 +4079,49 @@
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="R19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S19" t="n">
         <v>1.96</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.02</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="X19" t="n">
         <v>40</v>
       </c>
       <c r="Y19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z19" t="n">
         <v>110</v>
       </c>
       <c r="AA19" t="n">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AC19" t="n">
         <v>16</v>
@@ -4139,13 +4139,13 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI19" t="n">
         <v>95</v>
       </c>
       <c r="AJ19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
         <v>12</v>
@@ -4157,16 +4157,16 @@
         <v>95</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AO19" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AR19" t="n">
         <v>90</v>
@@ -4175,7 +4175,7 @@
         <v>110</v>
       </c>
       <c r="AT19" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU19" t="n">
         <v>15.5</v>
@@ -4184,7 +4184,7 @@
         <v>34</v>
       </c>
       <c r="AW19" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AX19" t="n">
         <v>10</v>
@@ -4193,13 +4193,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC19" t="n">
         <v>11.5</v>
@@ -4211,14 +4211,14 @@
         <v>80</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BG19" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.66</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
@@ -4288,7 +4288,7 @@
         <v>1.2</v>
       </c>
       <c r="S20" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="T20" t="n">
         <v>2.4</v>
@@ -4357,10 +4357,10 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AR20" t="n">
         <v>10.5</v>
@@ -4369,10 +4369,10 @@
         <v>12</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AU20" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV20" t="n">
         <v>9</v>
@@ -4381,10 +4381,10 @@
         <v>11.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
         <v>9</v>
@@ -4393,10 +4393,10 @@
         <v>11.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BC20" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4405,14 +4405,14 @@
         <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="G21" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>7.6</v>
+        <v>6.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.44</v>
@@ -4467,34 +4467,34 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="O21" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P21" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R21" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="U21" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="V21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4551,62 +4551,62 @@
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4.5</v>
       </c>
-      <c r="BA21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4</v>
-      </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -4643,13 +4643,13 @@
         <v>1.68</v>
       </c>
       <c r="H22" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I22" t="n">
         <v>10.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
         <v>3.9</v>
@@ -4661,7 +4661,7 @@
         <v>1.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="O22" t="n">
         <v>1.58</v>
@@ -4676,7 +4676,7 @@
         <v>1.16</v>
       </c>
       <c r="S22" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="T22" t="n">
         <v>2.56</v>
@@ -4739,68 +4739,68 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.45</v>
+        <v>7.2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS22" t="n">
         <v>5.3</v>
       </c>
       <c r="AT22" t="n">
-        <v>2.84</v>
+        <v>4.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>3.55</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.35</v>
+        <v>6.8</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BD22" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
         <v>5.3</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>1.55</v>
       </c>
       <c r="G23" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="H23" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="I23" t="n">
         <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.42</v>
@@ -4861,10 +4861,10 @@
         <v>1.48</v>
       </c>
       <c r="P23" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R23" t="n">
         <v>1.21</v>
@@ -4873,22 +4873,22 @@
         <v>4.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="V23" t="n">
         <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="X23" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD23" t="n">
         <v>44</v>
@@ -4909,7 +4909,7 @@
         <v>260</v>
       </c>
       <c r="AF23" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG23" t="n">
         <v>970</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
         <v>5.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
         <v>11</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.98</v>
       </c>
       <c r="G24" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H24" t="n">
         <v>3.7</v>
@@ -5055,7 +5055,7 @@
         <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q24" t="n">
         <v>1.8</v>
@@ -5064,7 +5064,7 @@
         <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T24" t="n">
         <v>1.76</v>
@@ -5076,7 +5076,7 @@
         <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="X24" t="n">
         <v>14</v>
@@ -5136,7 +5136,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.8</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
         <v>5.7</v>
@@ -5184,11 +5184,11 @@
         <v>13.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -5413,10 +5413,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H26" t="n">
         <v>2.04</v>
@@ -5425,28 +5425,28 @@
         <v>2.2</v>
       </c>
       <c r="J26" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="L26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="O26" t="n">
         <v>1.25</v>
       </c>
       <c r="P26" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
@@ -5458,19 +5458,19 @@
         <v>1.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
         <v>1.84</v>
       </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
         <v>970</v>
@@ -5521,62 +5521,62 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.84</v>
+        <v>3.85</v>
       </c>
       <c r="AR26" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.86</v>
+        <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>2.3</v>
+        <v>6.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.14</v>
+        <v>1.35</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="BB26" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="BF26" t="n">
-        <v>2.3</v>
+        <v>1.34</v>
       </c>
       <c r="BG26" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H27" t="n">
         <v>6.2</v>
@@ -5619,7 +5619,7 @@
         <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
         <v>4.5</v>
@@ -5649,16 +5649,16 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V27" t="n">
         <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X27" t="n">
         <v>17.5</v>
@@ -5676,7 +5676,7 @@
         <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD27" t="n">
         <v>26</v>
@@ -5685,7 +5685,7 @@
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG27" t="n">
         <v>10</v>
@@ -5721,13 +5721,13 @@
         <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU27" t="n">
         <v>8.800000000000001</v>
@@ -5736,7 +5736,7 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AX27" t="n">
         <v>8.6</v>
@@ -5757,20 +5757,20 @@
         <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="BF27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG27" t="n">
-        <v>11.5</v>
+        <v>40</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -5840,13 +5840,13 @@
         <v>1.35</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
         <v>1.84</v>
       </c>
       <c r="U28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V28" t="n">
         <v>1.29</v>
@@ -5873,19 +5873,19 @@
         <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE28" t="n">
         <v>60</v>
       </c>
       <c r="AF28" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG28" t="n">
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI28" t="n">
         <v>70</v>
@@ -5921,19 +5921,19 @@
         <v>36</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU28" t="n">
         <v>7.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW28" t="n">
         <v>46</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>9.199999999999999</v>
@@ -5951,7 +5951,7 @@
         <v>18.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BE28" t="n">
         <v>38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
         <v>1.31</v>
       </c>
       <c r="S29" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
         <v>1.84</v>
@@ -6043,7 +6043,7 @@
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W29" t="n">
         <v>1.64</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -6192,13 +6192,13 @@
         <v>2.38</v>
       </c>
       <c r="G30" t="n">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="H30" t="n">
         <v>3.3</v>
       </c>
       <c r="I30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>2.8</v>
@@ -6228,7 +6228,7 @@
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
         <v>2.08</v>
@@ -6237,7 +6237,7 @@
         <v>1.72</v>
       </c>
       <c r="V30" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
         <v>1.56</v>
@@ -6264,10 +6264,10 @@
         <v>19</v>
       </c>
       <c r="AE30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF30" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AG30" t="n">
         <v>15</v>
@@ -6294,7 +6294,7 @@
         <v>50</v>
       </c>
       <c r="AO30" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -6306,7 +6306,7 @@
         <v>19.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT30" t="n">
         <v>6.4</v>
@@ -6318,7 +6318,7 @@
         <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AX30" t="n">
         <v>12.5</v>
@@ -6330,29 +6330,29 @@
         <v>19.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF30" t="n">
         <v>5.1</v>
       </c>
-      <c r="BE30" t="n">
+      <c r="BG30" t="n">
         <v>5.3</v>
       </c>
-      <c r="BF30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G31" t="n">
         <v>2.54</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I31" t="n">
         <v>3.6</v>
@@ -6428,7 +6428,7 @@
         <v>1.92</v>
       </c>
       <c r="U31" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
         <v>1.39</v>
@@ -6491,7 +6491,7 @@
         <v>60</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ31" t="n">
         <v>9.800000000000001</v>
@@ -6500,7 +6500,7 @@
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="AT31" t="n">
         <v>7.6</v>
@@ -6521,10 +6521,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
         <v>6.4</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
         <v>5.5</v>
@@ -6610,13 +6610,13 @@
         <v>1.81</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R32" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
         <v>2</v>
@@ -6628,7 +6628,7 @@
         <v>1.19</v>
       </c>
       <c r="W32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X32" t="n">
         <v>15.5</v>
@@ -6655,7 +6655,7 @@
         <v>120</v>
       </c>
       <c r="AF32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AG32" t="n">
         <v>11</v>
@@ -6691,34 +6691,34 @@
         <v>14.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT32" t="n">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV32" t="n">
         <v>19</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AX32" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.7</v>
+        <v>9</v>
       </c>
       <c r="AZ32" t="n">
         <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BB32" t="n">
         <v>16</v>
@@ -6727,27 +6727,27 @@
         <v>17</v>
       </c>
       <c r="BD32" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE32" t="n">
         <v>7</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>7.8</v>
       </c>
       <c r="BF32" t="n">
         <v>11</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Internacional de Bogotá</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Olancho</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.69</v>
+        <v>1.26</v>
       </c>
       <c r="G33" t="n">
-        <v>1.7</v>
+        <v>1000</v>
       </c>
       <c r="H33" t="n">
-        <v>6.2</v>
+        <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="J33" t="n">
-        <v>3.6</v>
+        <v>1.03</v>
       </c>
       <c r="K33" t="n">
-        <v>3.9</v>
+        <v>950</v>
       </c>
       <c r="L33" t="n">
         <v>1.01</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>2.78</v>
+        <v>1.24</v>
       </c>
       <c r="O33" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="P33" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.46</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S33" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="V33" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W33" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AC33" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ33" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR33" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU33" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW33" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX33" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA33" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BD33" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG33" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,184 +6951,184 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:20:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Internacional de Bogotá</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Deportivo Pereira</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>2.86</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="S34" t="n">
-        <v>1.79</v>
+        <v>4.9</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W34" t="n">
-        <v>1.47</v>
+        <v>2.32</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM34" t="n">
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7150,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Libertad</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q35" t="n">
         <v>1.01</v>
@@ -7198,7 +7198,7 @@
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.05</v>
+        <v>1.79</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -7210,7 +7210,7 @@
         <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,14 +7322,14 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7344,73 +7344,73 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
         <v>1.05</v>
       </c>
-      <c r="N36" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="P36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S36" t="n">
-        <v>2.66</v>
-      </c>
       <c r="T36" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="X36" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
         <v>1000</v>
@@ -7419,34 +7419,34 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
         <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
         <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
         <v>1000</v>
@@ -7455,75 +7455,75 @@
         <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,114 +7533,114 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Libertad FC</t>
+          <t>Metropolitanos</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Barcelona (ECU)</t>
+          <t>Monagas</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.84</v>
+        <v>2.08</v>
       </c>
       <c r="G37" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="H37" t="n">
-        <v>2.54</v>
+        <v>3.65</v>
       </c>
       <c r="I37" t="n">
-        <v>2.88</v>
+        <v>3.85</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="M37" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="O37" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V37" t="n">
         <v>1.35</v>
       </c>
-      <c r="P37" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S37" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.53</v>
-      </c>
       <c r="W37" t="n">
-        <v>1.45</v>
+        <v>1.77</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="Z37" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC37" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AD37" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AE37" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>30</v>
+        <v>16.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AH37" t="n">
-        <v>26</v>
+        <v>19.5</v>
       </c>
       <c r="AI37" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK37" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="AL37" t="n">
         <v>1000</v>
@@ -7649,75 +7649,75 @@
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.16</v>
+        <v>14.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.9</v>
+        <v>12.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>2</v>
+        <v>5.3</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.08</v>
+        <v>5.9</v>
       </c>
       <c r="AT37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY37" t="n">
         <v>9.4</v>
       </c>
-      <c r="AU37" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AZ37" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.08</v>
+        <v>34</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.06</v>
+        <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.1</v>
+        <v>5.5</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.16</v>
+        <v>6</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.16</v>
+        <v>12</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.16</v>
+        <v>21</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7727,184 +7727,184 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Libertad FC</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Barcelona (ECU)</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="G38" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H38" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="I38" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="J38" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="K38" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="L38" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M38" t="n">
         <v>1.08</v>
       </c>
       <c r="N38" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P38" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T38" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="U38" t="n">
-        <v>2.1</v>
+        <v>1.74</v>
       </c>
       <c r="V38" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="W38" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X38" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z38" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
         <v>16</v>
       </c>
-      <c r="AA38" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>12</v>
-      </c>
       <c r="AC38" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AE38" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF38" t="n">
         <v>29</v>
       </c>
-      <c r="AF38" t="n">
-        <v>23</v>
-      </c>
       <c r="AG38" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AI38" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AL38" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>11</v>
+        <v>2.26</v>
       </c>
       <c r="AQ38" t="n">
         <v>9</v>
       </c>
       <c r="AR38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>30</v>
+        <v>2.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>10.5</v>
+        <v>1.99</v>
       </c>
       <c r="AU38" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW38" t="n">
-        <v>9.6</v>
+        <v>2.16</v>
       </c>
       <c r="AX38" t="n">
-        <v>19</v>
+        <v>2.1</v>
       </c>
       <c r="AY38" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>16</v>
+        <v>2.08</v>
       </c>
       <c r="BA38" t="n">
-        <v>36</v>
+        <v>2.18</v>
       </c>
       <c r="BB38" t="n">
-        <v>11.5</v>
+        <v>2.2</v>
       </c>
       <c r="BC38" t="n">
-        <v>34</v>
+        <v>2.18</v>
       </c>
       <c r="BD38" t="n">
-        <v>11</v>
+        <v>2.2</v>
       </c>
       <c r="BE38" t="n">
-        <v>12.5</v>
+        <v>2.28</v>
       </c>
       <c r="BF38" t="n">
-        <v>27</v>
+        <v>2.26</v>
       </c>
       <c r="BG38" t="n">
-        <v>20</v>
+        <v>2.26</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -7926,186 +7926,186 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="G39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H39" t="n">
         <v>2.46</v>
       </c>
-      <c r="H39" t="n">
-        <v>3.25</v>
-      </c>
       <c r="I39" t="n">
-        <v>3.55</v>
+        <v>2.56</v>
       </c>
       <c r="J39" t="n">
         <v>3.35</v>
       </c>
       <c r="K39" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L39" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M39" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O39" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="R39" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="S39" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="T39" t="n">
-        <v>1.71</v>
+        <v>1.83</v>
       </c>
       <c r="U39" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="V39" t="n">
-        <v>1.39</v>
+        <v>1.64</v>
       </c>
       <c r="W39" t="n">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="X39" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH39" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y39" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z39" t="n">
+      <c r="AI39" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS39" t="n">
         <v>30</v>
       </c>
-      <c r="AA39" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>13</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AT39" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU39" t="n">
         <v>7</v>
       </c>
       <c r="AV39" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY39" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>10</v>
-      </c>
       <c r="AZ39" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
-        <v>5.3</v>
+        <v>36</v>
       </c>
       <c r="BB39" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BD39" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="BE39" t="n">
-        <v>5.3</v>
+        <v>12.5</v>
       </c>
       <c r="BF39" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="BG39" t="n">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -8120,179 +8120,179 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Atletico Bucaramanga</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Once Caldas</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.86</v>
+        <v>2.32</v>
       </c>
       <c r="G40" t="n">
-        <v>1.92</v>
+        <v>2.48</v>
       </c>
       <c r="H40" t="n">
-        <v>5.1</v>
+        <v>3.3</v>
       </c>
       <c r="I40" t="n">
-        <v>5.5</v>
+        <v>3.55</v>
       </c>
       <c r="J40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K40" t="n">
         <v>3.6</v>
       </c>
       <c r="L40" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N40" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="O40" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="R40" t="n">
         <v>1.4</v>
       </c>
-      <c r="P40" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="U40" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="V40" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>2.06</v>
+        <v>1.67</v>
       </c>
       <c r="X40" t="n">
-        <v>12.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y40" t="n">
         <v>16.5</v>
       </c>
       <c r="Z40" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AA40" t="n">
-        <v>700</v>
+        <v>70</v>
       </c>
       <c r="AB40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC40" t="n">
         <v>8</v>
       </c>
-      <c r="AC40" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AD40" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AE40" t="n">
-        <v>700</v>
+        <v>46</v>
       </c>
       <c r="AF40" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AG40" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH40" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>700</v>
+        <v>55</v>
       </c>
       <c r="AJ40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN40" t="n">
         <v>23</v>
       </c>
-      <c r="AK40" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>120</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>17</v>
-      </c>
       <c r="AO40" t="n">
-        <v>700</v>
+        <v>40</v>
       </c>
       <c r="AP40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY40" t="n">
         <v>10</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>32</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AZ40" t="n">
         <v>14</v>
       </c>
       <c r="BA40" t="n">
-        <v>8.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>18</v>
+        <v>6.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="BD40" t="n">
-        <v>7.6</v>
+        <v>5.2</v>
       </c>
       <c r="BE40" t="n">
-        <v>29</v>
+        <v>5.6</v>
       </c>
       <c r="BF40" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BG40" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
@@ -8309,378 +8309,572 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Deportivo Cali</t>
+          <t>Atletico Bucaramanga</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Once Caldas</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.22</v>
+        <v>1.86</v>
       </c>
       <c r="G41" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="H41" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="J41" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L41" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M41" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="P41" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="V41" t="n">
         <v>1.22</v>
       </c>
-      <c r="S41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.32</v>
-      </c>
       <c r="W41" t="n">
-        <v>1.71</v>
+        <v>2.06</v>
       </c>
       <c r="X41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y41" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>120</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>450</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>700</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF41" t="n">
         <v>13.5</v>
       </c>
-      <c r="Z41" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>38</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BG41" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-17 14:12:51</t>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="H42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>23:07:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Leon</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="H42" t="n">
-        <v>8</v>
-      </c>
-      <c r="I42" t="n">
+      <c r="F43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="J43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X43" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>60</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY43" t="n">
         <v>9</v>
       </c>
-      <c r="J42" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N42" t="n">
+      <c r="AZ43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF43" t="n">
         <v>5</v>
       </c>
-      <c r="O42" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W42" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="X42" t="n">
-        <v>24</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF42" t="n">
+      <c r="BG43" t="n">
         <v>10</v>
       </c>
-      <c r="AG42" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE42" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF42" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG42" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH42" t="inlineStr">
-        <is>
-          <t>2026-03-17 14:12:51</t>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-17 16:24:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -787,7 +787,7 @@
         <v>1.45</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
         <v>2.32</v>
@@ -799,10 +799,10 @@
         <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
         <v>1.36</v>
@@ -874,7 +874,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -898,29 +898,29 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD2" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -951,28 +951,28 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L3" t="n">
         <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3" t="n">
         <v>2.94</v>
@@ -981,10 +981,10 @@
         <v>1.46</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -993,22 +993,22 @@
         <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W3" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y3" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z3" t="n">
         <v>32</v>
@@ -1017,13 +1017,13 @@
         <v>110</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>70</v>
@@ -1032,13 +1032,13 @@
         <v>11.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ3" t="n">
         <v>27</v>
@@ -1050,37 +1050,37 @@
         <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AO3" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP3" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>11.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="AS3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AT3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV3" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1089,32 +1089,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD3" t="n">
-        <v>40</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BF3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>12</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
         <v>1.93</v>
@@ -1160,7 +1160,7 @@
         <v>3.15</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4" t="n">
         <v>1.53</v>
@@ -1187,10 +1187,10 @@
         <v>5.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="V4" t="n">
         <v>1.17</v>
@@ -1271,7 +1271,7 @@
         <v>7</v>
       </c>
       <c r="AV4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AW4" t="n">
         <v>8.800000000000001</v>
@@ -1283,7 +1283,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BA4" t="n">
         <v>8.800000000000001</v>
@@ -1292,7 +1292,7 @@
         <v>17.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BD4" t="n">
         <v>8.199999999999999</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I5" t="n">
         <v>7.2</v>
       </c>
-      <c r="I5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="J5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5" t="n">
         <v>1.38</v>
@@ -1384,19 +1384,19 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V5" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z5" t="n">
         <v>65</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
         <v>10.5</v>
@@ -1417,7 +1417,7 @@
         <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
         <v>9.800000000000001</v>
@@ -1435,40 +1435,40 @@
         <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
         <v>140</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP5" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT5" t="n">
         <v>7.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX5" t="n">
         <v>8.199999999999999</v>
@@ -1477,13 +1477,13 @@
         <v>9.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA5" t="n">
         <v>38</v>
       </c>
       <c r="BB5" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC5" t="n">
         <v>14.5</v>
@@ -1492,17 +1492,17 @@
         <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
         <v>7.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
         <v>19</v>
@@ -1542,7 +1542,7 @@
         <v>1.31</v>
       </c>
       <c r="I6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="J6" t="n">
         <v>4.4</v>
@@ -1557,7 +1557,7 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.38</v>
@@ -1569,19 +1569,19 @@
         <v>1.94</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="S6" t="n">
         <v>3.55</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>2.72</v>
       </c>
       <c r="U6" t="n">
         <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="W6" t="n">
         <v>1.05</v>
@@ -1644,13 +1644,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AT6" t="n">
         <v>4.2</v>
@@ -1659,7 +1659,7 @@
         <v>3.65</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AW6" t="n">
         <v>3.95</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie B</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CA Vinotinto</t>
+          <t>Basaksehir</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportivo Santo Domingo</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>990</v>
+        <v>1.56</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="I7" t="n">
-        <v>990</v>
+        <v>7.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>4.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>2.76</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -1912,34 +1912,34 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Basaksehir</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.51</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1.56</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>1.69</v>
       </c>
       <c r="I8" t="n">
-        <v>7.6</v>
+        <v>1.73</v>
       </c>
       <c r="J8" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>1.05</v>
@@ -1948,150 +1948,150 @@
         <v>4.5</v>
       </c>
       <c r="O8" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S8" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T8" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.15</v>
+        <v>2.36</v>
       </c>
       <c r="W8" t="n">
-        <v>2.8</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Y8" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="Z8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL8" t="n">
         <v>70</v>
       </c>
-      <c r="AA8" t="n">
-        <v>230</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA8" t="n">
         <v>26</v>
       </c>
-      <c r="AI8" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>42</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BB8" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BC8" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.4</v>
+        <v>60</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.2</v>
+        <v>50</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>14:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Eyupspor</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Newcastle</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.5</v>
+        <v>1.65</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>1.66</v>
       </c>
       <c r="H9" t="n">
-        <v>1.62</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.67</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>48</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF9" t="n">
         <v>4.7</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V9" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X9" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>40</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>26</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BG9" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:45:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Newcastle</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="I10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="X10" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>230</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF10" t="n">
         <v>5.5</v>
       </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N10" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P10" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>120</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>46</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SSD Bari</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.49</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="M11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU11" t="n">
         <v>7.2</v>
       </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="K11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="X11" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AV11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX11" t="n">
         <v>7.8</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="AY11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>4.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>4.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ecuadorian Serie A</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Macara</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Delfin</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.69</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.4</v>
       </c>
-      <c r="K12" t="n">
-        <v>3.8</v>
-      </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1.63</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>1.97</v>
       </c>
       <c r="R12" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="X12" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>260</v>
+        <v>70</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG12" t="n">
         <v>11</v>
       </c>
-      <c r="AG12" t="n">
-        <v>13</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>160</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
         <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM12" t="n">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.65</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.1</v>
+        <v>23</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.9</v>
+        <v>13.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.3</v>
+        <v>29</v>
       </c>
       <c r="AX12" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.7</v>
+        <v>25</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.8</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.3</v>
+        <v>12.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.55</v>
+        <v>15.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.3</v>
+        <v>34</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -2882,179 +2882,179 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Pescara</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Entella</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.98</v>
       </c>
       <c r="G13" t="n">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
-        <v>3.55</v>
+        <v>2.96</v>
       </c>
       <c r="L13" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
-        <v>3.75</v>
+        <v>2.96</v>
       </c>
       <c r="O13" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.63</v>
       </c>
       <c r="Q13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U13" t="n">
         <v>1.97</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U13" t="n">
-        <v>2.24</v>
-      </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="W13" t="n">
-        <v>1.8</v>
+        <v>1.49</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="AR13" t="n">
-        <v>23</v>
+        <v>1.15</v>
       </c>
       <c r="AS13" t="n">
-        <v>55</v>
+        <v>1.15</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>1.15</v>
       </c>
       <c r="AU13" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>13.5</v>
+        <v>1.15</v>
       </c>
       <c r="AW13" t="n">
-        <v>28</v>
+        <v>1.15</v>
       </c>
       <c r="AX13" t="n">
-        <v>12.5</v>
+        <v>1.15</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>1.15</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>1.15</v>
       </c>
       <c r="BB13" t="n">
-        <v>25</v>
+        <v>1.15</v>
       </c>
       <c r="BC13" t="n">
-        <v>19</v>
+        <v>1.15</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>1.15</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>1.15</v>
       </c>
       <c r="BF13" t="n">
-        <v>15.5</v>
+        <v>1.15</v>
       </c>
       <c r="BG13" t="n">
-        <v>36</v>
+        <v>1.15</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Calcio Avellino SSD</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sudtirol</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.96</v>
       </c>
-      <c r="G14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="I14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.98</v>
-      </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N14" t="n">
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
         <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.15</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.15</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
         <v>6</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.15</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.15</v>
+        <v>40</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.15</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.15</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.15</v>
+        <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.15</v>
+        <v>12.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.15</v>
+        <v>32</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.15</v>
+        <v>29</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.15</v>
+        <v>46</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.15</v>
+        <v>13.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.15</v>
+        <v>10.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.15</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Italian Serie B</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Deportivo Tachira</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>8</v>
       </c>
       <c r="H15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="J15" t="n">
         <v>3.4</v>
       </c>
-      <c r="I15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.74</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.98</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S15" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="X15" t="n">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>22</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.6</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AF15" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>18.5</v>
+        <v>27</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AJ15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>970</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="AQ15" t="n">
-        <v>10</v>
+        <v>3.25</v>
       </c>
       <c r="AR15" t="n">
-        <v>19.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS15" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AT15" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="AW15" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>4.8</v>
       </c>
       <c r="AY15" t="n">
-        <v>11</v>
+        <v>4.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA15" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BC15" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="BE15" t="n">
-        <v>11.5</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>9.4</v>
+        <v>3.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>10.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Deportivo Tachira</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>1.38</v>
       </c>
       <c r="G16" t="n">
-        <v>8</v>
+        <v>1.39</v>
       </c>
       <c r="H16" t="n">
-        <v>1.56</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="K16" t="n">
         <v>6.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="M16" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="P16" t="n">
-        <v>1.81</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.96</v>
+        <v>1.36</v>
       </c>
       <c r="R16" t="n">
-        <v>1.28</v>
+        <v>2.08</v>
       </c>
       <c r="S16" t="n">
-        <v>3.3</v>
+        <v>1.89</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>2.16</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>3.55</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="Z16" t="n">
-        <v>970</v>
+        <v>95</v>
       </c>
       <c r="AA16" t="n">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="AB16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD16" t="n">
         <v>22</v>
       </c>
-      <c r="AC16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>22</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="BE16" t="n">
         <v>60</v>
       </c>
-      <c r="AG16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU16" t="n">
+      <c r="BF16" t="n">
         <v>3.45</v>
       </c>
-      <c r="AV16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BG16" t="n">
-        <v>3.75</v>
+        <v>55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.36</v>
+        <v>2.62</v>
       </c>
       <c r="G17" t="n">
-        <v>1.38</v>
+        <v>2.64</v>
       </c>
       <c r="H17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU17" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="I17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="J17" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P17" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X17" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AV17" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AW17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="n">
         <v>23</v>
       </c>
-      <c r="AM17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BE17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.4</v>
+        <v>15</v>
       </c>
       <c r="BG17" t="n">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.66</v>
+        <v>1.31</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="H18" t="n">
-        <v>2.62</v>
+        <v>10.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2.64</v>
+        <v>11</v>
       </c>
       <c r="J18" t="n">
-        <v>4</v>
+        <v>6.8</v>
       </c>
       <c r="K18" t="n">
+        <v>7</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W18" t="n">
         <v>4.1</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N18" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.58</v>
-      </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>110</v>
       </c>
       <c r="AA18" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD18" t="n">
         <v>38</v>
       </c>
-      <c r="AB18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AE18" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>12</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AK18" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>38</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>75</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD18" t="n">
         <v>24</v>
       </c>
-      <c r="AF18" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>65</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>34</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>29</v>
-      </c>
       <c r="BE18" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="BF18" t="n">
-        <v>15.5</v>
+        <v>3.35</v>
       </c>
       <c r="BG18" t="n">
-        <v>15.5</v>
+        <v>75</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="G19" t="n">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="H19" t="n">
-        <v>10.5</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>6.8</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="L19" t="n">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="M19" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>8.6</v>
+        <v>2.82</v>
       </c>
       <c r="O19" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>1.63</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.38</v>
+        <v>2.3</v>
       </c>
       <c r="R19" t="n">
-        <v>2.02</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>1.96</v>
+        <v>4.3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>2.28</v>
+        <v>1.69</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="W19" t="n">
-        <v>4.1</v>
+        <v>2.32</v>
       </c>
       <c r="X19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>38</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>44</v>
+        <v>6.2</v>
       </c>
       <c r="AR19" t="n">
-        <v>90</v>
+        <v>4.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>110</v>
+        <v>2.06</v>
       </c>
       <c r="AT19" t="n">
-        <v>14</v>
+        <v>3.85</v>
       </c>
       <c r="AU19" t="n">
-        <v>15.5</v>
+        <v>4.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>34</v>
+        <v>2.48</v>
       </c>
       <c r="AW19" t="n">
-        <v>95</v>
+        <v>2.04</v>
       </c>
       <c r="AX19" t="n">
-        <v>10</v>
+        <v>4.8</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>5.2</v>
       </c>
       <c r="AZ19" t="n">
-        <v>23</v>
+        <v>2.52</v>
       </c>
       <c r="BA19" t="n">
-        <v>75</v>
+        <v>2.06</v>
       </c>
       <c r="BB19" t="n">
-        <v>11</v>
+        <v>3.9</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>2.44</v>
       </c>
       <c r="BD19" t="n">
-        <v>24</v>
+        <v>2.62</v>
       </c>
       <c r="BE19" t="n">
-        <v>80</v>
+        <v>2.06</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>85</v>
+        <v>2.06</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,73 +4240,73 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>CA Vinotinto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Deportivo Santo Domingo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1.66</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>990</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T20" t="n">
         <v>1.11</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
         <v>1000</v>
@@ -4315,34 +4315,34 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4434,73 +4434,73 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="G21" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="I21" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="N21" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="O21" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="P21" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="R21" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="U21" t="n">
-        <v>1.72</v>
+        <v>1.52</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="W21" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z21" t="n">
         <v>1000</v>
@@ -4509,104 +4509,104 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
         <v>7.2</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>3.9</v>
+        <v>6.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>14</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD21" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H22" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="n">
+        <v>9</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="X22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR22" t="n">
         <v>10.5</v>
       </c>
-      <c r="J22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AS22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT22" t="n">
         <v>5.1</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>4.6</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BB22" t="n">
         <v>14</v>
       </c>
       <c r="BC22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.4</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -4843,13 +4843,13 @@
         <v>11.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
         <v>1.12</v>
@@ -4882,10 +4882,10 @@
         <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
         <v>24</v>
@@ -4909,7 +4909,7 @@
         <v>260</v>
       </c>
       <c r="AF23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG23" t="n">
         <v>970</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU23" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.4</v>
-      </c>
       <c r="AV23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX23" t="n">
         <v>6.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF23" t="n">
         <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5049,7 @@
         <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.34</v>
@@ -5058,7 +5058,7 @@
         <v>1.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R24" t="n">
         <v>1.32</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5246,13 +5246,13 @@
         <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
         <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="R25" t="n">
         <v>1.18</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>4</v>
       </c>
       <c r="G26" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H26" t="n">
         <v>2.04</v>
@@ -5428,7 +5428,7 @@
         <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.42</v>
@@ -5437,34 +5437,34 @@
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="O26" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="V26" t="n">
         <v>1.84</v>
       </c>
       <c r="W26" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X26" t="n">
         <v>970</v>
@@ -5527,19 +5527,19 @@
         <v>3.85</v>
       </c>
       <c r="AR26" t="n">
-        <v>2.08</v>
+        <v>1.77</v>
       </c>
       <c r="AS26" t="n">
         <v>6.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>4.8</v>
+        <v>1.56</v>
       </c>
       <c r="AU26" t="n">
         <v>3.9</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.6</v>
+        <v>1.54</v>
       </c>
       <c r="AW26" t="n">
         <v>1.3</v>
@@ -5548,7 +5548,7 @@
         <v>6.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AZ26" t="n">
         <v>1.35</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5637,7 @@
         <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
         <v>1.87</v>
@@ -5649,7 +5649,7 @@
         <v>3.2</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
         <v>1.99</v>
@@ -5661,10 +5661,10 @@
         <v>2.58</v>
       </c>
       <c r="X27" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z27" t="n">
         <v>60</v>
@@ -5721,7 +5721,7 @@
         <v>18.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AS27" t="n">
         <v>46</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>1.99</v>
       </c>
       <c r="G28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J28" t="n">
         <v>3.6</v>
@@ -5819,7 +5819,7 @@
         <v>3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
         <v>1.07</v>
@@ -5828,7 +5828,7 @@
         <v>3.75</v>
       </c>
       <c r="O28" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
         <v>1.92</v>
@@ -5852,7 +5852,7 @@
         <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="X28" t="n">
         <v>14.5</v>
@@ -5873,7 +5873,7 @@
         <v>8.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE28" t="n">
         <v>60</v>
@@ -5885,7 +5885,7 @@
         <v>11</v>
       </c>
       <c r="AH28" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI28" t="n">
         <v>70</v>
@@ -5912,10 +5912,10 @@
         <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS28" t="n">
         <v>36</v>
@@ -5930,7 +5930,7 @@
         <v>15.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="AX28" t="n">
         <v>10.5</v>
@@ -5942,16 +5942,16 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB28" t="n">
         <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD28" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BE28" t="n">
         <v>38</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="H29" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I29" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J29" t="n">
         <v>3.3</v>
@@ -6025,7 +6025,7 @@
         <v>1.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q29" t="n">
         <v>2.12</v>
@@ -6043,16 +6043,16 @@
         <v>2.08</v>
       </c>
       <c r="V29" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W29" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X29" t="n">
         <v>12.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
         <v>22</v>
@@ -6061,7 +6061,7 @@
         <v>60</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC29" t="n">
         <v>7.6</v>
@@ -6106,16 +6106,16 @@
         <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR29" t="n">
         <v>18.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU29" t="n">
         <v>6.8</v>
@@ -6124,13 +6124,13 @@
         <v>12</v>
       </c>
       <c r="AW29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY29" t="n">
         <v>10</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>10.5</v>
       </c>
       <c r="AZ29" t="n">
         <v>16</v>
@@ -6139,16 +6139,16 @@
         <v>10.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC29" t="n">
         <v>23</v>
       </c>
       <c r="BD29" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF29" t="n">
         <v>19.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="G30" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="H30" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="K30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M30" t="n">
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O30" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P30" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R30" t="n">
         <v>1.18</v>
       </c>
       <c r="S30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U30" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AA30" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AK30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AL30" t="n">
         <v>75</v>
       </c>
       <c r="AM30" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN30" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO30" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS30" t="n">
         <v>7</v>
       </c>
-      <c r="AQ30" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AU30" t="n">
         <v>6</v>
       </c>
       <c r="AV30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX30" t="n">
         <v>13.5</v>
       </c>
-      <c r="AW30" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
         <v>19.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="BB30" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="BC30" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="BE30" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G31" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="H31" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J31" t="n">
         <v>3.2</v>
@@ -6407,16 +6407,16 @@
         <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P31" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
         <v>1.26</v>
@@ -6425,40 +6425,40 @@
         <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U31" t="n">
         <v>1.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W31" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
         <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="n">
         <v>16</v>
@@ -6485,34 +6485,34 @@
         <v>160</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
         <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR31" t="n">
         <v>19.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU31" t="n">
         <v>6.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -6524,29 +6524,29 @@
         <v>17.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB31" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD31" t="n">
-        <v>6.8</v>
+        <v>42</v>
       </c>
       <c r="BE31" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BF31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J32" t="n">
         <v>3.6</v>
@@ -6607,7 +6607,7 @@
         <v>1.38</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q32" t="n">
         <v>2.12</v>
@@ -6715,7 +6715,7 @@
         <v>9</v>
       </c>
       <c r="AZ32" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA32" t="n">
         <v>7</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6795,7 +6795,7 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O33" t="n">
         <v>1.24</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>3.5</v>
       </c>
       <c r="K34" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,13 +6989,13 @@
         <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q34" t="n">
         <v>2.46</v>
@@ -7034,7 +7034,7 @@
         <v>7.4</v>
       </c>
       <c r="AC34" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD34" t="n">
         <v>28</v>
@@ -7073,52 +7073,52 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="AT34" t="n">
         <v>5.6</v>
       </c>
       <c r="AU34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX34" t="n">
         <v>4.1</v>
       </c>
-      <c r="AV34" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX34" t="n">
+      <c r="AY34" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA34" t="n">
         <v>4</v>
       </c>
-      <c r="AY34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BB34" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BF34" t="n">
         <v>12</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>2.08</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H37" t="n">
         <v>3.65</v>
@@ -7598,7 +7598,7 @@
         <v>1.35</v>
       </c>
       <c r="W37" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X37" t="n">
         <v>19.5</v>
@@ -7637,7 +7637,7 @@
         <v>50</v>
       </c>
       <c r="AJ37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK37" t="n">
         <v>24</v>
@@ -7652,7 +7652,7 @@
         <v>15</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP37" t="n">
         <v>14.5</v>
@@ -7661,7 +7661,7 @@
         <v>12.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>5.3</v>
+        <v>22</v>
       </c>
       <c r="AS37" t="n">
         <v>5.9</v>
@@ -7676,7 +7676,7 @@
         <v>12.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AX37" t="n">
         <v>13</v>
@@ -7691,26 +7691,26 @@
         <v>34</v>
       </c>
       <c r="BB37" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BC37" t="n">
         <v>18.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BE37" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF37" t="n">
         <v>12</v>
       </c>
       <c r="BG37" t="n">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
         <v>2.88</v>
       </c>
       <c r="G38" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="H38" t="n">
         <v>2.54</v>
@@ -7753,7 +7753,7 @@
         <v>2.68</v>
       </c>
       <c r="J38" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.65</v>
@@ -7792,7 +7792,7 @@
         <v>1.59</v>
       </c>
       <c r="W38" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7858,10 +7858,10 @@
         <v>12</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.99</v>
+        <v>9.6</v>
       </c>
       <c r="AU38" t="n">
         <v>6.6</v>
@@ -7876,7 +7876,7 @@
         <v>2.1</v>
       </c>
       <c r="AY38" t="n">
-        <v>10</v>
+        <v>2.02</v>
       </c>
       <c r="AZ38" t="n">
         <v>2.08</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -8049,7 +8049,7 @@
         <v>9</v>
       </c>
       <c r="AR39" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS39" t="n">
         <v>30</v>
@@ -8064,7 +8064,7 @@
         <v>10.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX39" t="n">
         <v>19</v>
@@ -8073,7 +8073,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA39" t="n">
         <v>36</v>
@@ -8082,7 +8082,7 @@
         <v>11.5</v>
       </c>
       <c r="BC39" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BD39" t="n">
         <v>11</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G40" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I40" t="n">
         <v>3.55</v>
       </c>
       <c r="J40" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K40" t="n">
         <v>3.6</v>
@@ -8150,16 +8150,16 @@
         <v>1.39</v>
       </c>
       <c r="M40" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N40" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="Q40" t="n">
         <v>1.85</v>
@@ -8171,22 +8171,22 @@
         <v>3.2</v>
       </c>
       <c r="T40" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U40" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V40" t="n">
         <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="X40" t="n">
         <v>18.5</v>
       </c>
       <c r="Y40" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Z40" t="n">
         <v>30</v>
@@ -8195,7 +8195,7 @@
         <v>70</v>
       </c>
       <c r="AB40" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC40" t="n">
         <v>8</v>
@@ -8207,7 +8207,7 @@
         <v>46</v>
       </c>
       <c r="AF40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG40" t="n">
         <v>13</v>
@@ -8228,28 +8228,28 @@
         <v>44</v>
       </c>
       <c r="AM40" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO40" t="n">
         <v>40</v>
       </c>
       <c r="AP40" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ40" t="n">
         <v>12.5</v>
       </c>
       <c r="AR40" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS40" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU40" t="n">
         <v>7</v>
@@ -8258,7 +8258,7 @@
         <v>12.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX40" t="n">
         <v>14</v>
@@ -8267,10 +8267,10 @@
         <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB40" t="n">
         <v>6.8</v>
@@ -8279,20 +8279,20 @@
         <v>21</v>
       </c>
       <c r="BD40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE40" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE40" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF40" t="n">
-        <v>16</v>
+        <v>4.4</v>
       </c>
       <c r="BG40" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8329,7 @@
         <v>1.92</v>
       </c>
       <c r="H41" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I41" t="n">
         <v>5.5</v>
@@ -8338,7 +8338,7 @@
         <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L41" t="n">
         <v>1.4</v>
@@ -8356,7 +8356,7 @@
         <v>1.76</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R41" t="n">
         <v>1.29</v>
@@ -8365,7 +8365,7 @@
         <v>4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U41" t="n">
         <v>1.93</v>
@@ -8374,16 +8374,16 @@
         <v>1.22</v>
       </c>
       <c r="W41" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X41" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y41" t="n">
         <v>16.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AA41" t="n">
         <v>700</v>
@@ -8410,7 +8410,7 @@
         <v>22</v>
       </c>
       <c r="AI41" t="n">
-        <v>450</v>
+        <v>700</v>
       </c>
       <c r="AJ41" t="n">
         <v>23</v>
@@ -8422,7 +8422,7 @@
         <v>46</v>
       </c>
       <c r="AM41" t="n">
-        <v>580</v>
+        <v>800</v>
       </c>
       <c r="AN41" t="n">
         <v>17</v>
@@ -8437,10 +8437,10 @@
         <v>13</v>
       </c>
       <c r="AR41" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AS41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT41" t="n">
         <v>6.8</v>
@@ -8452,7 +8452,7 @@
         <v>17</v>
       </c>
       <c r="AW41" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="AX41" t="n">
         <v>9.6</v>
@@ -8461,7 +8461,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ41" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BA41" t="n">
         <v>9.800000000000001</v>
@@ -8473,7 +8473,7 @@
         <v>18.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE41" t="n">
         <v>29</v>
@@ -8482,11 +8482,11 @@
         <v>13.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>
@@ -8711,43 +8711,43 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="G43" t="n">
         <v>1.44</v>
       </c>
       <c r="H43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I43" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J43" t="n">
         <v>5.2</v>
       </c>
       <c r="K43" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L43" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M43" t="n">
         <v>1.04</v>
       </c>
       <c r="N43" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O43" t="n">
         <v>1.21</v>
       </c>
       <c r="P43" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="R43" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S43" t="n">
         <v>2.6</v>
@@ -8756,22 +8756,22 @@
         <v>1.92</v>
       </c>
       <c r="U43" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X43" t="n">
         <v>24</v>
       </c>
       <c r="Y43" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="Z43" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AA43" t="n">
         <v>290</v>
@@ -8822,13 +8822,13 @@
         <v>19</v>
       </c>
       <c r="AQ43" t="n">
-        <v>22</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR43" t="n">
         <v>60</v>
       </c>
       <c r="AS43" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT43" t="n">
         <v>8.800000000000001</v>
@@ -8837,22 +8837,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV43" t="n">
-        <v>25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX43" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY43" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ43" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BA43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB43" t="n">
         <v>10.5</v>
@@ -8861,10 +8861,10 @@
         <v>12.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="BE43" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF43" t="n">
         <v>5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-17 16:24:34</t>
+          <t>2026-03-17 18:34:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,7 +805,7 @@
         <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
         <v>1.61</v>
@@ -817,10 +817,10 @@
         <v>11.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA2" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AB2" t="n">
         <v>8.800000000000001</v>
@@ -847,7 +847,7 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -874,7 +874,7 @@
         <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>7.2</v>
@@ -886,7 +886,7 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -898,29 +898,29 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
         <v>1.11</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
         <v>1.46</v>
@@ -990,13 +990,13 @@
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
         <v>2.06</v>
       </c>
       <c r="U3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="V3" t="n">
         <v>1.28</v>
@@ -1011,7 +1011,7 @@
         <v>13</v>
       </c>
       <c r="Z3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1020,10 +1020,10 @@
         <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE3" t="n">
         <v>160</v>
@@ -1068,7 +1068,7 @@
         <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
@@ -1080,7 +1080,7 @@
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1104,17 +1104,17 @@
         <v>24</v>
       </c>
       <c r="BE3" t="n">
-        <v>19.5</v>
+        <v>65</v>
       </c>
       <c r="BF3" t="n">
         <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G4" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H4" t="n">
         <v>5.8</v>
@@ -1157,13 +1157,13 @@
         <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K4" t="n">
         <v>3.55</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
@@ -1178,13 +1178,13 @@
         <v>1.46</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
         <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="T4" t="n">
         <v>2.38</v>
@@ -1241,7 +1241,7 @@
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1295,10 +1295,10 @@
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF4" t="n">
         <v>20</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>1.54</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H5" t="n">
         <v>6.8</v>
@@ -1357,46 +1357,46 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T5" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X5" t="n">
         <v>18</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
@@ -1405,19 +1405,19 @@
         <v>220</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG5" t="n">
         <v>9.800000000000001</v>
@@ -1432,25 +1432,25 @@
         <v>13.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO5" t="n">
         <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
         <v>50</v>
@@ -1462,13 +1462,13 @@
         <v>8.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX5" t="n">
         <v>8.6</v>
@@ -1486,7 +1486,7 @@
         <v>12.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD5" t="n">
         <v>30</v>
@@ -1498,11 +1498,11 @@
         <v>7</v>
       </c>
       <c r="BG5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O6" t="n">
         <v>1.01</v>
@@ -1566,7 +1566,7 @@
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.18</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
         <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.2</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -1927,43 +1927,43 @@
         <v>21</v>
       </c>
       <c r="H8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="I8" t="n">
         <v>1.38</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
         <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
         <v>1.32</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="U8" t="n">
         <v>1.54</v>
@@ -2032,16 +2032,16 @@
         <v>5.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR8" t="n">
         <v>4.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2050,19 +2050,19 @@
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX8" t="n">
         <v>4.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.1</v>
+        <v>9</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="BB8" t="n">
         <v>4.2</v>
@@ -2074,17 +2074,17 @@
         <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.9</v>
+        <v>2.42</v>
       </c>
       <c r="BF8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O9" t="n">
         <v>1.12</v>
@@ -2154,7 +2154,7 @@
         <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T9" t="n">
         <v>1.11</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="H10" t="n">
         <v>6.6</v>
       </c>
       <c r="I10" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
@@ -2357,16 +2357,16 @@
         <v>2.06</v>
       </c>
       <c r="V10" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="X10" t="n">
         <v>21</v>
       </c>
       <c r="Y10" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="Z10" t="n">
         <v>420</v>
@@ -2378,7 +2378,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
         <v>60</v>
@@ -2390,7 +2390,7 @@
         <v>10.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
@@ -2420,13 +2420,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
         <v>8.4</v>
@@ -2435,22 +2435,22 @@
         <v>9.4</v>
       </c>
       <c r="AV10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>19</v>
       </c>
       <c r="BA10" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
         <v>12.5</v>
@@ -2468,11 +2468,11 @@
         <v>6.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="I11" t="n">
         <v>1.71</v>
@@ -2533,22 +2533,22 @@
         <v>1.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S11" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>2.4</v>
@@ -2557,10 +2557,10 @@
         <v>1.21</v>
       </c>
       <c r="X11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
@@ -2575,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE11" t="n">
         <v>16.5</v>
@@ -2590,7 +2590,7 @@
         <v>19.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="AJ11" t="n">
         <v>140</v>
@@ -2611,7 +2611,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AP11" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>9</v>
@@ -2623,13 +2623,13 @@
         <v>15.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AU11" t="n">
         <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
         <v>15</v>
@@ -2647,26 +2647,26 @@
         <v>26</v>
       </c>
       <c r="BB11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="BD11" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="BE11" t="n">
         <v>26</v>
       </c>
       <c r="BF11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>4.9</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
         <v>1.22</v>
@@ -2727,16 +2727,16 @@
         <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="R12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S12" t="n">
         <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.98</v>
       </c>
       <c r="T12" t="n">
         <v>1.49</v>
@@ -2754,7 +2754,7 @@
         <v>40</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z12" t="n">
         <v>55</v>
@@ -2796,13 +2796,13 @@
         <v>21</v>
       </c>
       <c r="AM12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AO12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP12" t="n">
         <v>36</v>
@@ -2811,7 +2811,7 @@
         <v>32</v>
       </c>
       <c r="AR12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AS12" t="n">
         <v>110</v>
@@ -2835,13 +2835,13 @@
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BC12" t="n">
         <v>13</v>
@@ -2853,21 +2853,21 @@
         <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rayo Zuliano</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Tachira</t>
+          <t>SSD Bari</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N13" t="n">
         <v>5.3</v>
       </c>
-      <c r="G13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O13" t="n">
-        <v>1.35</v>
+        <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.56</v>
       </c>
       <c r="S13" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="V13" t="n">
-        <v>2.16</v>
+        <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>1.15</v>
+        <v>2.8</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="Z13" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>230</v>
       </c>
       <c r="AB13" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>480</v>
       </c>
       <c r="AF13" t="n">
-        <v>500</v>
+        <v>11</v>
       </c>
       <c r="AG13" t="n">
-        <v>950</v>
+        <v>10</v>
       </c>
       <c r="AH13" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>500</v>
+        <v>190</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.9</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX13" t="n">
         <v>9</v>
       </c>
-      <c r="AT13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AY13" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>3</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.34</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.32</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.32</v>
+        <v>26</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.76</v>
+        <v>48</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.34</v>
+        <v>5.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Macara</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Delfin</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.38</v>
+        <v>1.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1.39</v>
+        <v>1.78</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC14" t="n">
         <v>8.6</v>
       </c>
-      <c r="J14" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="AD14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF14" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X14" t="n">
-        <v>44</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>46</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>210</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AG14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AR14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
         <v>19.5</v>
       </c>
-      <c r="AI14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="AW14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF14" t="n">
         <v>13</v>
       </c>
-      <c r="AL14" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>40</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>55</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG14" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tottenham</t>
+          <t>Pescara</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Atletico Madrid</t>
+          <t>Entella</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.64</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>2.44</v>
+        <v>1.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="U15" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="X15" t="n">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Y15" t="n">
         <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>38</v>
+        <v>440</v>
       </c>
       <c r="AB15" t="n">
-        <v>14.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD15" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AH15" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI15" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>60</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD15" t="n">
         <v>32</v>
       </c>
-      <c r="AT15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>29</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>29</v>
-      </c>
       <c r="BE15" t="n">
-        <v>55</v>
+        <v>15.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Champions League</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Calcio Avellino SSD</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Sudtirol</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.31</v>
+        <v>2.88</v>
       </c>
       <c r="G16" t="n">
-        <v>1.32</v>
+        <v>3</v>
       </c>
       <c r="H16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA16" t="n">
         <v>10</v>
       </c>
-      <c r="I16" t="n">
+      <c r="BB16" t="n">
         <v>10.5</v>
       </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="BC16" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF16" t="n">
         <v>7.2</v>
       </c>
-      <c r="L16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N16" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>27</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>75</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>70</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>75</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.45</v>
-      </c>
       <c r="BG16" t="n">
-        <v>80</v>
+        <v>7.2</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Italian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Kabylie</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P17" t="n">
         <v>1.66</v>
       </c>
-      <c r="G17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.63</v>
-      </c>
       <c r="Q17" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="U17" t="n">
-        <v>1.69</v>
+        <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>370</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.2</v>
       </c>
-      <c r="AC17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AV17" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.1</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>3.75</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>7.8</v>
+        <v>29</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.6</v>
+        <v>23</v>
       </c>
       <c r="BE17" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Rayo Zuliano</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ES Setif</t>
+          <t>Deportivo Tachira</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.59</v>
+        <v>5.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1.68</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
-        <v>7.6</v>
+        <v>1.65</v>
       </c>
       <c r="I18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X18" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>950</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS18" t="n">
         <v>9</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N18" t="n">
+      <c r="AT18" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BF18" t="n">
         <v>2.44</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="X18" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>540</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>9</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>14</v>
-      </c>
       <c r="BG18" t="n">
-        <v>8.800000000000001</v>
+        <v>3.45</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Algerian Ligue 1</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Belouizdad</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N19" t="n">
         <v>9</v>
       </c>
-      <c r="J19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>1.11</v>
       </c>
-      <c r="N19" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.5</v>
-      </c>
       <c r="P19" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>1.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2</v>
+        <v>2.06</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>1.91</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>2.52</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="X19" t="n">
-        <v>9.800000000000001</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="Z19" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.8</v>
+        <v>16.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="AD19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP19" t="n">
         <v>40</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG19" t="n">
+      <c r="AQ19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB19" t="n">
         <v>13</v>
       </c>
-      <c r="AH19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>20</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>140</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>14</v>
-      </c>
       <c r="BC19" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BF19" t="n">
-        <v>11.5</v>
+        <v>3.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Tottenham</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cerro Porteno</t>
+          <t>Atletico Madrid</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.9</v>
+        <v>2.66</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="I20" t="n">
-        <v>1.95</v>
+        <v>2.66</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>2.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="T20" t="n">
-        <v>2.02</v>
+        <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>1.83</v>
+        <v>2.52</v>
       </c>
       <c r="V20" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="W20" t="n">
-        <v>1.22</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.2</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AA20" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AB20" t="n">
         <v>15</v>
       </c>
       <c r="AC20" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AF20" t="n">
-        <v>120</v>
+        <v>19.5</v>
       </c>
       <c r="AG20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW20" t="n">
         <v>22</v>
       </c>
-      <c r="AH20" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
         <v>18.5</v>
       </c>
-      <c r="AX20" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BB20" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BC20" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="BE20" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>UEFA Champions League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Estudiantes de Merida</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Carabobo FC</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.85</v>
+        <v>1.31</v>
       </c>
       <c r="G21" t="n">
-        <v>4.9</v>
+        <v>1.32</v>
       </c>
       <c r="H21" t="n">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>10.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="L21" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="M21" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>2.62</v>
+        <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>1.39</v>
       </c>
       <c r="R21" t="n">
-        <v>1.21</v>
+        <v>1.98</v>
       </c>
       <c r="S21" t="n">
-        <v>4.7</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.04</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.27</v>
+        <v>4.1</v>
       </c>
       <c r="X21" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="Z21" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AA21" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD21" t="n">
         <v>36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.4</v>
+        <v>36</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.3</v>
+        <v>42</v>
       </c>
       <c r="AR21" t="n">
-        <v>5.6</v>
+        <v>80</v>
       </c>
       <c r="AS21" t="n">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="AT21" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.4</v>
+        <v>15</v>
       </c>
       <c r="AV21" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.8</v>
+        <v>100</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.6</v>
+        <v>22</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.94</v>
+        <v>75</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.97</v>
+        <v>11</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.99</v>
+        <v>11.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.99</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.97</v>
+        <v>75</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.95</v>
+        <v>3.4</v>
       </c>
       <c r="BG21" t="n">
-        <v>5.5</v>
+        <v>75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie B</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SE Palmeiras</t>
+          <t>CA Vinotinto</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Deportivo Santo Domingo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.59</v>
+        <v>1.04</v>
       </c>
       <c r="G22" t="n">
-        <v>1.62</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I22" t="n">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="P22" t="n">
-        <v>2.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.88</v>
+        <v>1.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.18</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="T22" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Bull Bragantino</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="G23" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="I23" t="n">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD23" t="n">
         <v>3.6</v>
       </c>
-      <c r="K23" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="X23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>300</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>320</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>26</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>32</v>
-      </c>
       <c r="BE23" t="n">
-        <v>40</v>
+        <v>2.4</v>
       </c>
       <c r="BF23" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>30</v>
+        <v>2.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>ES Setif</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.32</v>
+        <v>1.59</v>
       </c>
       <c r="G24" t="n">
-        <v>2.36</v>
+        <v>1.68</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>7.6</v>
       </c>
       <c r="I24" t="n">
-        <v>3.65</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="P24" t="n">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.16</v>
       </c>
       <c r="S24" t="n">
-        <v>3.95</v>
+        <v>5.3</v>
       </c>
       <c r="T24" t="n">
-        <v>1.89</v>
+        <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>2.06</v>
+        <v>1.52</v>
       </c>
       <c r="V24" t="n">
-        <v>1.37</v>
+        <v>1.12</v>
       </c>
       <c r="W24" t="n">
-        <v>1.73</v>
+        <v>2.46</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Z24" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.6</v>
+        <v>5.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>9.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>38</v>
       </c>
       <c r="AE24" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG24" t="n">
         <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>18.5</v>
+        <v>40</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>540</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC24" t="n">
         <v>21</v>
       </c>
-      <c r="AO24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT24" t="n">
+      <c r="BD24" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>36</v>
-      </c>
       <c r="BE24" t="n">
-        <v>60</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BG24" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Zamora FC</t>
+          <t>Belouizdad</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Portuguesa FC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>2.84</v>
+        <v>1.66</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>7.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3.15</v>
+        <v>9</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O25" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.99</v>
+        <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>1.54</v>
+        <v>2.52</v>
       </c>
       <c r="X25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Z25" t="n">
-        <v>22</v>
+        <v>170</v>
       </c>
       <c r="AA25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AC25" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC25" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="AE25" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AI25" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="AK25" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>42</v>
+        <v>19.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU25" t="n">
         <v>8</v>
       </c>
-      <c r="AQ25" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT25" t="n">
+      <c r="AV25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX25" t="n">
         <v>7</v>
       </c>
-      <c r="AU25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AY25" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>18.5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF25" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Boyaca Chico</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.74</v>
+        <v>1.55</v>
       </c>
       <c r="G26" t="n">
-        <v>1.78</v>
+        <v>1.56</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K26" t="n">
         <v>3.95</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.08</v>
+        <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="U26" t="n">
-        <v>1.92</v>
+        <v>1.57</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="W26" t="n">
-        <v>2.28</v>
+        <v>2.78</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>18</v>
+        <v>950</v>
       </c>
       <c r="Z26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="AF26" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="AG26" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="AJ26" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="AL26" t="n">
-        <v>42</v>
+        <v>380</v>
       </c>
       <c r="AM26" t="n">
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
-        <v>38</v>
+        <v>9.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="AT26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB26" t="n">
         <v>7</v>
       </c>
-      <c r="AU26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>60</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>15</v>
-      </c>
       <c r="BC26" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="BE26" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BF26" t="n">
-        <v>11</v>
+        <v>6.2</v>
       </c>
       <c r="BG26" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Ecuadorian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Atletico MG</t>
+          <t>Manta FC</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Guayaquil City</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2.58</v>
+        <v>2.12</v>
       </c>
       <c r="H27" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.45</v>
       </c>
-      <c r="J27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T27" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U27" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="W27" t="n">
-        <v>1.63</v>
+        <v>1.9</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="AA27" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="AB27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>7.4</v>
       </c>
-      <c r="AD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG27" t="n">
+      <c r="BA27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF27" t="n">
         <v>12</v>
       </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL27" t="n">
+      <c r="BG27" t="n">
         <v>55</v>
       </c>
-      <c r="AM27" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>19</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>27</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Libertad</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Cerro Porteno</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.22</v>
+        <v>4.9</v>
       </c>
       <c r="G28" t="n">
-        <v>2.42</v>
+        <v>5.6</v>
       </c>
       <c r="H28" t="n">
-        <v>3.65</v>
+        <v>1.85</v>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>1.95</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="P28" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V28" t="n">
-        <v>1.33</v>
+        <v>2.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="X28" t="n">
         <v>11</v>
       </c>
       <c r="Y28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>120</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>190</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT28" t="n">
         <v>13</v>
       </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ28" t="n">
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AR28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AW28" t="n">
-        <v>4.8</v>
+        <v>18.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA28" t="n">
         <v>10</v>
       </c>
-      <c r="AZ28" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BB28" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.7</v>
+        <v>11</v>
       </c>
       <c r="BE28" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Venezuelan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,96 +5981,96 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Estudiantes de Merida</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Carabobo FC</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.81</v>
+        <v>3.85</v>
       </c>
       <c r="G29" t="n">
-        <v>1.99</v>
+        <v>4.7</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.02</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>1.84</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF29" t="n">
         <v>1000</v>
@@ -6103,69 +6103,69 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Venezuelan Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Metropolitanos</t>
+          <t>SE Palmeiras</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monagas</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="G30" t="n">
-        <v>2.28</v>
+        <v>1.61</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="K30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N30" t="n">
         <v>4.1</v>
       </c>
-      <c r="L30" t="n">
+      <c r="O30" t="n">
         <v>1.3</v>
       </c>
-      <c r="M30" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N30" t="n">
-        <v>4</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.26</v>
-      </c>
       <c r="P30" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="R30" t="n">
         <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>2.92</v>
+        <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.64</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="V30" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
         <v>9</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AO30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC30" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>85</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>18.5</v>
-      </c>
       <c r="BD30" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.46</v>
+        <v>65</v>
       </c>
       <c r="BF30" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG30" t="n">
-        <v>4.1</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -6369,184 +6369,184 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Red Bull Bragantino</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T31" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="W31" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="X31" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB31" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL31" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>15.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AP31" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
         <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="AS31" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AT31" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF31" t="n">
         <v>13</v>
       </c>
-      <c r="AW31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD31" t="n">
+      <c r="BG31" t="n">
         <v>30</v>
       </c>
-      <c r="BE31" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>15</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>28</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
@@ -6563,378 +6563,2900 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3.2</v>
+        <v>2.32</v>
       </c>
       <c r="G32" t="n">
-        <v>3.35</v>
+        <v>2.36</v>
       </c>
       <c r="H32" t="n">
-        <v>2.46</v>
+        <v>3.55</v>
       </c>
       <c r="I32" t="n">
-        <v>2.56</v>
+        <v>3.65</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.37</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.64</v>
-      </c>
       <c r="W32" t="n">
-        <v>1.42</v>
+        <v>1.73</v>
       </c>
       <c r="X32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y32" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y32" t="n">
-        <v>10</v>
-      </c>
       <c r="Z32" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AA32" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="AB32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG32" t="n">
         <v>12</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>14.5</v>
       </c>
       <c r="AH32" t="n">
         <v>18.5</v>
       </c>
       <c r="AI32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL32" t="n">
         <v>44</v>
       </c>
-      <c r="AJ32" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>55</v>
-      </c>
       <c r="AM32" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AO32" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AP32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="AS32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT32" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
       </c>
       <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW32" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB32" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="BC32" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="BD32" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="BE32" t="n">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="BF32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG32" t="n">
         <v>27</v>
       </c>
-      <c r="BG32" t="n">
-        <v>21</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-17 22:55:16</t>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Zamora FC</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Portuguesa FC</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>500</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Atletico MG</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Sao Paulo</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>36</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>27</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="H35" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>6</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="X35" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>60</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:15:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G36" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I36" t="n">
+        <v>110</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>7</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>950</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I37" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N37" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="X37" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>190</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Nacional (Par)</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H38" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X38" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Guarani (Par)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I39" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Venezuelan Primera Division</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Monagas</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="H40" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P40" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S40" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W40" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="X40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>260</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Libertad FC</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Barcelona (ECU)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>36</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>34</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>11</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N43" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>38</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>29</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>15</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>28</v>
+      </c>
+      <c r="BH43" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Atletico Bucaramanga</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H44" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R44" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X44" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>260</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>450</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>29</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BH44" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I45" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K45" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S45" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH45" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Mexican Liga MX</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>23:07:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Guadalajara</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Leon</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F46" t="n">
         <v>1.4</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G46" t="n">
         <v>1.43</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I46" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J46" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P46" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X46" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>340</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA46" t="n">
         <v>8.6</v>
       </c>
-      <c r="I33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="J33" t="n">
+      <c r="BB46" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF46" t="n">
         <v>5.1</v>
       </c>
-      <c r="K33" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>36</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>340</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>130</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT33" t="n">
+      <c r="BG46" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-17 22:55:16</t>
+      <c r="BH46" t="inlineStr">
+        <is>
+          <t>2026-03-18 01:04:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-18.xlsx
@@ -757,85 +757,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="R2" t="n">
         <v>1.23</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>110</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AF2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12.5</v>
@@ -844,13 +844,13 @@
         <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AJ2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
@@ -859,10 +859,10 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="AP2" t="n">
         <v>8.6</v>
@@ -874,10 +874,10 @@
         <v>19.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU2" t="n">
         <v>6.4</v>
@@ -886,41 +886,41 @@
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA2" t="n">
-        <v>27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
         <v>15</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -957,16 +957,16 @@
         <v>2.14</v>
       </c>
       <c r="H3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I3" t="n">
         <v>4.4</v>
       </c>
-      <c r="I3" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.52</v>
@@ -984,34 +984,34 @@
         <v>1.68</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X3" t="n">
         <v>10.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA3" t="n">
         <v>100</v>
@@ -1020,13 +1020,13 @@
         <v>7.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="AF3" t="n">
         <v>11.5</v>
@@ -1050,7 +1050,7 @@
         <v>50</v>
       </c>
       <c r="AM3" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
         <v>24</v>
@@ -1068,19 +1068,19 @@
         <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT3" t="n">
         <v>6.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
       </c>
       <c r="AW3" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AX3" t="n">
         <v>10.5</v>
@@ -1092,29 +1092,29 @@
         <v>18.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="BB3" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="BE3" t="n">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="BF3" t="n">
         <v>20</v>
       </c>
       <c r="BG3" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1145,64 +1145,64 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="G4" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4" t="n">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
         <v>1.16</v>
       </c>
       <c r="S4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T4" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="U4" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
         <v>55</v>
@@ -1211,37 +1211,37 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AC4" t="n">
         <v>8.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE4" t="n">
         <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AG4" t="n">
         <v>12</v>
       </c>
       <c r="AH4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
       </c>
       <c r="AL4" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ4" t="n">
         <v>11.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU4" t="n">
         <v>6.8</v>
       </c>
       <c r="AV4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BC4" t="n">
         <v>13</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE4" t="n">
-        <v>9.4</v>
+        <v>28</v>
       </c>
       <c r="BF4" t="n">
         <v>20</v>
       </c>
       <c r="BG4" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1357,22 +1357,22 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
         <v>1.45</v>
@@ -1384,7 +1384,7 @@
         <v>1.98</v>
       </c>
       <c r="U5" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V5" t="n">
         <v>1.16</v>
@@ -1402,13 +1402,13 @@
         <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>25</v>
@@ -1417,7 +1417,7 @@
         <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AG5" t="n">
         <v>9.800000000000001</v>
@@ -1435,19 +1435,19 @@
         <v>15.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM5" t="n">
         <v>130</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AQ5" t="n">
         <v>21</v>
@@ -1456,22 +1456,22 @@
         <v>50</v>
       </c>
       <c r="AS5" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV5" t="n">
         <v>23</v>
       </c>
       <c r="AW5" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5" t="n">
         <v>9.4</v>
@@ -1480,7 +1480,7 @@
         <v>21</v>
       </c>
       <c r="BA5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1495,14 +1495,14 @@
         <v>75</v>
       </c>
       <c r="BF5" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG5" t="n">
         <v>90</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1533,94 +1533,94 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.24</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.02</v>
+        <v>1.89</v>
       </c>
       <c r="R6" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>1.35</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>1.71</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1638,65 +1638,65 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>1.28</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.28</v>
+        <v>1.66</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>1.28</v>
+        <v>2.48</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Z7" t="n">
         <v>1000</v>
@@ -1793,104 +1793,104 @@
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H8" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O8" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P8" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="S8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
         <v>1.54</v>
       </c>
       <c r="V8" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -1981,19 +1981,19 @@
         <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c r="AB8" t="n">
         <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE8" t="n">
         <v>1000</v>
@@ -2008,7 +2008,7 @@
         <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ8" t="n">
         <v>1000</v>
@@ -2032,16 +2032,16 @@
         <v>5.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AT8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU8" t="n">
         <v>6.2</v>
@@ -2050,19 +2050,19 @@
         <v>7</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX8" t="n">
         <v>4.2</v>
       </c>
       <c r="AY8" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="BB8" t="n">
         <v>4.2</v>
@@ -2074,17 +2074,17 @@
         <v>4.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.42</v>
+        <v>2.86</v>
       </c>
       <c r="BF8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2115,58 +2115,58 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.02</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K9" t="n">
-        <v>950</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
       </c>
       <c r="N9" t="n">
         <v>1.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>2.42</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>1000</v>
@@ -2205,7 +2205,7 @@
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK9" t="n">
         <v>1000</v>
@@ -2217,68 +2217,68 @@
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2309,52 +2309,52 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G10" t="n">
         <v>1.58</v>
       </c>
       <c r="H10" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I10" t="n">
         <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K10" t="n">
         <v>4.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="T10" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V10" t="n">
         <v>1.16</v>
@@ -2363,19 +2363,19 @@
         <v>2.74</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
         <v>26</v>
       </c>
       <c r="Z10" t="n">
-        <v>420</v>
+        <v>65</v>
       </c>
       <c r="AA10" t="n">
-        <v>230</v>
+        <v>700</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC10" t="n">
         <v>10.5</v>
@@ -2387,16 +2387,16 @@
         <v>480</v>
       </c>
       <c r="AF10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
         <v>23</v>
       </c>
       <c r="AI10" t="n">
-        <v>390</v>
+        <v>190</v>
       </c>
       <c r="AJ10" t="n">
         <v>15.5</v>
@@ -2405,13 +2405,13 @@
         <v>16.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="AM10" t="n">
-        <v>380</v>
+        <v>700</v>
       </c>
       <c r="AN10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
@@ -2420,7 +2420,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
         <v>23</v>
@@ -2429,7 +2429,7 @@
         <v>10.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU10" t="n">
         <v>9.4</v>
@@ -2438,7 +2438,7 @@
         <v>21</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
         <v>8.800000000000001</v>
@@ -2447,32 +2447,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
         <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC10" t="n">
         <v>13.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
         <v>30</v>
       </c>
       <c r="BF10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>10</v>
+        <v>13.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="G11" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="H11" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="I11" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="J11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K11" t="n">
         <v>4.3</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -2530,103 +2530,103 @@
         <v>4.6</v>
       </c>
       <c r="O11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U11" t="n">
         <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="W11" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD11" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AE11" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AF11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>140</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR11" t="n">
+      <c r="AT11" t="n">
         <v>10</v>
       </c>
-      <c r="AS11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>18</v>
-      </c>
       <c r="AU11" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AV11" t="n">
         <v>9.199999999999999</v>
@@ -2635,38 +2635,38 @@
         <v>15</v>
       </c>
       <c r="AX11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AY11" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>17</v>
       </c>
       <c r="BA11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="BD11" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BE11" t="n">
         <v>26</v>
       </c>
       <c r="BF11" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="BG11" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
         <v>1.64</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
         <v>4.9</v>
@@ -2727,19 +2727,19 @@
         <v>1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S12" t="n">
         <v>1.97</v>
       </c>
-      <c r="S12" t="n">
-        <v>2</v>
-      </c>
       <c r="T12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
         <v>2.92</v>
@@ -2760,16 +2760,16 @@
         <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC12" t="n">
         <v>12.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE12" t="n">
         <v>50</v>
@@ -2781,16 +2781,16 @@
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ12" t="n">
         <v>18</v>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL12" t="n">
         <v>21</v>
@@ -2799,10 +2799,10 @@
         <v>48</v>
       </c>
       <c r="AN12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP12" t="n">
         <v>36</v>
@@ -2811,34 +2811,34 @@
         <v>32</v>
       </c>
       <c r="AR12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS12" t="n">
         <v>110</v>
       </c>
       <c r="AT12" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AU12" t="n">
         <v>12</v>
       </c>
       <c r="AV12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AY12" t="n">
         <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BB12" t="n">
         <v>17</v>
@@ -2850,17 +2850,17 @@
         <v>19.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -2891,43 +2891,43 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G13" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I13" t="n">
         <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M13" t="n">
         <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.21</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="S13" t="n">
         <v>2.62</v>
@@ -2936,31 +2936,31 @@
         <v>1.8</v>
       </c>
       <c r="U13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V13" t="n">
         <v>1.15</v>
       </c>
       <c r="W13" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB13" t="n">
         <v>11</v>
       </c>
       <c r="AC13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
         <v>48</v>
@@ -2969,7 +2969,7 @@
         <v>480</v>
       </c>
       <c r="AF13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10</v>
@@ -2981,10 +2981,10 @@
         <v>190</v>
       </c>
       <c r="AJ13" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL13" t="n">
         <v>30</v>
@@ -2993,7 +2993,7 @@
         <v>320</v>
       </c>
       <c r="AN13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,34 +3005,34 @@
         <v>23</v>
       </c>
       <c r="AR13" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AT13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV13" t="n">
         <v>23</v>
       </c>
       <c r="AW13" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX13" t="n">
         <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
         <v>12</v>
@@ -3047,14 +3047,14 @@
         <v>48</v>
       </c>
       <c r="BF13" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3085,25 +3085,25 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G14" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K14" t="n">
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
@@ -3112,28 +3112,28 @@
         <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
         <v>2.28</v>
@@ -3151,7 +3151,7 @@
         <v>900</v>
       </c>
       <c r="AB14" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC14" t="n">
         <v>8.6</v>
@@ -3163,7 +3163,7 @@
         <v>700</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
         <v>11</v>
@@ -3187,7 +3187,7 @@
         <v>700</v>
       </c>
       <c r="AN14" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3196,25 +3196,25 @@
         <v>9</v>
       </c>
       <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS14" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>10</v>
       </c>
       <c r="AT14" t="n">
         <v>5.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
         <v>7.8</v>
@@ -3223,32 +3223,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BC14" t="n">
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF14" t="n">
         <v>13</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.26</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I15" t="n">
         <v>3.85</v>
@@ -3297,40 +3297,40 @@
         <v>3.55</v>
       </c>
       <c r="L15" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="M15" t="n">
         <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T15" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V15" t="n">
         <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="X15" t="n">
         <v>13.5</v>
@@ -3342,7 +3342,7 @@
         <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
         <v>9.800000000000001</v>
@@ -3354,7 +3354,7 @@
         <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>44</v>
       </c>
       <c r="AF15" t="n">
         <v>14</v>
@@ -3369,22 +3369,22 @@
         <v>55</v>
       </c>
       <c r="AJ15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15" t="n">
         <v>85</v>
       </c>
       <c r="AM15" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN15" t="n">
         <v>17.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3393,22 +3393,22 @@
         <v>13</v>
       </c>
       <c r="AR15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS15" t="n">
         <v>23</v>
       </c>
-      <c r="AS15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU15" t="n">
         <v>7</v>
       </c>
       <c r="AV15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
         <v>12.5</v>
@@ -3420,7 +3420,7 @@
         <v>15</v>
       </c>
       <c r="BA15" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BB15" t="n">
         <v>25</v>
@@ -3432,17 +3432,17 @@
         <v>32</v>
       </c>
       <c r="BE15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF15" t="n">
         <v>15.5</v>
       </c>
-      <c r="BF15" t="n">
-        <v>15</v>
-      </c>
       <c r="BG15" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="J16" t="n">
         <v>2.94</v>
@@ -3491,46 +3491,46 @@
         <v>2.98</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.34</v>
+        <v>2.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X16" t="n">
-        <v>17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z16" t="n">
         <v>20</v>
@@ -3539,13 +3539,13 @@
         <v>55</v>
       </c>
       <c r="AB16" t="n">
-        <v>19</v>
+        <v>9.4</v>
       </c>
       <c r="AC16" t="n">
         <v>6.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>44</v>
@@ -3557,7 +3557,7 @@
         <v>13.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI16" t="n">
         <v>70</v>
@@ -3578,65 +3578,65 @@
         <v>44</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP16" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AY16" t="n">
         <v>12</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="AZ16" t="n">
         <v>16</v>
       </c>
-      <c r="AX16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BA16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB16" t="n">
         <v>10</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>10.5</v>
       </c>
       <c r="BC16" t="n">
         <v>16</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
         <v>29</v>
       </c>
       <c r="BF16" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>7.2</v>
+        <v>38</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3667,16 +3667,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G17" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>2.96</v>
@@ -3685,28 +3685,28 @@
         <v>3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T17" t="n">
         <v>1.95</v>
@@ -3715,13 +3715,13 @@
         <v>2.02</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="X17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y17" t="n">
         <v>11</v>
@@ -3751,10 +3751,10 @@
         <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="n">
         <v>38</v>
@@ -3763,7 +3763,7 @@
         <v>36</v>
       </c>
       <c r="AL17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM17" t="n">
         <v>450</v>
@@ -3775,16 +3775,16 @@
         <v>55</v>
       </c>
       <c r="AP17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
         <v>19</v>
       </c>
       <c r="AS17" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AT17" t="n">
         <v>8.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AX17" t="n">
         <v>14</v>
@@ -3805,32 +3805,32 @@
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
       </c>
       <c r="BC17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE17" t="n">
         <v>28</v>
       </c>
       <c r="BF17" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="BG17" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -3861,58 +3861,58 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="I18" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="J18" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="L18" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
       </c>
       <c r="N18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.5</v>
       </c>
-      <c r="O18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.65</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="V18" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="W18" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
         <v>970</v>
@@ -3924,7 +3924,7 @@
         <v>40</v>
       </c>
       <c r="AA18" t="n">
-        <v>900</v>
+        <v>50</v>
       </c>
       <c r="AB18" t="n">
         <v>950</v>
@@ -3936,7 +3936,7 @@
         <v>36</v>
       </c>
       <c r="AE18" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AF18" t="n">
         <v>500</v>
@@ -3945,7 +3945,7 @@
         <v>950</v>
       </c>
       <c r="AH18" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI18" t="n">
         <v>500</v>
@@ -3966,65 +3966,65 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.4</v>
+        <v>3.2</v>
       </c>
       <c r="AQ18" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="AR18" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>2.64</v>
       </c>
       <c r="AT18" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AU18" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="AV18" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.9</v>
+        <v>3.55</v>
       </c>
       <c r="AX18" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY18" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6.2</v>
+        <v>2.78</v>
       </c>
       <c r="BA18" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="BB18" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>3.35</v>
+        <v>2.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>2.44</v>
+        <v>4.2</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.45</v>
+        <v>2.92</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4055,31 +4055,31 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J19" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="K19" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="L19" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O19" t="n">
         <v>1.11</v>
@@ -4088,103 +4088,103 @@
         <v>3.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R19" t="n">
         <v>2.06</v>
       </c>
       <c r="S19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U19" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="V19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W19" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X19" t="n">
         <v>44</v>
       </c>
       <c r="Y19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Z19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA19" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AB19" t="n">
         <v>16.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AK19" t="n">
         <v>13</v>
       </c>
       <c r="AL19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM19" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN19" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AO19" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP19" t="n">
         <v>40</v>
       </c>
       <c r="AQ19" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AR19" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AS19" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AT19" t="n">
         <v>15.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AV19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AW19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AX19" t="n">
         <v>12</v>
@@ -4193,13 +4193,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
         <v>50</v>
       </c>
       <c r="BB19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC19" t="n">
         <v>12</v>
@@ -4208,17 +4208,17 @@
         <v>21</v>
       </c>
       <c r="BE19" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4249,43 +4249,43 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H20" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="I20" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="O20" t="n">
         <v>1.23</v>
       </c>
       <c r="P20" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="S20" t="n">
         <v>2.68</v>
@@ -4294,52 +4294,52 @@
         <v>1.61</v>
       </c>
       <c r="U20" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="V20" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
         <v>38</v>
       </c>
       <c r="AB20" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AF20" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
         <v>24</v>
@@ -4351,25 +4351,25 @@
         <v>60</v>
       </c>
       <c r="AN20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO20" t="n">
         <v>17.5</v>
       </c>
-      <c r="AO20" t="n">
-        <v>16</v>
-      </c>
       <c r="AP20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR20" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ20" t="n">
+      <c r="AS20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT20" t="n">
         <v>13.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>14</v>
       </c>
       <c r="AU20" t="n">
         <v>8.800000000000001</v>
@@ -4378,19 +4378,19 @@
         <v>12</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX20" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY20" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>32</v>
@@ -4399,20 +4399,20 @@
         <v>22</v>
       </c>
       <c r="BD20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE20" t="n">
         <v>55</v>
       </c>
       <c r="BF20" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4443,79 +4443,79 @@
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G21" t="n">
         <v>1.31</v>
       </c>
-      <c r="G21" t="n">
-        <v>1.32</v>
-      </c>
       <c r="H21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="I21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P21" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="R21" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="S21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V21" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="Y21" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="Z21" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AA21" t="n">
-        <v>300</v>
+        <v>340</v>
       </c>
       <c r="AB21" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AD21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AE21" t="n">
         <v>120</v>
@@ -4524,67 +4524,67 @@
         <v>11</v>
       </c>
       <c r="AG21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK21" t="n">
         <v>12</v>
       </c>
       <c r="AL21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AM21" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AN21" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="AO21" t="n">
         <v>100</v>
       </c>
       <c r="AP21" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AV21" t="n">
         <v>36</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>15</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>30</v>
       </c>
       <c r="AW21" t="n">
         <v>100</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ21" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4593,20 +4593,20 @@
         <v>11.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE21" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF21" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BG21" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -4831,31 +4831,31 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="G23" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="O23" t="n">
         <v>1.47</v>
@@ -4864,25 +4864,25 @@
         <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="R23" t="n">
         <v>1.22</v>
       </c>
       <c r="S23" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W23" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4897,10 +4897,10 @@
         <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AC23" t="n">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AD23" t="n">
         <v>1000</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AG23" t="n">
         <v>21</v>
@@ -4921,7 +4921,7 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK23" t="n">
         <v>85</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
         <v>7.6</v>
       </c>
       <c r="AR23" t="n">
-        <v>9.6</v>
+        <v>4.2</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.42</v>
+        <v>3.35</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AY23" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ23" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="BB23" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC23" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="BF23" t="n">
         <v>4.4</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5025,52 +5025,52 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G24" t="n">
         <v>1.68</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L24" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="M24" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N24" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.58</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="R24" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S24" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="T24" t="n">
         <v>2.56</v>
       </c>
       <c r="U24" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="V24" t="n">
         <v>1.12</v>
@@ -5082,7 +5082,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5094,10 +5094,10 @@
         <v>5.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
@@ -5109,7 +5109,7 @@
         <v>12</v>
       </c>
       <c r="AH24" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5118,7 +5118,7 @@
         <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL24" t="n">
         <v>540</v>
@@ -5139,13 +5139,13 @@
         <v>14.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AT24" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU24" t="n">
         <v>7.8</v>
@@ -5154,7 +5154,7 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AX24" t="n">
         <v>6.8</v>
@@ -5163,10 +5163,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="BA24" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB24" t="n">
         <v>13.5</v>
@@ -5175,20 +5175,20 @@
         <v>21</v>
       </c>
       <c r="BD24" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE24" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF24" t="n">
         <v>14</v>
       </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5237,34 +5237,34 @@
         <v>4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
       </c>
       <c r="N25" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="O25" t="n">
         <v>1.5</v>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="R25" t="n">
         <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
         <v>2.4</v>
       </c>
       <c r="U25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V25" t="n">
         <v>1.13</v>
@@ -5297,7 +5297,7 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG25" t="n">
         <v>13</v>
@@ -5327,16 +5327,16 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ25" t="n">
         <v>15.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT25" t="n">
         <v>5.1</v>
@@ -5348,7 +5348,7 @@
         <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX25" t="n">
         <v>7</v>
@@ -5360,7 +5360,7 @@
         <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB25" t="n">
         <v>14</v>
@@ -5369,10 +5369,10 @@
         <v>20</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF25" t="n">
         <v>11.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5413,64 +5413,64 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G26" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I26" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K26" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
         <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="Q26" t="n">
         <v>2.44</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T26" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U26" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="X26" t="n">
         <v>16</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="Z26" t="n">
         <v>1000</v>
@@ -5488,10 +5488,10 @@
         <v>950</v>
       </c>
       <c r="AE26" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AG26" t="n">
         <v>19</v>
@@ -5500,13 +5500,13 @@
         <v>950</v>
       </c>
       <c r="AI26" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AJ26" t="n">
         <v>44</v>
       </c>
       <c r="AK26" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL26" t="n">
         <v>380</v>
@@ -5524,25 +5524,25 @@
         <v>6.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU26" t="n">
         <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX26" t="n">
         <v>6.4</v>
@@ -5554,7 +5554,7 @@
         <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB26" t="n">
         <v>7</v>
@@ -5563,7 +5563,7 @@
         <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE26" t="n">
         <v>28</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5607,82 +5607,82 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="W27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA27" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB27" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AF27" t="n">
         <v>12</v>
@@ -5691,86 +5691,86 @@
         <v>11.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="AJ27" t="n">
         <v>26</v>
       </c>
       <c r="AK27" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="AL27" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AS27" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="AT27" t="n">
         <v>5.1</v>
       </c>
       <c r="AU27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV27" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AX27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ27" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BA27" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC27" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BD27" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG27" t="n">
         <v>55</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5801,25 +5801,25 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="I28" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
@@ -5828,10 +5828,10 @@
         <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P28" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q28" t="n">
         <v>2.4</v>
@@ -5840,16 +5840,16 @@
         <v>1.25</v>
       </c>
       <c r="S28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W28" t="n">
         <v>1.22</v>
@@ -5861,10 +5861,10 @@
         <v>7.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB28" t="n">
         <v>15</v>
@@ -5882,7 +5882,7 @@
         <v>120</v>
       </c>
       <c r="AG28" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="AH28" t="n">
         <v>38</v>
@@ -5906,7 +5906,7 @@
         <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>36</v>
+        <v>18.5</v>
       </c>
       <c r="AP28" t="n">
         <v>9.6</v>
@@ -5918,7 +5918,7 @@
         <v>9.4</v>
       </c>
       <c r="AS28" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT28" t="n">
         <v>13</v>
@@ -5933,7 +5933,7 @@
         <v>18.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY28" t="n">
         <v>10.5</v>
@@ -5942,29 +5942,29 @@
         <v>18.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G29" t="n">
         <v>4.7</v>
@@ -6013,34 +6013,34 @@
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T29" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V29" t="n">
         <v>1.84</v>
@@ -6052,7 +6052,7 @@
         <v>17</v>
       </c>
       <c r="Y29" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Z29" t="n">
         <v>970</v>
@@ -6106,7 +6106,7 @@
         <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AR29" t="n">
         <v>5.6</v>
@@ -6124,10 +6124,10 @@
         <v>7.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AX29" t="n">
-        <v>3.95</v>
+        <v>13</v>
       </c>
       <c r="AY29" t="n">
         <v>6.4</v>
@@ -6136,29 +6136,29 @@
         <v>7</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="BB29" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="BD29" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.1</v>
+        <v>2.42</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
       <c r="BG29" t="n">
         <v>5.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -6189,55 +6189,55 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="G30" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="H30" t="n">
         <v>6.4</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K30" t="n">
         <v>4.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
         <v>1.06</v>
       </c>
       <c r="N30" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O30" t="n">
         <v>1.3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S30" t="n">
         <v>3.25</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
         <v>2.6</v>
@@ -6252,19 +6252,19 @@
         <v>55</v>
       </c>
       <c r="AA30" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB30" t="n">
         <v>8.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE30" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF30" t="n">
         <v>9.4</v>
@@ -6276,7 +6276,7 @@
         <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ30" t="n">
         <v>15</v>
@@ -6288,22 +6288,22 @@
         <v>36</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO30" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AP30" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS30" t="n">
         <v>46</v>
@@ -6315,7 +6315,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>36</v>
@@ -6327,16 +6327,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
         <v>13.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>30</v>
@@ -6345,14 +6345,14 @@
         <v>65</v>
       </c>
       <c r="BF30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG30" t="n">
         <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -6383,46 +6383,46 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="G31" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M31" t="n">
         <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
         <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
         <v>1.87</v>
@@ -6431,19 +6431,19 @@
         <v>2.06</v>
       </c>
       <c r="V31" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W31" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA31" t="n">
         <v>300</v>
@@ -6452,55 +6452,55 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="AF31" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI31" t="n">
         <v>70</v>
       </c>
       <c r="AJ31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM31" t="n">
         <v>320</v>
       </c>
       <c r="AN31" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AO31" t="n">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AP31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
         <v>26</v>
       </c>
       <c r="AS31" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT31" t="n">
         <v>8.199999999999999</v>
@@ -6515,10 +6515,10 @@
         <v>48</v>
       </c>
       <c r="AX31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
         <v>17</v>
@@ -6527,26 +6527,26 @@
         <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE31" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG31" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I32" t="n">
         <v>3.55</v>
       </c>
-      <c r="I32" t="n">
-        <v>3.65</v>
-      </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K32" t="n">
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6604,31 +6604,31 @@
         <v>3.45</v>
       </c>
       <c r="O32" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R32" t="n">
         <v>1.3</v>
       </c>
       <c r="S32" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T32" t="n">
         <v>1.89</v>
       </c>
       <c r="U32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V32" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="W32" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X32" t="n">
         <v>11.5</v>
@@ -6643,7 +6643,7 @@
         <v>70</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
@@ -6655,10 +6655,10 @@
         <v>46</v>
       </c>
       <c r="AF32" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
         <v>18.5</v>
@@ -6670,16 +6670,16 @@
         <v>30</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL32" t="n">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="AM32" t="n">
         <v>120</v>
       </c>
       <c r="AN32" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AO32" t="n">
         <v>48</v>
@@ -6694,10 +6694,10 @@
         <v>21</v>
       </c>
       <c r="AS32" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AT32" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
@@ -6706,10 +6706,10 @@
         <v>13.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY32" t="n">
         <v>10.5</v>
@@ -6718,13 +6718,13 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD32" t="n">
         <v>26</v>
@@ -6736,11 +6736,11 @@
         <v>19.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="G33" t="n">
         <v>2.8</v>
@@ -6795,19 +6795,19 @@
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O33" t="n">
         <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q33" t="n">
         <v>2.48</v>
       </c>
       <c r="R33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
         <v>4.8</v>
@@ -6816,7 +6816,7 @@
         <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V33" t="n">
         <v>1.47</v>
@@ -6834,7 +6834,7 @@
         <v>22</v>
       </c>
       <c r="AA33" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AB33" t="n">
         <v>9.199999999999999</v>
@@ -6846,7 +6846,7 @@
         <v>15</v>
       </c>
       <c r="AE33" t="n">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="AF33" t="n">
         <v>17</v>
@@ -6870,13 +6870,13 @@
         <v>65</v>
       </c>
       <c r="AM33" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN33" t="n">
         <v>42</v>
       </c>
       <c r="AO33" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP33" t="n">
         <v>8</v>
@@ -6888,19 +6888,19 @@
         <v>17.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU33" t="n">
         <v>6.2</v>
       </c>
       <c r="AV33" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6912,29 +6912,29 @@
         <v>18.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC33" t="n">
         <v>7.4</v>
       </c>
-      <c r="BC33" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -6971,13 +6971,13 @@
         <v>2.58</v>
       </c>
       <c r="H34" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
         <v>3.45</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K34" t="n">
         <v>3.3</v>
@@ -6989,28 +6989,28 @@
         <v>1.1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O34" t="n">
         <v>1.44</v>
       </c>
       <c r="P34" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R34" t="n">
         <v>1.26</v>
       </c>
       <c r="S34" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T34" t="n">
         <v>1.93</v>
       </c>
       <c r="U34" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V34" t="n">
         <v>1.41</v>
@@ -7031,7 +7031,7 @@
         <v>150</v>
       </c>
       <c r="AB34" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC34" t="n">
         <v>7.4</v>
@@ -7040,7 +7040,7 @@
         <v>14.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF34" t="n">
         <v>15.5</v>
@@ -7049,7 +7049,7 @@
         <v>12</v>
       </c>
       <c r="AH34" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI34" t="n">
         <v>65</v>
@@ -7058,7 +7058,7 @@
         <v>38</v>
       </c>
       <c r="AK34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL34" t="n">
         <v>55</v>
@@ -7076,22 +7076,22 @@
         <v>10</v>
       </c>
       <c r="AQ34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR34" t="n">
         <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT34" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW34" t="n">
         <v>36</v>
@@ -7100,7 +7100,7 @@
         <v>13</v>
       </c>
       <c r="AY34" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
         <v>17</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -7159,19 +7159,19 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="G35" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
@@ -7183,7 +7183,7 @@
         <v>1.08</v>
       </c>
       <c r="N35" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O35" t="n">
         <v>1.37</v>
@@ -7192,70 +7192,70 @@
         <v>1.89</v>
       </c>
       <c r="Q35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T35" t="n">
         <v>2.08</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2</v>
-      </c>
       <c r="U35" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="V35" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W35" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="X35" t="n">
         <v>13.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z35" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AA35" t="n">
         <v>700</v>
       </c>
       <c r="AB35" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC35" t="n">
         <v>9</v>
       </c>
       <c r="AD35" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AE35" t="n">
         <v>480</v>
       </c>
       <c r="AF35" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AG35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI35" t="n">
-        <v>240</v>
+        <v>450</v>
       </c>
       <c r="AJ35" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL35" t="n">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="AM35" t="n">
         <v>580</v>
@@ -7270,7 +7270,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR35" t="n">
         <v>38</v>
@@ -7279,50 +7279,50 @@
         <v>44</v>
       </c>
       <c r="AT35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU35" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW35" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AX35" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="BB35" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BC35" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD35" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BE35" t="n">
         <v>44</v>
       </c>
       <c r="BF35" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -7547,58 +7547,58 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="G37" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="H37" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I37" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="J37" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="K37" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M37" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
-        <v>2.82</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="P37" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.44</v>
+        <v>2.18</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S37" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="T37" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="U37" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="V37" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W37" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="X37" t="n">
         <v>90</v>
@@ -7613,10 +7613,10 @@
         <v>700</v>
       </c>
       <c r="AB37" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AC37" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AD37" t="n">
         <v>950</v>
@@ -7625,7 +7625,7 @@
         <v>700</v>
       </c>
       <c r="AF37" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AG37" t="n">
         <v>36</v>
@@ -7658,59 +7658,59 @@
         <v>6.8</v>
       </c>
       <c r="AQ37" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR37" t="n">
-        <v>2.14</v>
+        <v>36</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="AT37" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="AU37" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC37" t="n">
         <v>7.6</v>
       </c>
-      <c r="AV37" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.84</v>
-      </c>
       <c r="BD37" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="BE37" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="BF37" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.95</v>
+        <v>4.2</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -7741,76 +7741,76 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G38" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H38" t="n">
         <v>3.65</v>
       </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K38" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="M38" t="n">
         <v>1.11</v>
       </c>
       <c r="N38" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="O38" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P38" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="R38" t="n">
         <v>1.21</v>
       </c>
       <c r="S38" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA38" t="n">
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC38" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
@@ -7819,13 +7819,13 @@
         <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI38" t="n">
         <v>1000</v>
@@ -7855,10 +7855,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR38" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="AT38" t="n">
         <v>6.6</v>
@@ -7867,44 +7867,44 @@
         <v>6.4</v>
       </c>
       <c r="AV38" t="n">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY38" t="n">
         <v>10</v>
       </c>
       <c r="AZ38" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB38" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BC38" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD38" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG38" t="n">
-        <v>5.7</v>
+        <v>7.8</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -7938,76 +7938,76 @@
         <v>1.88</v>
       </c>
       <c r="G39" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H39" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J39" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K39" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L39" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M39" t="n">
         <v>1.08</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P39" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S39" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T39" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="U39" t="n">
-        <v>1.11</v>
+        <v>1.95</v>
       </c>
       <c r="V39" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X39" t="n">
         <v>15</v>
       </c>
       <c r="Y39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z39" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA39" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB39" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC39" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AE39" t="n">
         <v>1000</v>
@@ -8016,10 +8016,10 @@
         <v>13</v>
       </c>
       <c r="AG39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
@@ -8028,16 +8028,16 @@
         <v>25</v>
       </c>
       <c r="AK39" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL39" t="n">
         <v>1000</v>
       </c>
       <c r="AM39" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN39" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO39" t="n">
         <v>1000</v>
@@ -8046,59 +8046,59 @@
         <v>11</v>
       </c>
       <c r="AQ39" t="n">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="AR39" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS39" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AT39" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU39" t="n">
-        <v>3.25</v>
+        <v>7.2</v>
       </c>
       <c r="AV39" t="n">
-        <v>3.8</v>
+        <v>16.5</v>
       </c>
       <c r="AW39" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX39" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY39" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3.85</v>
+        <v>17</v>
       </c>
       <c r="BA39" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BB39" t="n">
-        <v>3.85</v>
+        <v>18</v>
       </c>
       <c r="BC39" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="BD39" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BF39" t="n">
         <v>11.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>4.3</v>
+        <v>55</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -8129,170 +8129,170 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="G40" t="n">
-        <v>2.28</v>
+        <v>1.88</v>
       </c>
       <c r="H40" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="I40" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="J40" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K40" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="L40" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M40" t="n">
         <v>1.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O40" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P40" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="R40" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S40" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="T40" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="U40" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="V40" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="W40" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="X40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK40" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="AL40" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV40" t="n">
         <v>16</v>
       </c>
-      <c r="Z40" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>260</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AW40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX40" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AZ40" t="n">
         <v>13.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB40" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BC40" t="n">
-        <v>18.5</v>
+        <v>14.5</v>
       </c>
       <c r="BD40" t="n">
-        <v>16</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE40" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF40" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG40" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-18 01:04:20</t>
+          <t>2026-03-18 03:13:28</t>
         </is>
       </c>
     </row>
@@ -8323,55 +8323,55 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="G41" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="H41" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I41" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="J41" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="O41" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P41" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T41" t="n">
         <v>1.79</v>
       </c>
-      <c r="Q41" t="n">
-        <v>2</v>
-      </c>
-      <c r="R41" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U41" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V41" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="W41" t="n">
         <v>1.47</v>
@@ -8380,34 +8380,34 @@
         <v>1000</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
@@ -8416,7 +8416,7 @@
         <v>1000</v>
       </c>
       <c r="AK41" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL41" t="n">
         <v>1000</v>
@@ -8425,68 +8425,68 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.09</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.09</v>
+        <v>15</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.09</v>
+        <v>8.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.09</v>
+        <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.09</v>
+        <v>22</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.09</v>
+        <v>17.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.09</v>
+        <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.09</v>
+     